--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_EXCEL_PERMISSION_ENGINE\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79CEF91-01D9-4684-81C6-2350167306D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DF6A58-CB9D-49E1-B631-3AE268473044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1501" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="112">
   <si>
     <t>Users &amp; Roles</t>
   </si>
@@ -291,79 +291,76 @@
     <t>Hide Button</t>
   </si>
   <si>
-    <t>Example only</t>
+    <t>Yes/No</t>
+  </si>
+  <si>
+    <t>Roles</t>
+  </si>
+  <si>
+    <t>Pages</t>
+  </si>
+  <si>
+    <t>Components / Tables</t>
+  </si>
+  <si>
+    <t>V42 Excel-Based Enterprise Permissions Matrix</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Use this workbook to control page, table/component visibility, and export buttons by Role or by individual Username.</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Only values Yes / No are accepted in permission columns.</t>
+  </si>
+  <si>
+    <t>Step 1</t>
+  </si>
+  <si>
+    <t>Add users in Users sheet.</t>
+  </si>
+  <si>
+    <t>Step 2</t>
+  </si>
+  <si>
+    <t>Set page access in Role_Page_Access.</t>
+  </si>
+  <si>
+    <t>Step 3</t>
+  </si>
+  <si>
+    <t>Set table/button/export permissions in Role_Component_Access.</t>
+  </si>
+  <si>
+    <t>Step 4</t>
+  </si>
+  <si>
+    <t>Use User_Override only when a specific user differs from their role.</t>
+  </si>
+  <si>
+    <t>Step 5</t>
+  </si>
+  <si>
+    <t>Save this file as data/permissions.xlsx in GitHub once app.py is updated to V42.</t>
+  </si>
+  <si>
+    <t>Important</t>
+  </si>
+  <si>
+    <t>V41 currently reads permissions from Streamlit Secrets. This Excel method requires V42 code update to read permissions.xlsx.</t>
+  </si>
+  <si>
+    <t>Recommendation</t>
+  </si>
+  <si>
+    <t>Keep admin permissions as Yes for all items to avoid lockout.</t>
   </si>
   <si>
     <t>Executive Financial Report</t>
-  </si>
-  <si>
-    <t>Yes/No</t>
-  </si>
-  <si>
-    <t>Roles</t>
-  </si>
-  <si>
-    <t>Pages</t>
-  </si>
-  <si>
-    <t>Components / Tables</t>
-  </si>
-  <si>
-    <t>V42 Excel-Based Enterprise Permissions Matrix</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Use this workbook to control page, table/component visibility, and export buttons by Role or by individual Username.</t>
-  </si>
-  <si>
-    <t>Rule</t>
-  </si>
-  <si>
-    <t>Only values Yes / No are accepted in permission columns.</t>
-  </si>
-  <si>
-    <t>Step 1</t>
-  </si>
-  <si>
-    <t>Add users in Users sheet.</t>
-  </si>
-  <si>
-    <t>Step 2</t>
-  </si>
-  <si>
-    <t>Set page access in Role_Page_Access.</t>
-  </si>
-  <si>
-    <t>Step 3</t>
-  </si>
-  <si>
-    <t>Set table/button/export permissions in Role_Component_Access.</t>
-  </si>
-  <si>
-    <t>Step 4</t>
-  </si>
-  <si>
-    <t>Use User_Override only when a specific user differs from their role.</t>
-  </si>
-  <si>
-    <t>Step 5</t>
-  </si>
-  <si>
-    <t>Save this file as data/permissions.xlsx in GitHub once app.py is updated to V42.</t>
-  </si>
-  <si>
-    <t>Important</t>
-  </si>
-  <si>
-    <t>V41 currently reads permissions from Streamlit Secrets. This Excel method requires V42 code update to read permissions.xlsx.</t>
-  </si>
-  <si>
-    <t>Recommendation</t>
-  </si>
-  <si>
-    <t>Keep admin permissions as Yes for all items to avoid lockout.</t>
   </si>
 </sst>
 </file>
@@ -559,7 +556,14 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ComponentAccessTable" displayName="ComponentAccessTable" ref="A3:H179">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ComponentAccessTable" displayName="ComponentAccessTable" ref="A3:H178">
+  <autoFilter ref="A3:H178" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Executive Reports"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Role"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -575,7 +579,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I49">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Page"/>
@@ -1369,7 +1373,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="55.59765625" customWidth="1"/>
@@ -1420,7 +1424,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1466,7 +1470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" hidden="1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1489,7 +1493,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" hidden="1">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1512,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1535,7 +1539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1558,7 +1562,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1581,7 +1585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1604,7 +1608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1650,7 +1654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1696,7 +1700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1719,7 +1723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1742,7 +1746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1765,7 +1769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1788,7 +1792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1811,7 +1815,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1834,7 +1838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1857,7 +1861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1880,7 +1884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1903,7 +1907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1926,7 +1930,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1949,7 +1953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1972,7 +1976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1995,7 +1999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -2041,7 +2045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -2064,7 +2068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2087,7 +2091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -2110,7 +2114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -2133,7 +2137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -2156,7 +2160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -2179,7 +2183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -2225,7 +2229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -2271,7 +2275,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2294,7 +2298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -2317,7 +2321,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -2340,7 +2344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -2363,7 +2367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2386,7 +2390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2409,7 +2413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -2432,7 +2436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -2455,7 +2459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -2478,7 +2482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -2501,7 +2505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -2524,7 +2528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -2547,7 +2551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -2570,7 +2574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2616,7 +2620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" hidden="1">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2639,7 +2643,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2662,7 +2666,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" hidden="1">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2685,7 +2689,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" hidden="1">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2708,7 +2712,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" hidden="1">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2731,7 +2735,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2754,7 +2758,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2800,7 +2804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" hidden="1">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2846,7 +2850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" hidden="1">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2869,7 +2873,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" hidden="1">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2892,7 +2896,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" hidden="1">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -2915,7 +2919,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" hidden="1">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2938,7 +2942,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" hidden="1">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -2961,7 +2965,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" hidden="1">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -2984,7 +2988,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" hidden="1">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -3007,7 +3011,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -3030,7 +3034,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -3053,7 +3057,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3076,7 +3080,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -3099,7 +3103,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -3122,7 +3126,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" hidden="1">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3145,7 +3149,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" hidden="1">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3191,7 +3195,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" hidden="1">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3214,7 +3218,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -3237,7 +3241,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" hidden="1">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3260,7 +3264,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" hidden="1">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -3283,7 +3287,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -3306,7 +3310,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -3329,7 +3333,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -3375,7 +3379,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>23</v>
       </c>
@@ -3421,7 +3425,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" hidden="1">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -3444,7 +3448,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" hidden="1">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -3467,7 +3471,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" hidden="1">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -3490,7 +3494,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -3513,7 +3517,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -3536,7 +3540,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" hidden="1">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -3559,7 +3563,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" hidden="1">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3582,7 +3586,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" hidden="1">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -3605,7 +3609,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" hidden="1">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -3628,7 +3632,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" hidden="1">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -3651,7 +3655,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" hidden="1">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -3674,7 +3678,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" hidden="1">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -3697,7 +3701,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" hidden="1">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -3720,7 +3724,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" hidden="1">
       <c r="A104" t="s">
         <v>29</v>
       </c>
@@ -3766,7 +3770,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" hidden="1">
       <c r="A106" t="s">
         <v>29</v>
       </c>
@@ -3789,7 +3793,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" hidden="1">
       <c r="A107" t="s">
         <v>29</v>
       </c>
@@ -3812,7 +3816,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" hidden="1">
       <c r="A108" t="s">
         <v>29</v>
       </c>
@@ -3835,7 +3839,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" hidden="1">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -3858,7 +3862,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" hidden="1">
       <c r="A110" t="s">
         <v>29</v>
       </c>
@@ -3881,7 +3885,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" hidden="1">
       <c r="A111" t="s">
         <v>29</v>
       </c>
@@ -3904,7 +3908,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" hidden="1">
       <c r="A112" t="s">
         <v>29</v>
       </c>
@@ -3950,7 +3954,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" hidden="1">
       <c r="A114" t="s">
         <v>29</v>
       </c>
@@ -3996,7 +4000,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" hidden="1">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -4019,7 +4023,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" hidden="1">
       <c r="A117" t="s">
         <v>29</v>
       </c>
@@ -4042,7 +4046,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" hidden="1">
       <c r="A118" t="s">
         <v>29</v>
       </c>
@@ -4065,7 +4069,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" hidden="1">
       <c r="A119" t="s">
         <v>29</v>
       </c>
@@ -4088,7 +4092,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" hidden="1">
       <c r="A120" t="s">
         <v>29</v>
       </c>
@@ -4111,7 +4115,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" hidden="1">
       <c r="A121" t="s">
         <v>29</v>
       </c>
@@ -4134,7 +4138,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" hidden="1">
       <c r="A122" t="s">
         <v>29</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" hidden="1">
       <c r="A123" t="s">
         <v>29</v>
       </c>
@@ -4180,7 +4184,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" hidden="1">
       <c r="A124" t="s">
         <v>29</v>
       </c>
@@ -4203,7 +4207,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" hidden="1">
       <c r="A125" t="s">
         <v>29</v>
       </c>
@@ -4226,7 +4230,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" hidden="1">
       <c r="A126" t="s">
         <v>29</v>
       </c>
@@ -4249,7 +4253,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" hidden="1">
       <c r="A127" t="s">
         <v>29</v>
       </c>
@@ -4272,7 +4276,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" hidden="1">
       <c r="A128" t="s">
         <v>29</v>
       </c>
@@ -4295,7 +4299,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" hidden="1">
       <c r="A129" t="s">
         <v>33</v>
       </c>
@@ -4341,7 +4345,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" hidden="1">
       <c r="A131" t="s">
         <v>33</v>
       </c>
@@ -4364,7 +4368,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" hidden="1">
       <c r="A132" t="s">
         <v>33</v>
       </c>
@@ -4387,7 +4391,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" hidden="1">
       <c r="A133" t="s">
         <v>33</v>
       </c>
@@ -4410,7 +4414,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" hidden="1">
       <c r="A134" t="s">
         <v>33</v>
       </c>
@@ -4433,7 +4437,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" hidden="1">
       <c r="A135" t="s">
         <v>33</v>
       </c>
@@ -4456,7 +4460,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" hidden="1">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -4479,7 +4483,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" hidden="1">
       <c r="A137" t="s">
         <v>33</v>
       </c>
@@ -4525,7 +4529,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" hidden="1">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -4571,7 +4575,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" hidden="1">
       <c r="A141" t="s">
         <v>33</v>
       </c>
@@ -4594,7 +4598,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" hidden="1">
       <c r="A142" t="s">
         <v>33</v>
       </c>
@@ -4617,7 +4621,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" hidden="1">
       <c r="A143" t="s">
         <v>33</v>
       </c>
@@ -4640,7 +4644,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" hidden="1">
       <c r="A144" t="s">
         <v>33</v>
       </c>
@@ -4663,7 +4667,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" hidden="1">
       <c r="A145" t="s">
         <v>33</v>
       </c>
@@ -4686,7 +4690,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" hidden="1">
       <c r="A146" t="s">
         <v>33</v>
       </c>
@@ -4709,7 +4713,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" hidden="1">
       <c r="A147" t="s">
         <v>33</v>
       </c>
@@ -4732,7 +4736,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" hidden="1">
       <c r="A148" t="s">
         <v>33</v>
       </c>
@@ -4755,7 +4759,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" hidden="1">
       <c r="A149" t="s">
         <v>33</v>
       </c>
@@ -4778,7 +4782,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" hidden="1">
       <c r="A150" t="s">
         <v>33</v>
       </c>
@@ -4801,7 +4805,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" hidden="1">
       <c r="A151" t="s">
         <v>33</v>
       </c>
@@ -4824,7 +4828,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" hidden="1">
       <c r="A152" t="s">
         <v>33</v>
       </c>
@@ -4847,7 +4851,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" hidden="1">
       <c r="A153" t="s">
         <v>33</v>
       </c>
@@ -4870,7 +4874,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" hidden="1">
       <c r="A154" t="s">
         <v>35</v>
       </c>
@@ -4916,7 +4920,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" hidden="1">
       <c r="A156" t="s">
         <v>35</v>
       </c>
@@ -4939,7 +4943,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" hidden="1">
       <c r="A157" t="s">
         <v>35</v>
       </c>
@@ -4962,7 +4966,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" hidden="1">
       <c r="A158" t="s">
         <v>35</v>
       </c>
@@ -4985,7 +4989,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" hidden="1">
       <c r="A159" t="s">
         <v>35</v>
       </c>
@@ -5008,7 +5012,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" hidden="1">
       <c r="A160" t="s">
         <v>35</v>
       </c>
@@ -5031,7 +5035,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" hidden="1">
       <c r="A161" t="s">
         <v>35</v>
       </c>
@@ -5054,7 +5058,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" hidden="1">
       <c r="A162" t="s">
         <v>35</v>
       </c>
@@ -5100,7 +5104,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" hidden="1">
       <c r="A164" t="s">
         <v>35</v>
       </c>
@@ -5146,7 +5150,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" hidden="1">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -5169,7 +5173,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" hidden="1">
       <c r="A167" t="s">
         <v>35</v>
       </c>
@@ -5192,7 +5196,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" hidden="1">
       <c r="A168" t="s">
         <v>35</v>
       </c>
@@ -5215,7 +5219,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" hidden="1">
       <c r="A169" t="s">
         <v>35</v>
       </c>
@@ -5238,7 +5242,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" hidden="1">
       <c r="A170" t="s">
         <v>35</v>
       </c>
@@ -5261,7 +5265,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" hidden="1">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -5284,7 +5288,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" hidden="1">
       <c r="A172" t="s">
         <v>35</v>
       </c>
@@ -5307,7 +5311,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" hidden="1">
       <c r="A173" t="s">
         <v>35</v>
       </c>
@@ -5330,7 +5334,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" hidden="1">
       <c r="A174" t="s">
         <v>35</v>
       </c>
@@ -5353,7 +5357,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" hidden="1">
       <c r="A175" t="s">
         <v>35</v>
       </c>
@@ -5376,7 +5380,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" hidden="1">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -5399,7 +5403,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" hidden="1">
       <c r="A177" t="s">
         <v>35</v>
       </c>
@@ -5422,7 +5426,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" hidden="1">
       <c r="A178" t="s">
         <v>35</v>
       </c>
@@ -5442,29 +5446,6 @@
         <v>53</v>
       </c>
       <c r="G178" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7">
-      <c r="A179" t="s">
-        <v>25</v>
-      </c>
-      <c r="B179" t="s">
-        <v>40</v>
-      </c>
-      <c r="C179" t="s">
-        <v>61</v>
-      </c>
-      <c r="D179" t="s">
-        <v>53</v>
-      </c>
-      <c r="E179" t="s">
-        <v>53</v>
-      </c>
-      <c r="F179" t="s">
-        <v>53</v>
-      </c>
-      <c r="G179" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5472,7 +5453,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G1000">
+  <conditionalFormatting sqref="D4:G999">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
@@ -5481,10 +5462,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="D4:G1000" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="D4:G999" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="A4:A1000" xr:uid="{00000000-0002-0000-0200-000001000000}">
+    <dataValidation type="list" sqref="A4:A999" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"admin,pmo,board,finance,audit,operations,viewer"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5497,7 +5478,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
@@ -5555,16 +5536,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>53</v>
@@ -5573,46 +5551,80 @@
         <v>53</v>
       </c>
       <c r="G4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" t="s">
-        <v>88</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>53</v>
-      </c>
-      <c r="I5" t="s">
-        <v>88</v>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G500">
+  <conditionalFormatting sqref="D4:G499">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
@@ -5621,7 +5633,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:G500" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="D4:G499" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5636,7 +5648,7 @@
           <x14:formula1>
             <xm:f>Users!$A$4:$A$200</xm:f>
           </x14:formula1>
-          <xm:sqref>A4:A500</xm:sqref>
+          <xm:sqref>A4:A499</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5657,16 +5669,16 @@
   <sheetData>
     <row r="1" spans="1:4" ht="25.65" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -5877,7 +5889,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -5887,10 +5899,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -5899,10 +5911,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -5911,10 +5923,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -5923,10 +5935,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -5935,10 +5947,10 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -5947,10 +5959,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -5959,10 +5971,10 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -5971,10 +5983,10 @@
     </row>
     <row r="10" spans="1:6" ht="27.6">
       <c r="A10" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -5983,10 +5995,10 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_EXCEL_PERMISSION_ENGINE\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DF6A58-CB9D-49E1-B631-3AE268473044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61F61FC-5BAE-4F50-A133-77086E7A4356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -872,7 +872,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>24</v>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_EXCEL_PERMISSION_ENGINE\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_1_EXCEL_PERMISSION_ENGINE_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61F61FC-5BAE-4F50-A133-77086E7A4356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE65E23E-2A72-4A5E-BCC1-2857ECEFBDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -436,15 +436,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,7 +748,7 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.296875" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20.09765625" customWidth="1"/>
     <col min="3" max="3" width="10.59765625" customWidth="1"/>
     <col min="4" max="4" width="7.69921875" customWidth="1"/>
     <col min="5" max="5" width="33.796875" customWidth="1"/>
@@ -756,14 +756,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="3" spans="1:6" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -872,7 +872,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>24</v>
@@ -984,16 +984,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:14" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -1387,16 +1387,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -5493,17 +5493,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
     </row>
     <row r="3" spans="1:9" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -5888,14 +5888,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_1_EXCEL_PERMISSION_ENGINE_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE65E23E-2A72-4A5E-BCC1-2857ECEFBDE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F2FBE5-BCC6-434A-B85E-89A7ED90CE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="27.6">
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>53</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_1_EXCEL_PERMISSION_ENGINE_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F2FBE5-BCC6-434A-B85E-89A7ED90CE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE8B52F-8FF4-4C2F-BFF9-4454AB0100A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="112">
   <si>
     <t>Users &amp; Roles</t>
   </si>
@@ -436,15 +436,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,13 +557,6 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ComponentAccessTable" displayName="ComponentAccessTable" ref="A3:H178">
-  <autoFilter ref="A3:H178" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Executive Reports"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Role"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -579,7 +572,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I48">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Page"/>
@@ -756,14 +749,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -984,16 +977,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:14" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -1376,7 +1369,7 @@
   <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="55.59765625" customWidth="1"/>
+    <col min="1" max="1" width="9.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.296875" customWidth="1"/>
     <col min="3" max="3" width="40.796875" customWidth="1"/>
     <col min="4" max="4" width="7.09765625" customWidth="1"/>
@@ -1387,16 +1380,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -1424,7 +1417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1470,7 +1463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1493,7 +1486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1516,7 +1509,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1539,7 +1532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1562,7 +1555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1585,7 +1578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1608,7 +1601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1654,7 +1647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1700,7 +1693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1723,7 +1716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1746,7 +1739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1769,7 +1762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1792,7 +1785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1815,7 +1808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1838,7 +1831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1861,7 +1854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1884,7 +1877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1907,7 +1900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1930,7 +1923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1953,7 +1946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1976,7 +1969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1999,7 +1992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -2045,7 +2038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -2068,7 +2061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2091,7 +2084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -2114,7 +2107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -2137,7 +2130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -2160,7 +2153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -2183,7 +2176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -2229,7 +2222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -2275,7 +2268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2298,7 +2291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -2321,7 +2314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -2344,7 +2337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -2367,7 +2360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2390,7 +2383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2413,7 +2406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -2436,7 +2429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -2459,7 +2452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -2482,7 +2475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -2505,7 +2498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -2528,7 +2521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -2551,7 +2544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -2574,7 +2567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2620,7 +2613,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2643,7 +2636,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2666,7 +2659,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2689,7 +2682,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2712,7 +2705,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2735,7 +2728,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2758,7 +2751,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2804,7 +2797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2850,7 +2843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2873,7 +2866,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2896,7 +2889,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -2919,7 +2912,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2942,7 +2935,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -2965,7 +2958,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -2988,7 +2981,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -3011,7 +3004,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -3034,7 +3027,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -3057,7 +3050,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3080,7 +3073,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -3103,7 +3096,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -3126,7 +3119,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3149,7 +3142,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3195,7 +3188,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3218,7 +3211,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -3241,7 +3234,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3264,7 +3257,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -3287,7 +3280,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -3310,7 +3303,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -3333,7 +3326,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -3379,7 +3372,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>23</v>
       </c>
@@ -3425,7 +3418,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -3448,7 +3441,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -3471,7 +3464,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -3494,7 +3487,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -3517,7 +3510,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -3540,7 +3533,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -3563,7 +3556,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3586,7 +3579,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -3609,7 +3602,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -3632,7 +3625,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -3655,7 +3648,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -3678,7 +3671,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -3701,7 +3694,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -3724,7 +3717,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>29</v>
       </c>
@@ -3770,7 +3763,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>29</v>
       </c>
@@ -3793,7 +3786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>29</v>
       </c>
@@ -3816,7 +3809,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>29</v>
       </c>
@@ -3839,7 +3832,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -3862,7 +3855,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>29</v>
       </c>
@@ -3885,7 +3878,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>29</v>
       </c>
@@ -3908,7 +3901,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>29</v>
       </c>
@@ -3954,7 +3947,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>29</v>
       </c>
@@ -4000,7 +3993,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -4023,7 +4016,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>29</v>
       </c>
@@ -4046,7 +4039,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>29</v>
       </c>
@@ -4069,7 +4062,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>29</v>
       </c>
@@ -4092,7 +4085,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>29</v>
       </c>
@@ -4115,7 +4108,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>29</v>
       </c>
@@ -4138,7 +4131,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>29</v>
       </c>
@@ -4161,7 +4154,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>29</v>
       </c>
@@ -4184,7 +4177,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>29</v>
       </c>
@@ -4207,7 +4200,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>29</v>
       </c>
@@ -4230,7 +4223,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>29</v>
       </c>
@@ -4253,7 +4246,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>29</v>
       </c>
@@ -4276,7 +4269,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>29</v>
       </c>
@@ -4299,7 +4292,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
         <v>33</v>
       </c>
@@ -4345,7 +4338,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
         <v>33</v>
       </c>
@@ -4368,7 +4361,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
         <v>33</v>
       </c>
@@ -4391,7 +4384,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
         <v>33</v>
       </c>
@@ -4414,7 +4407,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
         <v>33</v>
       </c>
@@ -4437,7 +4430,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
         <v>33</v>
       </c>
@@ -4460,7 +4453,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -4483,7 +4476,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
         <v>33</v>
       </c>
@@ -4529,7 +4522,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -4575,7 +4568,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
         <v>33</v>
       </c>
@@ -4598,7 +4591,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
         <v>33</v>
       </c>
@@ -4621,7 +4614,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
         <v>33</v>
       </c>
@@ -4644,7 +4637,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
         <v>33</v>
       </c>
@@ -4667,7 +4660,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>33</v>
       </c>
@@ -4690,7 +4683,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>33</v>
       </c>
@@ -4713,7 +4706,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>33</v>
       </c>
@@ -4736,7 +4729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>33</v>
       </c>
@@ -4759,7 +4752,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>33</v>
       </c>
@@ -4782,7 +4775,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>33</v>
       </c>
@@ -4805,7 +4798,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>33</v>
       </c>
@@ -4828,7 +4821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1">
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
         <v>33</v>
       </c>
@@ -4851,7 +4844,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>33</v>
       </c>
@@ -4874,7 +4867,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1">
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
         <v>35</v>
       </c>
@@ -4920,7 +4913,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1">
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
         <v>35</v>
       </c>
@@ -4943,7 +4936,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1">
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
         <v>35</v>
       </c>
@@ -4966,7 +4959,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1">
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
         <v>35</v>
       </c>
@@ -4989,7 +4982,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>35</v>
       </c>
@@ -5012,7 +5005,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1">
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
         <v>35</v>
       </c>
@@ -5035,7 +5028,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1">
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
         <v>35</v>
       </c>
@@ -5058,7 +5051,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1">
+    <row r="162" spans="1:7">
       <c r="A162" t="s">
         <v>35</v>
       </c>
@@ -5104,7 +5097,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1">
+    <row r="164" spans="1:7">
       <c r="A164" t="s">
         <v>35</v>
       </c>
@@ -5150,7 +5143,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -5173,7 +5166,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1">
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>35</v>
       </c>
@@ -5196,7 +5189,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1">
+    <row r="168" spans="1:7">
       <c r="A168" t="s">
         <v>35</v>
       </c>
@@ -5219,7 +5212,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1">
+    <row r="169" spans="1:7">
       <c r="A169" t="s">
         <v>35</v>
       </c>
@@ -5242,7 +5235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1">
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>35</v>
       </c>
@@ -5265,7 +5258,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -5288,7 +5281,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>35</v>
       </c>
@@ -5311,7 +5304,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>35</v>
       </c>
@@ -5334,7 +5327,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1">
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>35</v>
       </c>
@@ -5357,7 +5350,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1">
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>35</v>
       </c>
@@ -5380,7 +5373,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1">
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -5403,7 +5396,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>35</v>
       </c>
@@ -5426,7 +5419,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>35</v>
       </c>
@@ -5478,7 +5471,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
@@ -5493,17 +5486,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -5576,7 +5569,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -5585,38 +5578,15 @@
         <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5624,7 +5594,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G499">
+  <conditionalFormatting sqref="D4:G498">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
@@ -5633,7 +5603,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:G499" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="D4:G498" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5648,7 +5618,7 @@
           <x14:formula1>
             <xm:f>Users!$A$4:$A$200</xm:f>
           </x14:formula1>
-          <xm:sqref>A4:A499</xm:sqref>
+          <xm:sqref>A4:A498</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5888,14 +5858,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_1_EXCEL_PERMISSION_ENGINE_FIXED\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_EXCEL_PERMISSION_ENGINE\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE8B52F-8FF4-4C2F-BFF9-4454AB0100A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61F61FC-5BAE-4F50-A133-77086E7A4356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="112">
   <si>
     <t>Users &amp; Roles</t>
   </si>
@@ -557,6 +557,13 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ComponentAccessTable" displayName="ComponentAccessTable" ref="A3:H178">
+  <autoFilter ref="A3:H178" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Executive Reports"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Role"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -572,7 +579,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I49">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Page"/>
@@ -741,7 +748,7 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.296875" customWidth="1"/>
-    <col min="2" max="2" width="20.09765625" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="10.59765625" customWidth="1"/>
     <col min="4" max="4" width="7.69921875" customWidth="1"/>
     <col min="5" max="5" width="33.796875" customWidth="1"/>
@@ -854,7 +861,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="27.6">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -865,7 +872,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>24</v>
@@ -1187,7 +1194,7 @@
         <v>53</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
@@ -1369,7 +1376,7 @@
   <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.59765625" customWidth="1"/>
     <col min="2" max="2" width="20.296875" customWidth="1"/>
     <col min="3" max="3" width="40.796875" customWidth="1"/>
     <col min="4" max="4" width="7.09765625" customWidth="1"/>
@@ -1417,7 +1424,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1463,7 +1470,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" hidden="1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1486,7 +1493,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" hidden="1">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1532,7 +1539,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1555,7 +1562,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1578,7 +1585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1601,7 +1608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1647,7 +1654,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1693,7 +1700,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1716,7 +1723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1739,7 +1746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1762,7 +1769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1785,7 +1792,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1808,7 +1815,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1831,7 +1838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1854,7 +1861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1877,7 +1884,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1900,7 +1907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1923,7 +1930,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1946,7 +1953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1969,7 +1976,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1992,7 +1999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -2038,7 +2045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -2061,7 +2068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2084,7 +2091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -2107,7 +2114,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -2130,7 +2137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -2153,7 +2160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -2176,7 +2183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -2222,7 +2229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -2268,7 +2275,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2291,7 +2298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -2314,7 +2321,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -2337,7 +2344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -2360,7 +2367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2383,7 +2390,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2406,7 +2413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -2429,7 +2436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -2452,7 +2459,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -2475,7 +2482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -2498,7 +2505,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -2521,7 +2528,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -2544,7 +2551,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -2567,7 +2574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2613,7 +2620,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" hidden="1">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2636,7 +2643,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2659,7 +2666,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" hidden="1">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2682,7 +2689,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" hidden="1">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2705,7 +2712,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" hidden="1">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2728,7 +2735,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2751,7 +2758,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2797,7 +2804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" hidden="1">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2843,7 +2850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" hidden="1">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2866,7 +2873,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" hidden="1">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2889,7 +2896,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" hidden="1">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -2912,7 +2919,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" hidden="1">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2935,7 +2942,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" hidden="1">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -2958,7 +2965,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" hidden="1">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -2981,7 +2988,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" hidden="1">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -3004,7 +3011,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -3027,7 +3034,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -3050,7 +3057,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3073,7 +3080,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -3096,7 +3103,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -3119,7 +3126,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" hidden="1">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3142,7 +3149,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" hidden="1">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3188,7 +3195,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" hidden="1">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3211,7 +3218,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -3234,7 +3241,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" hidden="1">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3257,7 +3264,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" hidden="1">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -3280,7 +3287,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -3303,7 +3310,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -3326,7 +3333,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -3372,7 +3379,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>23</v>
       </c>
@@ -3418,7 +3425,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" hidden="1">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -3441,7 +3448,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" hidden="1">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -3464,7 +3471,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" hidden="1">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -3487,7 +3494,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -3510,7 +3517,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -3533,7 +3540,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" hidden="1">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -3556,7 +3563,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" hidden="1">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3579,7 +3586,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" hidden="1">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -3602,7 +3609,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" hidden="1">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -3625,7 +3632,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" hidden="1">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -3648,7 +3655,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" hidden="1">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -3671,7 +3678,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" hidden="1">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -3694,7 +3701,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" hidden="1">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -3717,7 +3724,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" hidden="1">
       <c r="A104" t="s">
         <v>29</v>
       </c>
@@ -3763,7 +3770,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" hidden="1">
       <c r="A106" t="s">
         <v>29</v>
       </c>
@@ -3786,7 +3793,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" hidden="1">
       <c r="A107" t="s">
         <v>29</v>
       </c>
@@ -3809,7 +3816,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" hidden="1">
       <c r="A108" t="s">
         <v>29</v>
       </c>
@@ -3832,7 +3839,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" hidden="1">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -3855,7 +3862,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" hidden="1">
       <c r="A110" t="s">
         <v>29</v>
       </c>
@@ -3878,7 +3885,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" hidden="1">
       <c r="A111" t="s">
         <v>29</v>
       </c>
@@ -3901,7 +3908,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" hidden="1">
       <c r="A112" t="s">
         <v>29</v>
       </c>
@@ -3947,7 +3954,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" hidden="1">
       <c r="A114" t="s">
         <v>29</v>
       </c>
@@ -3993,7 +4000,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" hidden="1">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -4016,7 +4023,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" hidden="1">
       <c r="A117" t="s">
         <v>29</v>
       </c>
@@ -4039,7 +4046,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" hidden="1">
       <c r="A118" t="s">
         <v>29</v>
       </c>
@@ -4062,7 +4069,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" hidden="1">
       <c r="A119" t="s">
         <v>29</v>
       </c>
@@ -4085,7 +4092,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" hidden="1">
       <c r="A120" t="s">
         <v>29</v>
       </c>
@@ -4108,7 +4115,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" hidden="1">
       <c r="A121" t="s">
         <v>29</v>
       </c>
@@ -4131,7 +4138,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" hidden="1">
       <c r="A122" t="s">
         <v>29</v>
       </c>
@@ -4154,7 +4161,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" hidden="1">
       <c r="A123" t="s">
         <v>29</v>
       </c>
@@ -4177,7 +4184,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" hidden="1">
       <c r="A124" t="s">
         <v>29</v>
       </c>
@@ -4200,7 +4207,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" hidden="1">
       <c r="A125" t="s">
         <v>29</v>
       </c>
@@ -4223,7 +4230,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" hidden="1">
       <c r="A126" t="s">
         <v>29</v>
       </c>
@@ -4246,7 +4253,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" hidden="1">
       <c r="A127" t="s">
         <v>29</v>
       </c>
@@ -4269,7 +4276,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" hidden="1">
       <c r="A128" t="s">
         <v>29</v>
       </c>
@@ -4292,7 +4299,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" hidden="1">
       <c r="A129" t="s">
         <v>33</v>
       </c>
@@ -4338,7 +4345,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" hidden="1">
       <c r="A131" t="s">
         <v>33</v>
       </c>
@@ -4361,7 +4368,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" hidden="1">
       <c r="A132" t="s">
         <v>33</v>
       </c>
@@ -4384,7 +4391,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" hidden="1">
       <c r="A133" t="s">
         <v>33</v>
       </c>
@@ -4407,7 +4414,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" hidden="1">
       <c r="A134" t="s">
         <v>33</v>
       </c>
@@ -4430,7 +4437,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" hidden="1">
       <c r="A135" t="s">
         <v>33</v>
       </c>
@@ -4453,7 +4460,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" hidden="1">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -4476,7 +4483,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" hidden="1">
       <c r="A137" t="s">
         <v>33</v>
       </c>
@@ -4522,7 +4529,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" hidden="1">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -4568,7 +4575,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" hidden="1">
       <c r="A141" t="s">
         <v>33</v>
       </c>
@@ -4591,7 +4598,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" hidden="1">
       <c r="A142" t="s">
         <v>33</v>
       </c>
@@ -4614,7 +4621,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" hidden="1">
       <c r="A143" t="s">
         <v>33</v>
       </c>
@@ -4637,7 +4644,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" hidden="1">
       <c r="A144" t="s">
         <v>33</v>
       </c>
@@ -4660,7 +4667,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" hidden="1">
       <c r="A145" t="s">
         <v>33</v>
       </c>
@@ -4683,7 +4690,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" hidden="1">
       <c r="A146" t="s">
         <v>33</v>
       </c>
@@ -4706,7 +4713,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" hidden="1">
       <c r="A147" t="s">
         <v>33</v>
       </c>
@@ -4729,7 +4736,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" hidden="1">
       <c r="A148" t="s">
         <v>33</v>
       </c>
@@ -4752,7 +4759,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" hidden="1">
       <c r="A149" t="s">
         <v>33</v>
       </c>
@@ -4775,7 +4782,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" hidden="1">
       <c r="A150" t="s">
         <v>33</v>
       </c>
@@ -4798,7 +4805,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" hidden="1">
       <c r="A151" t="s">
         <v>33</v>
       </c>
@@ -4821,7 +4828,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" hidden="1">
       <c r="A152" t="s">
         <v>33</v>
       </c>
@@ -4844,7 +4851,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" hidden="1">
       <c r="A153" t="s">
         <v>33</v>
       </c>
@@ -4867,7 +4874,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" hidden="1">
       <c r="A154" t="s">
         <v>35</v>
       </c>
@@ -4913,7 +4920,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" hidden="1">
       <c r="A156" t="s">
         <v>35</v>
       </c>
@@ -4936,7 +4943,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" hidden="1">
       <c r="A157" t="s">
         <v>35</v>
       </c>
@@ -4959,7 +4966,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" hidden="1">
       <c r="A158" t="s">
         <v>35</v>
       </c>
@@ -4982,7 +4989,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" hidden="1">
       <c r="A159" t="s">
         <v>35</v>
       </c>
@@ -5005,7 +5012,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" hidden="1">
       <c r="A160" t="s">
         <v>35</v>
       </c>
@@ -5028,7 +5035,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" hidden="1">
       <c r="A161" t="s">
         <v>35</v>
       </c>
@@ -5051,7 +5058,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" hidden="1">
       <c r="A162" t="s">
         <v>35</v>
       </c>
@@ -5097,7 +5104,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" hidden="1">
       <c r="A164" t="s">
         <v>35</v>
       </c>
@@ -5143,7 +5150,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" hidden="1">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -5166,7 +5173,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" hidden="1">
       <c r="A167" t="s">
         <v>35</v>
       </c>
@@ -5189,7 +5196,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" hidden="1">
       <c r="A168" t="s">
         <v>35</v>
       </c>
@@ -5212,7 +5219,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" hidden="1">
       <c r="A169" t="s">
         <v>35</v>
       </c>
@@ -5235,7 +5242,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" hidden="1">
       <c r="A170" t="s">
         <v>35</v>
       </c>
@@ -5258,7 +5265,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" hidden="1">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -5281,7 +5288,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" hidden="1">
       <c r="A172" t="s">
         <v>35</v>
       </c>
@@ -5304,7 +5311,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" hidden="1">
       <c r="A173" t="s">
         <v>35</v>
       </c>
@@ -5327,7 +5334,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" hidden="1">
       <c r="A174" t="s">
         <v>35</v>
       </c>
@@ -5350,7 +5357,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" hidden="1">
       <c r="A175" t="s">
         <v>35</v>
       </c>
@@ -5373,7 +5380,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" hidden="1">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -5396,7 +5403,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" hidden="1">
       <c r="A177" t="s">
         <v>35</v>
       </c>
@@ -5419,7 +5426,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" hidden="1">
       <c r="A178" t="s">
         <v>35</v>
       </c>
@@ -5471,7 +5478,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
@@ -5569,7 +5576,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -5578,15 +5585,38 @@
         <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5594,7 +5624,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G498">
+  <conditionalFormatting sqref="D4:G499">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
@@ -5603,7 +5633,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:G498" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="D4:G499" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5618,7 +5648,7 @@
           <x14:formula1>
             <xm:f>Users!$A$4:$A$200</xm:f>
           </x14:formula1>
-          <xm:sqref>A4:A498</xm:sqref>
+          <xm:sqref>A4:A499</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_EXCEL_PERMISSION_ENGINE\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_2_USER_OVERRIDE_NAVIGATION_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B61F61FC-5BAE-4F50-A133-77086E7A4356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA03122A-98C5-4F47-A5D2-9F203C6495C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="112">
   <si>
     <t>Users &amp; Roles</t>
   </si>
@@ -436,15 +436,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,13 +557,6 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ComponentAccessTable" displayName="ComponentAccessTable" ref="A3:H178">
-  <autoFilter ref="A3:H178" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Executive Reports"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Role"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -579,7 +572,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I48">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Page"/>
@@ -756,14 +749,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="3" spans="1:6" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -872,7 +865,7 @@
         <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>24</v>
@@ -984,16 +977,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:14" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -1194,7 +1187,7 @@
         <v>53</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
@@ -1387,16 +1380,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -1424,7 +1417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1470,7 +1463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1493,7 +1486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1516,7 +1509,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1539,7 +1532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1562,7 +1555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1585,7 +1578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1608,7 +1601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1654,7 +1647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1700,7 +1693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1723,7 +1716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1746,7 +1739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1769,7 +1762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1792,7 +1785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1815,7 +1808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1838,7 +1831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1861,7 +1854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1884,7 +1877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1907,7 +1900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1930,7 +1923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1953,7 +1946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1976,7 +1969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1999,7 +1992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -2045,7 +2038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -2068,7 +2061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2091,7 +2084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -2114,7 +2107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -2137,7 +2130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -2160,7 +2153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -2183,7 +2176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -2229,7 +2222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -2275,7 +2268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2298,7 +2291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -2321,7 +2314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -2344,7 +2337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -2367,7 +2360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2390,7 +2383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2413,7 +2406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -2436,7 +2429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -2459,7 +2452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -2482,7 +2475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -2505,7 +2498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -2528,7 +2521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -2551,7 +2544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -2574,7 +2567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2620,7 +2613,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2643,7 +2636,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2666,7 +2659,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2689,7 +2682,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2712,7 +2705,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2735,7 +2728,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2758,7 +2751,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2804,7 +2797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2850,7 +2843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2873,7 +2866,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2896,7 +2889,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -2919,7 +2912,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2942,7 +2935,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -2965,7 +2958,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -2988,7 +2981,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -3011,7 +3004,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -3034,7 +3027,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -3057,7 +3050,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3080,7 +3073,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -3103,7 +3096,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -3126,7 +3119,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3149,7 +3142,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3195,7 +3188,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3218,7 +3211,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -3241,7 +3234,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3264,7 +3257,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -3287,7 +3280,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -3310,7 +3303,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -3333,7 +3326,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -3379,7 +3372,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>23</v>
       </c>
@@ -3425,7 +3418,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -3448,7 +3441,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -3471,7 +3464,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -3494,7 +3487,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -3517,7 +3510,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -3540,7 +3533,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -3563,7 +3556,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3586,7 +3579,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -3609,7 +3602,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -3632,7 +3625,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -3655,7 +3648,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -3678,7 +3671,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -3701,7 +3694,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -3724,7 +3717,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>29</v>
       </c>
@@ -3770,7 +3763,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>29</v>
       </c>
@@ -3793,7 +3786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>29</v>
       </c>
@@ -3816,7 +3809,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>29</v>
       </c>
@@ -3839,7 +3832,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -3862,7 +3855,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>29</v>
       </c>
@@ -3885,7 +3878,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>29</v>
       </c>
@@ -3908,7 +3901,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>29</v>
       </c>
@@ -3954,7 +3947,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>29</v>
       </c>
@@ -4000,7 +3993,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -4023,7 +4016,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>29</v>
       </c>
@@ -4046,7 +4039,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>29</v>
       </c>
@@ -4069,7 +4062,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>29</v>
       </c>
@@ -4092,7 +4085,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>29</v>
       </c>
@@ -4115,7 +4108,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>29</v>
       </c>
@@ -4138,7 +4131,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>29</v>
       </c>
@@ -4161,7 +4154,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>29</v>
       </c>
@@ -4184,7 +4177,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>29</v>
       </c>
@@ -4207,7 +4200,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>29</v>
       </c>
@@ -4230,7 +4223,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>29</v>
       </c>
@@ -4253,7 +4246,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>29</v>
       </c>
@@ -4276,7 +4269,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>29</v>
       </c>
@@ -4299,7 +4292,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
         <v>33</v>
       </c>
@@ -4345,7 +4338,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
         <v>33</v>
       </c>
@@ -4368,7 +4361,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
         <v>33</v>
       </c>
@@ -4391,7 +4384,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
         <v>33</v>
       </c>
@@ -4414,7 +4407,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
         <v>33</v>
       </c>
@@ -4437,7 +4430,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
         <v>33</v>
       </c>
@@ -4460,7 +4453,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -4483,7 +4476,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
         <v>33</v>
       </c>
@@ -4529,7 +4522,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -4575,7 +4568,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
         <v>33</v>
       </c>
@@ -4598,7 +4591,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
         <v>33</v>
       </c>
@@ -4621,7 +4614,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
         <v>33</v>
       </c>
@@ -4644,7 +4637,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
         <v>33</v>
       </c>
@@ -4667,7 +4660,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>33</v>
       </c>
@@ -4690,7 +4683,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>33</v>
       </c>
@@ -4713,7 +4706,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>33</v>
       </c>
@@ -4736,7 +4729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>33</v>
       </c>
@@ -4759,7 +4752,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>33</v>
       </c>
@@ -4782,7 +4775,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>33</v>
       </c>
@@ -4805,7 +4798,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>33</v>
       </c>
@@ -4828,7 +4821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1">
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
         <v>33</v>
       </c>
@@ -4851,7 +4844,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>33</v>
       </c>
@@ -4874,7 +4867,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1">
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
         <v>35</v>
       </c>
@@ -4920,7 +4913,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1">
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
         <v>35</v>
       </c>
@@ -4943,7 +4936,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1">
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
         <v>35</v>
       </c>
@@ -4966,7 +4959,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1">
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
         <v>35</v>
       </c>
@@ -4989,7 +4982,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>35</v>
       </c>
@@ -5012,7 +5005,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1">
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
         <v>35</v>
       </c>
@@ -5035,7 +5028,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1">
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
         <v>35</v>
       </c>
@@ -5058,7 +5051,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1">
+    <row r="162" spans="1:7">
       <c r="A162" t="s">
         <v>35</v>
       </c>
@@ -5104,7 +5097,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1">
+    <row r="164" spans="1:7">
       <c r="A164" t="s">
         <v>35</v>
       </c>
@@ -5150,7 +5143,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -5173,7 +5166,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1">
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>35</v>
       </c>
@@ -5196,7 +5189,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1">
+    <row r="168" spans="1:7">
       <c r="A168" t="s">
         <v>35</v>
       </c>
@@ -5219,7 +5212,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1">
+    <row r="169" spans="1:7">
       <c r="A169" t="s">
         <v>35</v>
       </c>
@@ -5242,7 +5235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1">
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>35</v>
       </c>
@@ -5265,7 +5258,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -5288,7 +5281,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>35</v>
       </c>
@@ -5311,7 +5304,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>35</v>
       </c>
@@ -5334,7 +5327,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1">
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>35</v>
       </c>
@@ -5357,7 +5350,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1">
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>35</v>
       </c>
@@ -5380,7 +5373,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1">
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -5403,7 +5396,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>35</v>
       </c>
@@ -5426,7 +5419,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>35</v>
       </c>
@@ -5478,7 +5471,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
@@ -5493,17 +5486,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
     </row>
     <row r="3" spans="1:9" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -5576,7 +5569,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -5588,35 +5581,12 @@
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s">
-        <v>111</v>
-      </c>
-      <c r="D7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5624,7 +5594,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G499">
+  <conditionalFormatting sqref="D4:G498">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
@@ -5633,7 +5603,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:G499" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="D4:G498" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5648,7 +5618,7 @@
           <x14:formula1>
             <xm:f>Users!$A$4:$A$200</xm:f>
           </x14:formula1>
-          <xm:sqref>A4:A499</xm:sqref>
+          <xm:sqref>A4:A498</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5888,14 +5858,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_2_USER_OVERRIDE_NAVIGATION_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA03122A-98C5-4F47-A5D2-9F203C6495C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5094A3-B79C-4275-94DF-DBED9146F146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="112">
   <si>
     <t>Users &amp; Roles</t>
   </si>
@@ -572,7 +572,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I47">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Page"/>
@@ -1369,7 +1369,7 @@
   <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="55.59765625" customWidth="1"/>
+    <col min="1" max="1" width="9.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.296875" customWidth="1"/>
     <col min="3" max="3" width="40.796875" customWidth="1"/>
     <col min="4" max="4" width="7.09765625" customWidth="1"/>
@@ -5471,7 +5471,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
@@ -5552,10 +5552,13 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E5" t="s">
         <v>53</v>
@@ -5564,29 +5567,6 @@
         <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5594,7 +5574,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G498">
+  <conditionalFormatting sqref="D4:G497">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
@@ -5603,7 +5583,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:G498" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="D4:G497" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5618,7 +5598,7 @@
           <x14:formula1>
             <xm:f>Users!$A$4:$A$200</xm:f>
           </x14:formula1>
-          <xm:sqref>A4:A498</xm:sqref>
+          <xm:sqref>A4:A497</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_2_USER_OVERRIDE_NAVIGATION_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA5094A3-B79C-4275-94DF-DBED9146F146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F81CC0-D8CB-4689-9C35-7DC6455830A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -557,6 +557,18 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ComponentAccessTable" displayName="ComponentAccessTable" ref="A3:H178">
+  <autoFilter ref="A3:H178" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="finance"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Executive Reports"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Role"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -1417,7 +1429,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1440,7 +1452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" hidden="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1463,7 +1475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" hidden="1">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1486,7 +1498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" hidden="1">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1532,7 +1544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1555,7 +1567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1578,7 +1590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1601,7 +1613,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1624,7 +1636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" hidden="1">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1647,7 +1659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1670,7 +1682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" hidden="1">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1693,7 +1705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1716,7 +1728,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1739,7 +1751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1762,7 +1774,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1785,7 +1797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1808,7 +1820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1831,7 +1843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1854,7 +1866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1877,7 +1889,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1900,7 +1912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1923,7 +1935,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1946,7 +1958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1969,7 +1981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1992,7 +2004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -2015,7 +2027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -2038,7 +2050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -2061,7 +2073,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2084,7 +2096,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -2107,7 +2119,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -2130,7 +2142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -2153,7 +2165,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -2176,7 +2188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -2199,7 +2211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -2222,7 +2234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -2245,7 +2257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -2268,7 +2280,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2291,7 +2303,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -2314,7 +2326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -2337,7 +2349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -2360,7 +2372,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2383,7 +2395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2406,7 +2418,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -2429,7 +2441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -2452,7 +2464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -2475,7 +2487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -2498,7 +2510,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -2521,7 +2533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -2544,7 +2556,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -2567,7 +2579,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2590,7 +2602,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" hidden="1">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -2613,7 +2625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" hidden="1">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2636,7 +2648,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2659,7 +2671,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" hidden="1">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2682,7 +2694,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" hidden="1">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2705,7 +2717,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" hidden="1">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2728,7 +2740,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2751,7 +2763,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2774,7 +2786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -2797,7 +2809,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" hidden="1">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2820,7 +2832,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" hidden="1">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -2843,7 +2855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" hidden="1">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2866,7 +2878,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" hidden="1">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2889,7 +2901,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" hidden="1">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -2912,7 +2924,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" hidden="1">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2935,7 +2947,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" hidden="1">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -2958,7 +2970,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" hidden="1">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -2981,7 +2993,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" hidden="1">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -3004,7 +3016,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -3027,7 +3039,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -3050,7 +3062,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3073,7 +3085,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -3096,7 +3108,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -3119,7 +3131,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" hidden="1">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3142,7 +3154,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" hidden="1">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3176,19 +3188,19 @@
         <v>62</v>
       </c>
       <c r="D80" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G80" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" hidden="1">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3211,7 +3223,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -3234,7 +3246,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" hidden="1">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3257,7 +3269,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" hidden="1">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -3280,7 +3292,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -3303,7 +3315,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -3326,7 +3338,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -3360,19 +3372,19 @@
         <v>70</v>
       </c>
       <c r="D88" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F88" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G88" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>23</v>
       </c>
@@ -3406,19 +3418,19 @@
         <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F90" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G90" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" hidden="1">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -3441,7 +3453,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" hidden="1">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -3464,7 +3476,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" hidden="1">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -3487,7 +3499,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -3510,7 +3522,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -3533,7 +3545,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" hidden="1">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -3556,7 +3568,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" hidden="1">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3579,7 +3591,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" hidden="1">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -3602,7 +3614,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" hidden="1">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -3625,7 +3637,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" hidden="1">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -3648,7 +3660,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" hidden="1">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -3671,7 +3683,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" hidden="1">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -3694,7 +3706,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" hidden="1">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -3717,7 +3729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" hidden="1">
       <c r="A104" t="s">
         <v>29</v>
       </c>
@@ -3740,7 +3752,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" hidden="1">
       <c r="A105" t="s">
         <v>29</v>
       </c>
@@ -3763,7 +3775,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" hidden="1">
       <c r="A106" t="s">
         <v>29</v>
       </c>
@@ -3786,7 +3798,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" hidden="1">
       <c r="A107" t="s">
         <v>29</v>
       </c>
@@ -3809,7 +3821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" hidden="1">
       <c r="A108" t="s">
         <v>29</v>
       </c>
@@ -3832,7 +3844,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" hidden="1">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -3855,7 +3867,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" hidden="1">
       <c r="A110" t="s">
         <v>29</v>
       </c>
@@ -3878,7 +3890,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" hidden="1">
       <c r="A111" t="s">
         <v>29</v>
       </c>
@@ -3901,7 +3913,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" hidden="1">
       <c r="A112" t="s">
         <v>29</v>
       </c>
@@ -3924,7 +3936,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" hidden="1">
       <c r="A113" t="s">
         <v>29</v>
       </c>
@@ -3947,7 +3959,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" hidden="1">
       <c r="A114" t="s">
         <v>29</v>
       </c>
@@ -3970,7 +3982,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" hidden="1">
       <c r="A115" t="s">
         <v>29</v>
       </c>
@@ -3993,7 +4005,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" hidden="1">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -4016,7 +4028,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" hidden="1">
       <c r="A117" t="s">
         <v>29</v>
       </c>
@@ -4039,7 +4051,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" hidden="1">
       <c r="A118" t="s">
         <v>29</v>
       </c>
@@ -4062,7 +4074,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" hidden="1">
       <c r="A119" t="s">
         <v>29</v>
       </c>
@@ -4085,7 +4097,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" hidden="1">
       <c r="A120" t="s">
         <v>29</v>
       </c>
@@ -4108,7 +4120,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" hidden="1">
       <c r="A121" t="s">
         <v>29</v>
       </c>
@@ -4131,7 +4143,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" hidden="1">
       <c r="A122" t="s">
         <v>29</v>
       </c>
@@ -4154,7 +4166,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" hidden="1">
       <c r="A123" t="s">
         <v>29</v>
       </c>
@@ -4177,7 +4189,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" hidden="1">
       <c r="A124" t="s">
         <v>29</v>
       </c>
@@ -4200,7 +4212,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" hidden="1">
       <c r="A125" t="s">
         <v>29</v>
       </c>
@@ -4223,7 +4235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" hidden="1">
       <c r="A126" t="s">
         <v>29</v>
       </c>
@@ -4246,7 +4258,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" hidden="1">
       <c r="A127" t="s">
         <v>29</v>
       </c>
@@ -4269,7 +4281,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" hidden="1">
       <c r="A128" t="s">
         <v>29</v>
       </c>
@@ -4292,7 +4304,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" hidden="1">
       <c r="A129" t="s">
         <v>33</v>
       </c>
@@ -4315,7 +4327,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" hidden="1">
       <c r="A130" t="s">
         <v>33</v>
       </c>
@@ -4338,7 +4350,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" hidden="1">
       <c r="A131" t="s">
         <v>33</v>
       </c>
@@ -4361,7 +4373,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" hidden="1">
       <c r="A132" t="s">
         <v>33</v>
       </c>
@@ -4384,7 +4396,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" hidden="1">
       <c r="A133" t="s">
         <v>33</v>
       </c>
@@ -4407,7 +4419,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" hidden="1">
       <c r="A134" t="s">
         <v>33</v>
       </c>
@@ -4430,7 +4442,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" hidden="1">
       <c r="A135" t="s">
         <v>33</v>
       </c>
@@ -4453,7 +4465,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" hidden="1">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -4476,7 +4488,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" hidden="1">
       <c r="A137" t="s">
         <v>33</v>
       </c>
@@ -4499,7 +4511,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" hidden="1">
       <c r="A138" t="s">
         <v>33</v>
       </c>
@@ -4522,7 +4534,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" hidden="1">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -4545,7 +4557,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" hidden="1">
       <c r="A140" t="s">
         <v>33</v>
       </c>
@@ -4568,7 +4580,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" hidden="1">
       <c r="A141" t="s">
         <v>33</v>
       </c>
@@ -4591,7 +4603,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" hidden="1">
       <c r="A142" t="s">
         <v>33</v>
       </c>
@@ -4614,7 +4626,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" hidden="1">
       <c r="A143" t="s">
         <v>33</v>
       </c>
@@ -4637,7 +4649,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" hidden="1">
       <c r="A144" t="s">
         <v>33</v>
       </c>
@@ -4660,7 +4672,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" hidden="1">
       <c r="A145" t="s">
         <v>33</v>
       </c>
@@ -4683,7 +4695,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" hidden="1">
       <c r="A146" t="s">
         <v>33</v>
       </c>
@@ -4706,7 +4718,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" hidden="1">
       <c r="A147" t="s">
         <v>33</v>
       </c>
@@ -4729,7 +4741,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" hidden="1">
       <c r="A148" t="s">
         <v>33</v>
       </c>
@@ -4752,7 +4764,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" hidden="1">
       <c r="A149" t="s">
         <v>33</v>
       </c>
@@ -4775,7 +4787,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" hidden="1">
       <c r="A150" t="s">
         <v>33</v>
       </c>
@@ -4798,7 +4810,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" hidden="1">
       <c r="A151" t="s">
         <v>33</v>
       </c>
@@ -4821,7 +4833,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" hidden="1">
       <c r="A152" t="s">
         <v>33</v>
       </c>
@@ -4844,7 +4856,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" hidden="1">
       <c r="A153" t="s">
         <v>33</v>
       </c>
@@ -4867,7 +4879,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" hidden="1">
       <c r="A154" t="s">
         <v>35</v>
       </c>
@@ -4890,7 +4902,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" hidden="1">
       <c r="A155" t="s">
         <v>35</v>
       </c>
@@ -4913,7 +4925,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" hidden="1">
       <c r="A156" t="s">
         <v>35</v>
       </c>
@@ -4936,7 +4948,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" hidden="1">
       <c r="A157" t="s">
         <v>35</v>
       </c>
@@ -4959,7 +4971,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" hidden="1">
       <c r="A158" t="s">
         <v>35</v>
       </c>
@@ -4982,7 +4994,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" hidden="1">
       <c r="A159" t="s">
         <v>35</v>
       </c>
@@ -5005,7 +5017,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" hidden="1">
       <c r="A160" t="s">
         <v>35</v>
       </c>
@@ -5028,7 +5040,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" hidden="1">
       <c r="A161" t="s">
         <v>35</v>
       </c>
@@ -5051,7 +5063,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" hidden="1">
       <c r="A162" t="s">
         <v>35</v>
       </c>
@@ -5074,7 +5086,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" hidden="1">
       <c r="A163" t="s">
         <v>35</v>
       </c>
@@ -5097,7 +5109,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" hidden="1">
       <c r="A164" t="s">
         <v>35</v>
       </c>
@@ -5120,7 +5132,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" hidden="1">
       <c r="A165" t="s">
         <v>35</v>
       </c>
@@ -5143,7 +5155,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" hidden="1">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -5166,7 +5178,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" hidden="1">
       <c r="A167" t="s">
         <v>35</v>
       </c>
@@ -5189,7 +5201,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" hidden="1">
       <c r="A168" t="s">
         <v>35</v>
       </c>
@@ -5212,7 +5224,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" hidden="1">
       <c r="A169" t="s">
         <v>35</v>
       </c>
@@ -5235,7 +5247,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" hidden="1">
       <c r="A170" t="s">
         <v>35</v>
       </c>
@@ -5258,7 +5270,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" hidden="1">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -5281,7 +5293,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" hidden="1">
       <c r="A172" t="s">
         <v>35</v>
       </c>
@@ -5304,7 +5316,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" hidden="1">
       <c r="A173" t="s">
         <v>35</v>
       </c>
@@ -5327,7 +5339,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" hidden="1">
       <c r="A174" t="s">
         <v>35</v>
       </c>
@@ -5350,7 +5362,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" hidden="1">
       <c r="A175" t="s">
         <v>35</v>
       </c>
@@ -5373,7 +5385,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" hidden="1">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -5396,7 +5408,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" hidden="1">
       <c r="A177" t="s">
         <v>35</v>
       </c>
@@ -5419,7 +5431,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" hidden="1">
       <c r="A178" t="s">
         <v>35</v>
       </c>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_2_USER_OVERRIDE_NAVIGATION_FIXED\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_1_EXCEL_PERMISSION_ENGINE_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F81CC0-D8CB-4689-9C35-7DC6455830A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE8B52F-8FF4-4C2F-BFF9-4454AB0100A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="112">
   <si>
     <t>Users &amp; Roles</t>
   </si>
@@ -436,15 +436,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,18 +557,6 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ComponentAccessTable" displayName="ComponentAccessTable" ref="A3:H178">
-  <autoFilter ref="A3:H178" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="finance"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Executive Reports"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Role"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -584,7 +572,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="UserOverrideTable" displayName="UserOverrideTable" ref="A3:I48">
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Page"/>
@@ -753,7 +741,7 @@
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.296875" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="2" max="2" width="20.09765625" customWidth="1"/>
     <col min="3" max="3" width="10.59765625" customWidth="1"/>
     <col min="4" max="4" width="7.69921875" customWidth="1"/>
     <col min="5" max="5" width="33.796875" customWidth="1"/>
@@ -761,14 +749,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -866,7 +854,7 @@
       </c>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6" ht="27.6">
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -989,16 +977,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:14" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -1392,16 +1380,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="3" spans="1:8" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -1429,7 +1417,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1452,7 +1440,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1475,7 +1463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1498,7 +1486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1521,7 +1509,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1544,7 +1532,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1567,7 +1555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1590,7 +1578,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1613,7 +1601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1636,7 +1624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1659,7 +1647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1682,7 +1670,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1705,7 +1693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1728,7 +1716,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1751,7 +1739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1774,7 +1762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1797,7 +1785,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1820,7 +1808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1843,7 +1831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1866,7 +1854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1889,7 +1877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1912,7 +1900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1935,7 +1923,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1958,7 +1946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1981,7 +1969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -2004,7 +1992,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>15</v>
       </c>
@@ -2027,7 +2015,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>15</v>
       </c>
@@ -2050,7 +2038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>15</v>
       </c>
@@ -2073,7 +2061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>15</v>
       </c>
@@ -2096,7 +2084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>15</v>
       </c>
@@ -2119,7 +2107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>15</v>
       </c>
@@ -2142,7 +2130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -2165,7 +2153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>15</v>
       </c>
@@ -2188,7 +2176,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>15</v>
       </c>
@@ -2211,7 +2199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>15</v>
       </c>
@@ -2234,7 +2222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>15</v>
       </c>
@@ -2257,7 +2245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -2280,7 +2268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>15</v>
       </c>
@@ -2303,7 +2291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -2326,7 +2314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>15</v>
       </c>
@@ -2349,7 +2337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>15</v>
       </c>
@@ -2372,7 +2360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>15</v>
       </c>
@@ -2395,7 +2383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>15</v>
       </c>
@@ -2418,7 +2406,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -2441,7 +2429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>15</v>
       </c>
@@ -2464,7 +2452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -2487,7 +2475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -2510,7 +2498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>15</v>
       </c>
@@ -2533,7 +2521,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>15</v>
       </c>
@@ -2556,7 +2544,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -2579,7 +2567,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -2602,7 +2590,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -2625,7 +2613,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -2648,7 +2636,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -2671,7 +2659,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -2694,7 +2682,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -2717,7 +2705,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -2740,7 +2728,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -2763,7 +2751,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -2786,7 +2774,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -2809,7 +2797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -2832,7 +2820,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -2855,7 +2843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -2878,7 +2866,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -2901,7 +2889,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -2924,7 +2912,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -2947,7 +2935,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -2970,7 +2958,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -2993,7 +2981,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -3016,7 +3004,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -3039,7 +3027,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -3062,7 +3050,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3085,7 +3073,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -3108,7 +3096,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -3131,7 +3119,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3154,7 +3142,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3188,19 +3176,19 @@
         <v>62</v>
       </c>
       <c r="D80" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G80" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3223,7 +3211,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -3246,7 +3234,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3269,7 +3257,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -3292,7 +3280,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -3315,7 +3303,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -3338,7 +3326,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -3372,19 +3360,19 @@
         <v>70</v>
       </c>
       <c r="D88" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F88" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G88" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>23</v>
       </c>
@@ -3418,19 +3406,19 @@
         <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E90" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="F90" t="s">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="G90" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>23</v>
       </c>
@@ -3453,7 +3441,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>23</v>
       </c>
@@ -3476,7 +3464,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>23</v>
       </c>
@@ -3499,7 +3487,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>23</v>
       </c>
@@ -3522,7 +3510,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -3545,7 +3533,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>23</v>
       </c>
@@ -3568,7 +3556,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>23</v>
       </c>
@@ -3591,7 +3579,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>23</v>
       </c>
@@ -3614,7 +3602,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>23</v>
       </c>
@@ -3637,7 +3625,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>23</v>
       </c>
@@ -3660,7 +3648,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>23</v>
       </c>
@@ -3683,7 +3671,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>23</v>
       </c>
@@ -3706,7 +3694,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>23</v>
       </c>
@@ -3729,7 +3717,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>29</v>
       </c>
@@ -3752,7 +3740,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1">
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
         <v>29</v>
       </c>
@@ -3775,7 +3763,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>29</v>
       </c>
@@ -3798,7 +3786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>29</v>
       </c>
@@ -3821,7 +3809,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>29</v>
       </c>
@@ -3844,7 +3832,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>29</v>
       </c>
@@ -3867,7 +3855,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>29</v>
       </c>
@@ -3890,7 +3878,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>29</v>
       </c>
@@ -3913,7 +3901,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>29</v>
       </c>
@@ -3936,7 +3924,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>29</v>
       </c>
@@ -3959,7 +3947,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>29</v>
       </c>
@@ -3982,7 +3970,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1">
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>29</v>
       </c>
@@ -4005,7 +3993,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>29</v>
       </c>
@@ -4028,7 +4016,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>29</v>
       </c>
@@ -4051,7 +4039,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>29</v>
       </c>
@@ -4074,7 +4062,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>29</v>
       </c>
@@ -4097,7 +4085,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>29</v>
       </c>
@@ -4120,7 +4108,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>29</v>
       </c>
@@ -4143,7 +4131,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>29</v>
       </c>
@@ -4166,7 +4154,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>29</v>
       </c>
@@ -4189,7 +4177,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>29</v>
       </c>
@@ -4212,7 +4200,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>29</v>
       </c>
@@ -4235,7 +4223,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>29</v>
       </c>
@@ -4258,7 +4246,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>29</v>
       </c>
@@ -4281,7 +4269,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>29</v>
       </c>
@@ -4304,7 +4292,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
         <v>33</v>
       </c>
@@ -4327,7 +4315,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1">
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
         <v>33</v>
       </c>
@@ -4350,7 +4338,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
         <v>33</v>
       </c>
@@ -4373,7 +4361,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
         <v>33</v>
       </c>
@@ -4396,7 +4384,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
         <v>33</v>
       </c>
@@ -4419,7 +4407,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
         <v>33</v>
       </c>
@@ -4442,7 +4430,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
         <v>33</v>
       </c>
@@ -4465,7 +4453,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
         <v>33</v>
       </c>
@@ -4488,7 +4476,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
         <v>33</v>
       </c>
@@ -4511,7 +4499,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1">
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
         <v>33</v>
       </c>
@@ -4534,7 +4522,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
         <v>33</v>
       </c>
@@ -4557,7 +4545,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1">
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
         <v>33</v>
       </c>
@@ -4580,7 +4568,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
         <v>33</v>
       </c>
@@ -4603,7 +4591,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
         <v>33</v>
       </c>
@@ -4626,7 +4614,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
         <v>33</v>
       </c>
@@ -4649,7 +4637,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
         <v>33</v>
       </c>
@@ -4672,7 +4660,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>33</v>
       </c>
@@ -4695,7 +4683,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>33</v>
       </c>
@@ -4718,7 +4706,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>33</v>
       </c>
@@ -4741,7 +4729,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>33</v>
       </c>
@@ -4764,7 +4752,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>33</v>
       </c>
@@ -4787,7 +4775,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>33</v>
       </c>
@@ -4810,7 +4798,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>33</v>
       </c>
@@ -4833,7 +4821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1">
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
         <v>33</v>
       </c>
@@ -4856,7 +4844,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>33</v>
       </c>
@@ -4879,7 +4867,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1">
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
         <v>35</v>
       </c>
@@ -4902,7 +4890,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1">
+    <row r="155" spans="1:7">
       <c r="A155" t="s">
         <v>35</v>
       </c>
@@ -4925,7 +4913,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1">
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
         <v>35</v>
       </c>
@@ -4948,7 +4936,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1">
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
         <v>35</v>
       </c>
@@ -4971,7 +4959,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1">
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
         <v>35</v>
       </c>
@@ -4994,7 +4982,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>35</v>
       </c>
@@ -5017,7 +5005,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1">
+    <row r="160" spans="1:7">
       <c r="A160" t="s">
         <v>35</v>
       </c>
@@ -5040,7 +5028,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1">
+    <row r="161" spans="1:7">
       <c r="A161" t="s">
         <v>35</v>
       </c>
@@ -5063,7 +5051,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1">
+    <row r="162" spans="1:7">
       <c r="A162" t="s">
         <v>35</v>
       </c>
@@ -5086,7 +5074,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1">
+    <row r="163" spans="1:7">
       <c r="A163" t="s">
         <v>35</v>
       </c>
@@ -5109,7 +5097,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1">
+    <row r="164" spans="1:7">
       <c r="A164" t="s">
         <v>35</v>
       </c>
@@ -5132,7 +5120,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1">
+    <row r="165" spans="1:7">
       <c r="A165" t="s">
         <v>35</v>
       </c>
@@ -5155,7 +5143,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1">
+    <row r="166" spans="1:7">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -5178,7 +5166,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1">
+    <row r="167" spans="1:7">
       <c r="A167" t="s">
         <v>35</v>
       </c>
@@ -5201,7 +5189,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1">
+    <row r="168" spans="1:7">
       <c r="A168" t="s">
         <v>35</v>
       </c>
@@ -5224,7 +5212,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1">
+    <row r="169" spans="1:7">
       <c r="A169" t="s">
         <v>35</v>
       </c>
@@ -5247,7 +5235,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1">
+    <row r="170" spans="1:7">
       <c r="A170" t="s">
         <v>35</v>
       </c>
@@ -5270,7 +5258,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1">
+    <row r="171" spans="1:7">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -5293,7 +5281,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1">
+    <row r="172" spans="1:7">
       <c r="A172" t="s">
         <v>35</v>
       </c>
@@ -5316,7 +5304,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1">
+    <row r="173" spans="1:7">
       <c r="A173" t="s">
         <v>35</v>
       </c>
@@ -5339,7 +5327,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1">
+    <row r="174" spans="1:7">
       <c r="A174" t="s">
         <v>35</v>
       </c>
@@ -5362,7 +5350,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1">
+    <row r="175" spans="1:7">
       <c r="A175" t="s">
         <v>35</v>
       </c>
@@ -5385,7 +5373,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1">
+    <row r="176" spans="1:7">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -5408,7 +5396,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1">
+    <row r="177" spans="1:7">
       <c r="A177" t="s">
         <v>35</v>
       </c>
@@ -5431,7 +5419,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1">
+    <row r="178" spans="1:7">
       <c r="A178" t="s">
         <v>35</v>
       </c>
@@ -5483,7 +5471,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
@@ -5498,17 +5486,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
     </row>
     <row r="3" spans="1:9" ht="25.65" customHeight="1">
       <c r="A3" s="3" t="s">
@@ -5564,21 +5552,41 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>111</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5586,7 +5594,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G497">
+  <conditionalFormatting sqref="D4:G498">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
@@ -5595,7 +5603,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:G497" xr:uid="{00000000-0002-0000-0300-000000000000}">
+    <dataValidation type="list" sqref="D4:G498" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5610,7 +5618,7 @@
           <x14:formula1>
             <xm:f>Users!$A$4:$A$200</xm:f>
           </x14:formula1>
-          <xm:sqref>A4:A497</xm:sqref>
+          <xm:sqref>A4:A498</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5850,14 +5858,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_1_EXCEL_PERMISSION_ENGINE_FIXED\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_42_3_STRICT_RBAC_RENDERING_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE8B52F-8FF4-4C2F-BFF9-4454AB0100A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352A7B53-728F-428B-A60C-6565EFB87B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1477" uniqueCount="111">
   <si>
     <t>Users &amp; Roles</t>
   </si>
@@ -358,9 +358,6 @@
   </si>
   <si>
     <t>Keep admin permissions as Yes for all items to avoid lockout.</t>
-  </si>
-  <si>
-    <t>Executive Financial Report</t>
   </si>
 </sst>
 </file>
@@ -1081,40 +1078,40 @@
         <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>53</v>
@@ -1125,7 +1122,7 @@
         <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>53</v>
@@ -1134,19 +1131,19 @@
         <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>53</v>
@@ -1169,10 +1166,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>53</v>
@@ -1199,7 +1196,7 @@
         <v>53</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>53</v>
@@ -1219,19 +1216,19 @@
         <v>53</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>53</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>53</v>
@@ -1243,7 +1240,7 @@
         <v>53</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>53</v>
@@ -1257,16 +1254,16 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>53</v>
@@ -1275,19 +1272,19 @@
         <v>53</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>53</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>53</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>53</v>
@@ -1301,7 +1298,7 @@
         <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>53</v>
@@ -2003,16 +2000,16 @@
         <v>61</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F29" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G29" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2026,16 +2023,16 @@
         <v>62</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F30" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G30" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2049,16 +2046,16 @@
         <v>63</v>
       </c>
       <c r="D31" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G31" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2072,16 +2069,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G32" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2095,16 +2092,16 @@
         <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G33" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2118,16 +2115,16 @@
         <v>66</v>
       </c>
       <c r="D34" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G34" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2141,16 +2138,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G35" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2164,16 +2161,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E36" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G36" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2187,16 +2184,16 @@
         <v>69</v>
       </c>
       <c r="D37" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E37" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G37" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2210,16 +2207,16 @@
         <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G38" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2233,16 +2230,16 @@
         <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E39" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G39" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2256,16 +2253,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F40" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G40" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2279,16 +2276,16 @@
         <v>73</v>
       </c>
       <c r="D41" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G41" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2302,16 +2299,16 @@
         <v>74</v>
       </c>
       <c r="D42" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G42" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2325,16 +2322,16 @@
         <v>75</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G43" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2348,16 +2345,16 @@
         <v>76</v>
       </c>
       <c r="D44" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G44" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2371,16 +2368,16 @@
         <v>77</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G45" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2394,16 +2391,16 @@
         <v>78</v>
       </c>
       <c r="D46" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G46" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2417,16 +2414,16 @@
         <v>79</v>
       </c>
       <c r="D47" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E47" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G47" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2440,16 +2437,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E48" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F48" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G48" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2463,16 +2460,16 @@
         <v>81</v>
       </c>
       <c r="D49" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F49" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G49" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2486,16 +2483,16 @@
         <v>82</v>
       </c>
       <c r="D50" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F50" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G50" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2509,16 +2506,16 @@
         <v>83</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G51" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2532,16 +2529,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E52" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F52" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G52" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2555,16 +2552,16 @@
         <v>85</v>
       </c>
       <c r="D53" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F53" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G53" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2578,13 +2575,13 @@
         <v>61</v>
       </c>
       <c r="D54" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E54" t="s">
         <v>53</v>
       </c>
       <c r="F54" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G54" t="s">
         <v>53</v>
@@ -2601,16 +2598,16 @@
         <v>62</v>
       </c>
       <c r="D55" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E55" t="s">
         <v>53</v>
       </c>
       <c r="F55" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G55" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2624,13 +2621,13 @@
         <v>63</v>
       </c>
       <c r="D56" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E56" t="s">
         <v>53</v>
       </c>
       <c r="F56" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G56" t="s">
         <v>53</v>
@@ -2647,13 +2644,13 @@
         <v>64</v>
       </c>
       <c r="D57" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E57" t="s">
         <v>53</v>
       </c>
       <c r="F57" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G57" t="s">
         <v>53</v>
@@ -2785,16 +2782,16 @@
         <v>70</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E63" t="s">
         <v>53</v>
       </c>
       <c r="F63" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G63" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2831,16 +2828,16 @@
         <v>72</v>
       </c>
       <c r="D65" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E65" t="s">
         <v>53</v>
       </c>
       <c r="F65" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G65" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2854,13 +2851,13 @@
         <v>73</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E66" t="s">
         <v>53</v>
       </c>
       <c r="F66" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G66" t="s">
         <v>53</v>
@@ -2946,13 +2943,13 @@
         <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E70" t="s">
         <v>53</v>
       </c>
       <c r="F70" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G70" t="s">
         <v>53</v>
@@ -2969,13 +2966,13 @@
         <v>78</v>
       </c>
       <c r="D71" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E71" t="s">
         <v>53</v>
       </c>
       <c r="F71" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G71" t="s">
         <v>53</v>
@@ -2992,13 +2989,13 @@
         <v>79</v>
       </c>
       <c r="D72" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E72" t="s">
         <v>53</v>
       </c>
       <c r="F72" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G72" t="s">
         <v>53</v>
@@ -3015,13 +3012,13 @@
         <v>80</v>
       </c>
       <c r="D73" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E73" t="s">
         <v>53</v>
       </c>
       <c r="F73" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G73" t="s">
         <v>53</v>
@@ -3038,13 +3035,13 @@
         <v>81</v>
       </c>
       <c r="D74" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E74" t="s">
         <v>53</v>
       </c>
       <c r="F74" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G74" t="s">
         <v>53</v>
@@ -3061,13 +3058,13 @@
         <v>82</v>
       </c>
       <c r="D75" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E75" t="s">
         <v>53</v>
       </c>
       <c r="F75" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G75" t="s">
         <v>53</v>
@@ -3084,13 +3081,13 @@
         <v>83</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E76" t="s">
         <v>53</v>
       </c>
       <c r="F76" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G76" t="s">
         <v>53</v>
@@ -3107,13 +3104,13 @@
         <v>84</v>
       </c>
       <c r="D77" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E77" t="s">
         <v>53</v>
       </c>
       <c r="F77" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G77" t="s">
         <v>53</v>
@@ -3130,13 +3127,13 @@
         <v>85</v>
       </c>
       <c r="D78" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E78" t="s">
         <v>53</v>
       </c>
       <c r="F78" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G78" t="s">
         <v>53</v>
@@ -3176,13 +3173,13 @@
         <v>62</v>
       </c>
       <c r="D80" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F80" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G80" t="s">
         <v>53</v>
@@ -3245,13 +3242,13 @@
         <v>65</v>
       </c>
       <c r="D83" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F83" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G83" t="s">
         <v>53</v>
@@ -3291,13 +3288,13 @@
         <v>67</v>
       </c>
       <c r="D85" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E85" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F85" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G85" t="s">
         <v>53</v>
@@ -3314,13 +3311,13 @@
         <v>68</v>
       </c>
       <c r="D86" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F86" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G86" t="s">
         <v>53</v>
@@ -3337,13 +3334,13 @@
         <v>69</v>
       </c>
       <c r="D87" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E87" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F87" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G87" t="s">
         <v>53</v>
@@ -3360,13 +3357,13 @@
         <v>70</v>
       </c>
       <c r="D88" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F88" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G88" t="s">
         <v>53</v>
@@ -3383,13 +3380,13 @@
         <v>71</v>
       </c>
       <c r="D89" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E89" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F89" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G89" t="s">
         <v>53</v>
@@ -3406,13 +3403,13 @@
         <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E90" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F90" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G90" t="s">
         <v>53</v>
@@ -3429,13 +3426,13 @@
         <v>73</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E91" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F91" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G91" t="s">
         <v>53</v>
@@ -3498,13 +3495,13 @@
         <v>76</v>
       </c>
       <c r="D94" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F94" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G94" t="s">
         <v>53</v>
@@ -3751,13 +3748,13 @@
         <v>62</v>
       </c>
       <c r="D105" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E105" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F105" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G105" t="s">
         <v>53</v>
@@ -3935,13 +3932,13 @@
         <v>70</v>
       </c>
       <c r="D113" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E113" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F113" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G113" t="s">
         <v>53</v>
@@ -3981,13 +3978,13 @@
         <v>72</v>
       </c>
       <c r="D115" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E115" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F115" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G115" t="s">
         <v>53</v>
@@ -4027,13 +4024,13 @@
         <v>74</v>
       </c>
       <c r="D117" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E117" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F117" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G117" t="s">
         <v>53</v>
@@ -4050,13 +4047,13 @@
         <v>75</v>
       </c>
       <c r="D118" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E118" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F118" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G118" t="s">
         <v>53</v>
@@ -4303,13 +4300,13 @@
         <v>61</v>
       </c>
       <c r="D129" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E129" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F129" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G129" t="s">
         <v>53</v>
@@ -4326,13 +4323,13 @@
         <v>62</v>
       </c>
       <c r="D130" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E130" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F130" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G130" t="s">
         <v>53</v>
@@ -4349,13 +4346,13 @@
         <v>63</v>
       </c>
       <c r="D131" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F131" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G131" t="s">
         <v>53</v>
@@ -4372,13 +4369,13 @@
         <v>64</v>
       </c>
       <c r="D132" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E132" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F132" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G132" t="s">
         <v>53</v>
@@ -4395,13 +4392,13 @@
         <v>65</v>
       </c>
       <c r="D133" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E133" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F133" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G133" t="s">
         <v>53</v>
@@ -4418,13 +4415,13 @@
         <v>66</v>
       </c>
       <c r="D134" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E134" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F134" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G134" t="s">
         <v>53</v>
@@ -4441,13 +4438,13 @@
         <v>67</v>
       </c>
       <c r="D135" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E135" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F135" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G135" t="s">
         <v>53</v>
@@ -4464,13 +4461,13 @@
         <v>68</v>
       </c>
       <c r="D136" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E136" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F136" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G136" t="s">
         <v>53</v>
@@ -4487,13 +4484,13 @@
         <v>69</v>
       </c>
       <c r="D137" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E137" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F137" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G137" t="s">
         <v>53</v>
@@ -4510,13 +4507,13 @@
         <v>70</v>
       </c>
       <c r="D138" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E138" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F138" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G138" t="s">
         <v>53</v>
@@ -4533,13 +4530,13 @@
         <v>71</v>
       </c>
       <c r="D139" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E139" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F139" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G139" t="s">
         <v>53</v>
@@ -4556,13 +4553,13 @@
         <v>72</v>
       </c>
       <c r="D140" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E140" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F140" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G140" t="s">
         <v>53</v>
@@ -4579,13 +4576,13 @@
         <v>73</v>
       </c>
       <c r="D141" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E141" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F141" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G141" t="s">
         <v>53</v>
@@ -4605,10 +4602,10 @@
         <v>53</v>
       </c>
       <c r="E142" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F142" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G142" t="s">
         <v>53</v>
@@ -4625,13 +4622,13 @@
         <v>75</v>
       </c>
       <c r="D143" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E143" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F143" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G143" t="s">
         <v>53</v>
@@ -4648,13 +4645,13 @@
         <v>76</v>
       </c>
       <c r="D144" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E144" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F144" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G144" t="s">
         <v>53</v>
@@ -4671,13 +4668,13 @@
         <v>77</v>
       </c>
       <c r="D145" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E145" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F145" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G145" t="s">
         <v>53</v>
@@ -4694,13 +4691,13 @@
         <v>78</v>
       </c>
       <c r="D146" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E146" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F146" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G146" t="s">
         <v>53</v>
@@ -4717,13 +4714,13 @@
         <v>79</v>
       </c>
       <c r="D147" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E147" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F147" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G147" t="s">
         <v>53</v>
@@ -4740,13 +4737,13 @@
         <v>80</v>
       </c>
       <c r="D148" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E148" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F148" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G148" t="s">
         <v>53</v>
@@ -4763,13 +4760,13 @@
         <v>81</v>
       </c>
       <c r="D149" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E149" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F149" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G149" t="s">
         <v>53</v>
@@ -4786,13 +4783,13 @@
         <v>82</v>
       </c>
       <c r="D150" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E150" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F150" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G150" t="s">
         <v>53</v>
@@ -4809,13 +4806,13 @@
         <v>83</v>
       </c>
       <c r="D151" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E151" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F151" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G151" t="s">
         <v>53</v>
@@ -4832,13 +4829,13 @@
         <v>84</v>
       </c>
       <c r="D152" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E152" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F152" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G152" t="s">
         <v>53</v>
@@ -4855,13 +4852,13 @@
         <v>85</v>
       </c>
       <c r="D153" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E153" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="F153" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="G153" t="s">
         <v>53</v>
@@ -4878,7 +4875,7 @@
         <v>61</v>
       </c>
       <c r="D154" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E154" t="s">
         <v>53</v>
@@ -4924,7 +4921,7 @@
         <v>63</v>
       </c>
       <c r="D156" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E156" t="s">
         <v>53</v>
@@ -4947,7 +4944,7 @@
         <v>64</v>
       </c>
       <c r="D157" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E157" t="s">
         <v>53</v>
@@ -5154,7 +5151,7 @@
         <v>73</v>
       </c>
       <c r="D166" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E166" t="s">
         <v>53</v>
@@ -5269,7 +5266,7 @@
         <v>78</v>
       </c>
       <c r="D171" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E171" t="s">
         <v>53</v>
@@ -5315,7 +5312,7 @@
         <v>80</v>
       </c>
       <c r="D173" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E173" t="s">
         <v>53</v>
@@ -5430,7 +5427,7 @@
         <v>85</v>
       </c>
       <c r="D178" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E178" t="s">
         <v>53</v>
@@ -5471,7 +5468,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.59765625" customWidth="1"/>
@@ -5525,69 +5522,6 @@
       </c>
       <c r="I3" s="3" t="s">
         <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E5" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_43_USER_BASED_PERMISSION_ENGINE\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DB04DA-8F30-439C-9066-4167E31D823B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457161A2-EF59-41D7-9304-94891CDB79AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -506,6 +506,13 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="UserComponentAccessTable" displayName="UserComponentAccessTable" ref="A3:H159">
+  <autoFilter ref="A3:H159" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="ahmedfekry"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -2585,7 +2592,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -2608,7 +2615,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -2631,7 +2638,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -2654,7 +2661,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -2677,7 +2684,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -2700,7 +2707,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -2723,7 +2730,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -2746,7 +2753,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -2769,7 +2776,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -2792,7 +2799,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -2815,7 +2822,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -2838,7 +2845,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -2861,7 +2868,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -2884,7 +2891,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2907,7 +2914,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -2930,7 +2937,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -2953,7 +2960,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -2976,7 +2983,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -2999,7 +3006,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -3022,7 +3029,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -3045,7 +3052,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -3068,7 +3075,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -3091,7 +3098,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -3114,7 +3121,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -3137,7 +3144,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -3160,7 +3167,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" hidden="1">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -3183,7 +3190,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" hidden="1">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -3206,7 +3213,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" hidden="1">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -3229,7 +3236,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" hidden="1">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -3252,7 +3259,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" hidden="1">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -3275,7 +3282,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" hidden="1">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -3298,7 +3305,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" hidden="1">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -3321,7 +3328,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" hidden="1">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -3344,7 +3351,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" hidden="1">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -3367,7 +3374,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" hidden="1">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -3390,7 +3397,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" hidden="1">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -3413,7 +3420,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" hidden="1">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -3436,7 +3443,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" hidden="1">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -3459,7 +3466,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" hidden="1">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -3482,7 +3489,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" hidden="1">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -3505,7 +3512,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" hidden="1">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -3528,7 +3535,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" hidden="1">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -3551,7 +3558,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" hidden="1">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -3574,7 +3581,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" hidden="1">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -3597,7 +3604,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" hidden="1">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -3620,7 +3627,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" hidden="1">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3643,7 +3650,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" hidden="1">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -3666,7 +3673,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" hidden="1">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -3689,7 +3696,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" hidden="1">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3712,7 +3719,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" hidden="1">
       <c r="A79" t="s">
         <v>17</v>
       </c>
@@ -3735,7 +3742,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" hidden="1">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -3758,7 +3765,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" hidden="1">
       <c r="A81" t="s">
         <v>17</v>
       </c>
@@ -3781,7 +3788,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" t="s">
         <v>20</v>
       </c>
@@ -3804,7 +3811,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" hidden="1">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -3827,7 +3834,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" hidden="1">
       <c r="A84" t="s">
         <v>20</v>
       </c>
@@ -3850,7 +3857,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" hidden="1">
       <c r="A85" t="s">
         <v>20</v>
       </c>
@@ -3873,7 +3880,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" hidden="1">
       <c r="A86" t="s">
         <v>20</v>
       </c>
@@ -3896,7 +3903,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" hidden="1">
       <c r="A87" t="s">
         <v>20</v>
       </c>
@@ -3919,7 +3926,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" hidden="1">
       <c r="A88" t="s">
         <v>20</v>
       </c>
@@ -3942,7 +3949,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" hidden="1">
       <c r="A89" t="s">
         <v>20</v>
       </c>
@@ -3965,7 +3972,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" hidden="1">
       <c r="A90" t="s">
         <v>20</v>
       </c>
@@ -3988,7 +3995,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" hidden="1">
       <c r="A91" t="s">
         <v>20</v>
       </c>
@@ -4011,7 +4018,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" hidden="1">
       <c r="A92" t="s">
         <v>20</v>
       </c>
@@ -4034,7 +4041,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" hidden="1">
       <c r="A93" t="s">
         <v>20</v>
       </c>
@@ -4057,7 +4064,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" hidden="1">
       <c r="A94" t="s">
         <v>20</v>
       </c>
@@ -4080,7 +4087,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" hidden="1">
       <c r="A95" t="s">
         <v>20</v>
       </c>
@@ -4103,7 +4110,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" hidden="1">
       <c r="A96" t="s">
         <v>20</v>
       </c>
@@ -4126,7 +4133,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" hidden="1">
       <c r="A97" t="s">
         <v>20</v>
       </c>
@@ -4149,7 +4156,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" hidden="1">
       <c r="A98" t="s">
         <v>20</v>
       </c>
@@ -4172,7 +4179,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" hidden="1">
       <c r="A99" t="s">
         <v>20</v>
       </c>
@@ -4195,7 +4202,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" hidden="1">
       <c r="A100" t="s">
         <v>20</v>
       </c>
@@ -4218,7 +4225,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" hidden="1">
       <c r="A101" t="s">
         <v>20</v>
       </c>
@@ -4241,7 +4248,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" hidden="1">
       <c r="A102" t="s">
         <v>20</v>
       </c>
@@ -4264,7 +4271,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" hidden="1">
       <c r="A103" t="s">
         <v>20</v>
       </c>
@@ -4287,7 +4294,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" hidden="1">
       <c r="A104" t="s">
         <v>20</v>
       </c>
@@ -4310,7 +4317,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" hidden="1">
       <c r="A105" t="s">
         <v>20</v>
       </c>
@@ -4333,7 +4340,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" hidden="1">
       <c r="A106" t="s">
         <v>20</v>
       </c>
@@ -4356,7 +4363,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" hidden="1">
       <c r="A107" t="s">
         <v>20</v>
       </c>
@@ -4379,7 +4386,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" hidden="1">
       <c r="A108" t="s">
         <v>24</v>
       </c>
@@ -4402,7 +4409,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" hidden="1">
       <c r="A109" t="s">
         <v>24</v>
       </c>
@@ -4425,7 +4432,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" hidden="1">
       <c r="A110" t="s">
         <v>24</v>
       </c>
@@ -4448,7 +4455,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" hidden="1">
       <c r="A111" t="s">
         <v>24</v>
       </c>
@@ -4471,7 +4478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" hidden="1">
       <c r="A112" t="s">
         <v>24</v>
       </c>
@@ -4494,7 +4501,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" hidden="1">
       <c r="A113" t="s">
         <v>24</v>
       </c>
@@ -4517,7 +4524,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" hidden="1">
       <c r="A114" t="s">
         <v>24</v>
       </c>
@@ -4540,7 +4547,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" hidden="1">
       <c r="A115" t="s">
         <v>24</v>
       </c>
@@ -4563,7 +4570,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" hidden="1">
       <c r="A116" t="s">
         <v>24</v>
       </c>
@@ -4586,7 +4593,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" hidden="1">
       <c r="A117" t="s">
         <v>24</v>
       </c>
@@ -4609,7 +4616,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" hidden="1">
       <c r="A118" t="s">
         <v>24</v>
       </c>
@@ -4632,7 +4639,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" hidden="1">
       <c r="A119" t="s">
         <v>24</v>
       </c>
@@ -4655,7 +4662,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" hidden="1">
       <c r="A120" t="s">
         <v>24</v>
       </c>
@@ -4678,7 +4685,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" hidden="1">
       <c r="A121" t="s">
         <v>24</v>
       </c>
@@ -4701,7 +4708,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" hidden="1">
       <c r="A122" t="s">
         <v>24</v>
       </c>
@@ -4724,7 +4731,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" hidden="1">
       <c r="A123" t="s">
         <v>24</v>
       </c>
@@ -4747,7 +4754,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" hidden="1">
       <c r="A124" t="s">
         <v>24</v>
       </c>
@@ -4770,7 +4777,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" hidden="1">
       <c r="A125" t="s">
         <v>24</v>
       </c>
@@ -4793,7 +4800,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" hidden="1">
       <c r="A126" t="s">
         <v>24</v>
       </c>
@@ -4816,7 +4823,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" hidden="1">
       <c r="A127" t="s">
         <v>24</v>
       </c>
@@ -4839,7 +4846,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" hidden="1">
       <c r="A128" t="s">
         <v>24</v>
       </c>
@@ -4862,7 +4869,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" hidden="1">
       <c r="A129" t="s">
         <v>24</v>
       </c>
@@ -4885,7 +4892,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" hidden="1">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -4908,7 +4915,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" hidden="1">
       <c r="A131" t="s">
         <v>24</v>
       </c>
@@ -4931,7 +4938,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" hidden="1">
       <c r="A132" t="s">
         <v>24</v>
       </c>
@@ -4954,7 +4961,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" hidden="1">
       <c r="A133" t="s">
         <v>24</v>
       </c>
@@ -4977,7 +4984,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" hidden="1">
       <c r="A134" t="s">
         <v>28</v>
       </c>
@@ -5000,7 +5007,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" hidden="1">
       <c r="A135" t="s">
         <v>28</v>
       </c>
@@ -5023,7 +5030,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" hidden="1">
       <c r="A136" t="s">
         <v>28</v>
       </c>
@@ -5046,7 +5053,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" hidden="1">
       <c r="A137" t="s">
         <v>28</v>
       </c>
@@ -5069,7 +5076,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" hidden="1">
       <c r="A138" t="s">
         <v>28</v>
       </c>
@@ -5092,7 +5099,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" hidden="1">
       <c r="A139" t="s">
         <v>28</v>
       </c>
@@ -5115,7 +5122,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" hidden="1">
       <c r="A140" t="s">
         <v>28</v>
       </c>
@@ -5138,7 +5145,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" hidden="1">
       <c r="A141" t="s">
         <v>28</v>
       </c>
@@ -5161,7 +5168,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" hidden="1">
       <c r="A142" t="s">
         <v>28</v>
       </c>
@@ -5184,7 +5191,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" hidden="1">
       <c r="A143" t="s">
         <v>28</v>
       </c>
@@ -5207,7 +5214,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" hidden="1">
       <c r="A144" t="s">
         <v>28</v>
       </c>
@@ -5230,7 +5237,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" hidden="1">
       <c r="A145" t="s">
         <v>28</v>
       </c>
@@ -5253,7 +5260,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" hidden="1">
       <c r="A146" t="s">
         <v>28</v>
       </c>
@@ -5276,7 +5283,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" hidden="1">
       <c r="A147" t="s">
         <v>28</v>
       </c>
@@ -5299,7 +5306,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" hidden="1">
       <c r="A148" t="s">
         <v>28</v>
       </c>
@@ -5322,7 +5329,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" hidden="1">
       <c r="A149" t="s">
         <v>28</v>
       </c>
@@ -5345,7 +5352,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" hidden="1">
       <c r="A150" t="s">
         <v>28</v>
       </c>
@@ -5368,7 +5375,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" hidden="1">
       <c r="A151" t="s">
         <v>28</v>
       </c>
@@ -5391,7 +5398,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" hidden="1">
       <c r="A152" t="s">
         <v>28</v>
       </c>
@@ -5414,7 +5421,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" hidden="1">
       <c r="A153" t="s">
         <v>28</v>
       </c>
@@ -5437,7 +5444,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" hidden="1">
       <c r="A154" t="s">
         <v>28</v>
       </c>
@@ -5460,7 +5467,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" hidden="1">
       <c r="A155" t="s">
         <v>28</v>
       </c>
@@ -5483,7 +5490,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" hidden="1">
       <c r="A156" t="s">
         <v>28</v>
       </c>
@@ -5506,7 +5513,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" hidden="1">
       <c r="A157" t="s">
         <v>28</v>
       </c>
@@ -5529,7 +5536,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" hidden="1">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -5552,7 +5559,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" hidden="1">
       <c r="A159" t="s">
         <v>28</v>
       </c>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_43_USER_BASED_PERMISSION_ENGINE\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_43_1_USER_BASED_PERMISSION_ENGINE_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{457161A2-EF59-41D7-9304-94891CDB79AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B996879B-467B-45C0-84A3-D5D5C84DC4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -506,13 +506,7 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="UserComponentAccessTable" displayName="UserComponentAccessTable" ref="A3:H159">
-  <autoFilter ref="A3:H159" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="ahmedfekry"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:H159" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -1755,7 +1749,7 @@
         <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E6" t="s">
         <v>46</v>
@@ -1773,7 +1767,7 @@
         <v>46</v>
       </c>
       <c r="J6" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="K6" t="s">
         <v>46</v>
@@ -2592,7 +2586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -2615,7 +2609,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -2638,7 +2632,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -2661,7 +2655,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -2684,7 +2678,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -2707,7 +2701,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -2730,7 +2724,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -2753,7 +2747,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -2776,7 +2770,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -2799,7 +2793,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -2822,7 +2816,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -2845,7 +2839,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -2868,7 +2862,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -2891,7 +2885,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2914,7 +2908,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -2937,7 +2931,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1">
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -2960,7 +2954,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -2983,7 +2977,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -3006,7 +3000,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -3029,7 +3023,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -3052,7 +3046,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -3075,7 +3069,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -3098,7 +3092,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -3121,7 +3115,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -3144,7 +3138,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -3167,7 +3161,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1">
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -3190,7 +3184,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1">
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -3213,7 +3207,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -3236,7 +3230,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1">
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -3259,7 +3253,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1">
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -3282,7 +3276,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1">
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -3305,7 +3299,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -3328,7 +3322,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -3351,7 +3345,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -3374,7 +3368,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -3397,7 +3391,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1">
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -3420,7 +3414,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -3443,7 +3437,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1">
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -3466,7 +3460,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -3489,7 +3483,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1">
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -3512,7 +3506,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -3535,7 +3529,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -3558,7 +3552,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -3581,7 +3575,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -3604,7 +3598,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -3627,7 +3621,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3650,7 +3644,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -3673,7 +3667,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -3696,7 +3690,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -3719,7 +3713,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>17</v>
       </c>
@@ -3742,7 +3736,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1">
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -3765,7 +3759,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>17</v>
       </c>
@@ -3788,7 +3782,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>20</v>
       </c>
@@ -3811,7 +3805,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -3834,7 +3828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1">
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>20</v>
       </c>
@@ -3857,7 +3851,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1">
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>20</v>
       </c>
@@ -3880,7 +3874,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>20</v>
       </c>
@@ -3903,7 +3897,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>20</v>
       </c>
@@ -3926,7 +3920,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1">
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>20</v>
       </c>
@@ -3949,7 +3943,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>20</v>
       </c>
@@ -3972,7 +3966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1">
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>20</v>
       </c>
@@ -3995,7 +3989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>20</v>
       </c>
@@ -4018,7 +4012,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>20</v>
       </c>
@@ -4041,7 +4035,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1">
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>20</v>
       </c>
@@ -4064,7 +4058,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>20</v>
       </c>
@@ -4087,7 +4081,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>20</v>
       </c>
@@ -4110,7 +4104,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>20</v>
       </c>
@@ -4133,7 +4127,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1">
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>20</v>
       </c>
@@ -4156,7 +4150,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1">
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>20</v>
       </c>
@@ -4179,7 +4173,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1">
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>20</v>
       </c>
@@ -4202,7 +4196,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1">
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>20</v>
       </c>
@@ -4225,7 +4219,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1">
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>20</v>
       </c>
@@ -4248,7 +4242,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1">
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>20</v>
       </c>
@@ -4271,7 +4265,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1">
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>20</v>
       </c>
@@ -4294,7 +4288,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1">
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>20</v>
       </c>
@@ -4317,7 +4311,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1">
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
         <v>20</v>
       </c>
@@ -4340,7 +4334,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1">
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>20</v>
       </c>
@@ -4363,7 +4357,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1">
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>20</v>
       </c>
@@ -4386,7 +4380,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1">
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>24</v>
       </c>
@@ -4409,7 +4403,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1">
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>24</v>
       </c>
@@ -4432,7 +4426,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1">
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>24</v>
       </c>
@@ -4455,7 +4449,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1">
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>24</v>
       </c>
@@ -4478,7 +4472,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1">
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>24</v>
       </c>
@@ -4501,7 +4495,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1">
+    <row r="113" spans="1:7">
       <c r="A113" t="s">
         <v>24</v>
       </c>
@@ -4524,7 +4518,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1">
+    <row r="114" spans="1:7">
       <c r="A114" t="s">
         <v>24</v>
       </c>
@@ -4547,7 +4541,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1">
+    <row r="115" spans="1:7">
       <c r="A115" t="s">
         <v>24</v>
       </c>
@@ -4570,7 +4564,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1">
+    <row r="116" spans="1:7">
       <c r="A116" t="s">
         <v>24</v>
       </c>
@@ -4593,7 +4587,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1">
+    <row r="117" spans="1:7">
       <c r="A117" t="s">
         <v>24</v>
       </c>
@@ -4616,7 +4610,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1">
+    <row r="118" spans="1:7">
       <c r="A118" t="s">
         <v>24</v>
       </c>
@@ -4639,7 +4633,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1">
+    <row r="119" spans="1:7">
       <c r="A119" t="s">
         <v>24</v>
       </c>
@@ -4662,7 +4656,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1">
+    <row r="120" spans="1:7">
       <c r="A120" t="s">
         <v>24</v>
       </c>
@@ -4685,7 +4679,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1">
+    <row r="121" spans="1:7">
       <c r="A121" t="s">
         <v>24</v>
       </c>
@@ -4708,7 +4702,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1">
+    <row r="122" spans="1:7">
       <c r="A122" t="s">
         <v>24</v>
       </c>
@@ -4731,7 +4725,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1">
+    <row r="123" spans="1:7">
       <c r="A123" t="s">
         <v>24</v>
       </c>
@@ -4754,7 +4748,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1">
+    <row r="124" spans="1:7">
       <c r="A124" t="s">
         <v>24</v>
       </c>
@@ -4777,7 +4771,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1">
+    <row r="125" spans="1:7">
       <c r="A125" t="s">
         <v>24</v>
       </c>
@@ -4800,7 +4794,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1">
+    <row r="126" spans="1:7">
       <c r="A126" t="s">
         <v>24</v>
       </c>
@@ -4823,7 +4817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1">
+    <row r="127" spans="1:7">
       <c r="A127" t="s">
         <v>24</v>
       </c>
@@ -4846,7 +4840,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1">
+    <row r="128" spans="1:7">
       <c r="A128" t="s">
         <v>24</v>
       </c>
@@ -4869,7 +4863,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1">
+    <row r="129" spans="1:7">
       <c r="A129" t="s">
         <v>24</v>
       </c>
@@ -4892,7 +4886,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1">
+    <row r="130" spans="1:7">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -4915,7 +4909,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1">
+    <row r="131" spans="1:7">
       <c r="A131" t="s">
         <v>24</v>
       </c>
@@ -4938,7 +4932,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1">
+    <row r="132" spans="1:7">
       <c r="A132" t="s">
         <v>24</v>
       </c>
@@ -4961,7 +4955,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1">
+    <row r="133" spans="1:7">
       <c r="A133" t="s">
         <v>24</v>
       </c>
@@ -4984,7 +4978,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1">
+    <row r="134" spans="1:7">
       <c r="A134" t="s">
         <v>28</v>
       </c>
@@ -5007,7 +5001,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1">
+    <row r="135" spans="1:7">
       <c r="A135" t="s">
         <v>28</v>
       </c>
@@ -5030,7 +5024,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1">
+    <row r="136" spans="1:7">
       <c r="A136" t="s">
         <v>28</v>
       </c>
@@ -5053,7 +5047,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1">
+    <row r="137" spans="1:7">
       <c r="A137" t="s">
         <v>28</v>
       </c>
@@ -5076,7 +5070,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1">
+    <row r="138" spans="1:7">
       <c r="A138" t="s">
         <v>28</v>
       </c>
@@ -5099,7 +5093,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1">
+    <row r="139" spans="1:7">
       <c r="A139" t="s">
         <v>28</v>
       </c>
@@ -5122,7 +5116,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1">
+    <row r="140" spans="1:7">
       <c r="A140" t="s">
         <v>28</v>
       </c>
@@ -5145,7 +5139,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1">
+    <row r="141" spans="1:7">
       <c r="A141" t="s">
         <v>28</v>
       </c>
@@ -5168,7 +5162,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1">
+    <row r="142" spans="1:7">
       <c r="A142" t="s">
         <v>28</v>
       </c>
@@ -5191,7 +5185,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1">
+    <row r="143" spans="1:7">
       <c r="A143" t="s">
         <v>28</v>
       </c>
@@ -5214,7 +5208,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1">
+    <row r="144" spans="1:7">
       <c r="A144" t="s">
         <v>28</v>
       </c>
@@ -5237,7 +5231,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1">
+    <row r="145" spans="1:7">
       <c r="A145" t="s">
         <v>28</v>
       </c>
@@ -5260,7 +5254,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1">
+    <row r="146" spans="1:7">
       <c r="A146" t="s">
         <v>28</v>
       </c>
@@ -5283,7 +5277,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1">
+    <row r="147" spans="1:7">
       <c r="A147" t="s">
         <v>28</v>
       </c>
@@ -5306,7 +5300,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1">
+    <row r="148" spans="1:7">
       <c r="A148" t="s">
         <v>28</v>
       </c>
@@ -5329,7 +5323,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1">
+    <row r="149" spans="1:7">
       <c r="A149" t="s">
         <v>28</v>
       </c>
@@ -5352,7 +5346,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1">
+    <row r="150" spans="1:7">
       <c r="A150" t="s">
         <v>28</v>
       </c>
@@ -5375,7 +5369,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1">
+    <row r="151" spans="1:7">
       <c r="A151" t="s">
         <v>28</v>
       </c>
@@ -5398,7 +5392,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1">
+    <row r="152" spans="1:7">
       <c r="A152" t="s">
         <v>28</v>
       </c>
@@ -5421,7 +5415,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1">
+    <row r="153" spans="1:7">
       <c r="A153" t="s">
         <v>28</v>
       </c>
@@ -5444,7 +5438,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1">
+    <row r="154" spans="1:7">
       <c r="A154" t="s">
         <v>28</v>
       </c>
@@ -5467,7 +5461,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1">
+    <row r="155" spans="1:7">
       <c r="A155" t="s">
         <v>28</v>
       </c>
@@ -5490,7 +5484,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1">
+    <row r="156" spans="1:7">
       <c r="A156" t="s">
         <v>28</v>
       </c>
@@ -5513,7 +5507,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1">
+    <row r="157" spans="1:7">
       <c r="A157" t="s">
         <v>28</v>
       </c>
@@ -5536,7 +5530,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1">
+    <row r="158" spans="1:7">
       <c r="A158" t="s">
         <v>28</v>
       </c>
@@ -5559,7 +5553,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1">
+    <row r="159" spans="1:7">
       <c r="A159" t="s">
         <v>28</v>
       </c>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_43_1_USER_BASED_PERMISSION_ENGINE_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B996879B-467B-45C0-84A3-D5D5C84DC4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA47EC1-136A-4996-B0EF-EA7658DD0896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="100">
   <si>
     <t>Users</t>
   </si>
@@ -74,16 +74,10 @@
     <t>Finance</t>
   </si>
   <si>
-    <t>Example: PPT Builder allowed</t>
-  </si>
-  <si>
     <t>mohamed_syed</t>
   </si>
   <si>
     <t>Mohamed@12345$</t>
-  </si>
-  <si>
-    <t>Example: PPT Builder not allowed</t>
   </si>
   <si>
     <t>board_user</t>
@@ -506,7 +500,13 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="UserComponentAccessTable" displayName="UserComponentAccessTable" ref="A3:H159">
-  <autoFilter ref="A3:H159" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
+  <autoFilter ref="A3:H159" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="mohamed_syed"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -743,16 +743,14 @@
       <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>15</v>
@@ -763,68 +761,66 @@
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1590,7 +1586,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="22.35" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1611,43 +1607,43 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1699,219 +1695,219 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J6" t="s">
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1952,7 +1948,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.35" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1967,36 +1963,36 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" hidden="1">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -2011,15 +2007,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" hidden="1">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -2034,15 +2030,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" hidden="1">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
@@ -2057,15 +2053,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" hidden="1">
       <c r="A7" t="s">
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -2080,15 +2076,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" hidden="1">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -2103,15 +2099,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" hidden="1">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -2126,15 +2122,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" t="s">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -2149,15 +2145,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -2172,15 +2168,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" t="s">
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -2195,15 +2191,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" hidden="1">
       <c r="A13" t="s">
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -2218,15 +2214,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -2241,15 +2237,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" hidden="1">
       <c r="A15" t="s">
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -2264,15 +2260,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" hidden="1">
       <c r="A16" t="s">
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -2287,15 +2283,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" hidden="1">
       <c r="A17" t="s">
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -2310,15 +2306,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" hidden="1">
       <c r="A18" t="s">
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
         <v>10</v>
@@ -2333,15 +2329,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" hidden="1">
       <c r="A19" t="s">
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -2356,15 +2352,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" hidden="1">
       <c r="A20" t="s">
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -2379,15 +2375,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" hidden="1">
       <c r="A21" t="s">
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -2402,15 +2398,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" hidden="1">
       <c r="A22" t="s">
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
@@ -2425,15 +2421,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" hidden="1">
       <c r="A23" t="s">
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
@@ -2448,15 +2444,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" hidden="1">
       <c r="A24" t="s">
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -2471,15 +2467,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" hidden="1">
       <c r="A25" t="s">
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
@@ -2494,15 +2490,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" hidden="1">
       <c r="A26" t="s">
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -2517,15 +2513,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" hidden="1">
       <c r="A27" t="s">
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -2540,15 +2536,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" hidden="1">
       <c r="A28" t="s">
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -2563,15 +2559,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" hidden="1">
       <c r="A29" t="s">
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -2586,2994 +2582,2994 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" hidden="1">
       <c r="A30" t="s">
         <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" hidden="1">
       <c r="A31" t="s">
         <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" hidden="1">
       <c r="A32" t="s">
         <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G32" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" hidden="1">
       <c r="A33" t="s">
         <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" t="s">
         <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" hidden="1">
       <c r="A35" t="s">
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" t="s">
         <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" hidden="1">
       <c r="A37" t="s">
         <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G37" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" t="s">
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G38" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" hidden="1">
       <c r="A39" t="s">
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" t="s">
         <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G40" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1">
       <c r="A41" t="s">
         <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G41" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1">
       <c r="A42" t="s">
         <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G42" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" t="s">
         <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G43" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" t="s">
         <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G44" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" t="s">
         <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" hidden="1">
       <c r="A46" t="s">
         <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" t="s">
         <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1">
       <c r="A48" t="s">
         <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G48" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" hidden="1">
       <c r="A49" t="s">
         <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G49" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" hidden="1">
       <c r="A50" t="s">
         <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G50" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" hidden="1">
       <c r="A51" t="s">
         <v>13</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G51" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" hidden="1">
       <c r="A52" t="s">
         <v>13</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G52" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" hidden="1">
       <c r="A53" t="s">
         <v>13</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C53" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G53" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" hidden="1">
       <c r="A54" t="s">
         <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E54" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F54" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G54" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1">
       <c r="A55" t="s">
         <v>13</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B56" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E56" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F56" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G56" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B58" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E59" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F59" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G59" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C60" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E60" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F60" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G60" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C61" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D61" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E61" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F61" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G61" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C62" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E63" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F63" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G63" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C64" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D65" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E65" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F65" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G65" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E66" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F66" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G66" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C67" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D67" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E67" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F67" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G67" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D68" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E68" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F68" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G68" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C69" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E69" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F69" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G69" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B70" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C71" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D71" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E71" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F71" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G71" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B72" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C72" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D72" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E72" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F72" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G72" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B73" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C73" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B74" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C74" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C75" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D75" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E75" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F75" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G75" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C76" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D76" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E76" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F76" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G76" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B77" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C77" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D77" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E77" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F77" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G77" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B78" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D78" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E78" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F78" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G78" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B79" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C79" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B80" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C80" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G80" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B81" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C81" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D81" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E81" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F81" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G81" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1">
       <c r="A82" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B82" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" t="s">
+        <v>52</v>
+      </c>
+      <c r="D82" t="s">
+        <v>44</v>
+      </c>
+      <c r="E82" t="s">
+        <v>44</v>
+      </c>
+      <c r="F82" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" hidden="1">
+      <c r="A83" t="s">
+        <v>18</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" t="s">
+        <v>53</v>
+      </c>
+      <c r="D83" t="s">
+        <v>44</v>
+      </c>
+      <c r="E83" t="s">
+        <v>44</v>
+      </c>
+      <c r="F83" t="s">
+        <v>44</v>
+      </c>
+      <c r="G83" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" hidden="1">
+      <c r="A84" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" t="s">
+        <v>54</v>
+      </c>
+      <c r="D84" t="s">
+        <v>44</v>
+      </c>
+      <c r="E84" t="s">
+        <v>44</v>
+      </c>
+      <c r="F84" t="s">
+        <v>44</v>
+      </c>
+      <c r="G84" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1">
+      <c r="A85" t="s">
+        <v>18</v>
+      </c>
+      <c r="B85" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" t="s">
+        <v>55</v>
+      </c>
+      <c r="D85" t="s">
+        <v>44</v>
+      </c>
+      <c r="E85" t="s">
+        <v>44</v>
+      </c>
+      <c r="F85" t="s">
+        <v>44</v>
+      </c>
+      <c r="G85" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1">
+      <c r="A86" t="s">
+        <v>18</v>
+      </c>
+      <c r="B86" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" t="s">
+        <v>56</v>
+      </c>
+      <c r="D86" t="s">
+        <v>44</v>
+      </c>
+      <c r="E86" t="s">
+        <v>44</v>
+      </c>
+      <c r="F86" t="s">
+        <v>44</v>
+      </c>
+      <c r="G86" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1">
+      <c r="A87" t="s">
+        <v>18</v>
+      </c>
+      <c r="B87" t="s">
+        <v>31</v>
+      </c>
+      <c r="C87" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87" t="s">
+        <v>44</v>
+      </c>
+      <c r="E87" t="s">
+        <v>44</v>
+      </c>
+      <c r="F87" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" hidden="1">
+      <c r="A88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B88" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" t="s">
+        <v>58</v>
+      </c>
+      <c r="D88" t="s">
+        <v>44</v>
+      </c>
+      <c r="E88" t="s">
+        <v>44</v>
+      </c>
+      <c r="F88" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1">
+      <c r="A89" t="s">
+        <v>18</v>
+      </c>
+      <c r="B89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" t="s">
+        <v>44</v>
+      </c>
+      <c r="E89" t="s">
+        <v>44</v>
+      </c>
+      <c r="F89" t="s">
+        <v>44</v>
+      </c>
+      <c r="G89" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1">
+      <c r="A90" t="s">
+        <v>18</v>
+      </c>
+      <c r="B90" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" t="s">
+        <v>60</v>
+      </c>
+      <c r="D90" t="s">
+        <v>44</v>
+      </c>
+      <c r="E90" t="s">
+        <v>44</v>
+      </c>
+      <c r="F90" t="s">
+        <v>44</v>
+      </c>
+      <c r="G90" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1">
+      <c r="A91" t="s">
+        <v>18</v>
+      </c>
+      <c r="B91" t="s">
+        <v>32</v>
+      </c>
+      <c r="C91" t="s">
+        <v>61</v>
+      </c>
+      <c r="D91" t="s">
+        <v>44</v>
+      </c>
+      <c r="E91" t="s">
+        <v>44</v>
+      </c>
+      <c r="F91" t="s">
+        <v>44</v>
+      </c>
+      <c r="G91" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" hidden="1">
+      <c r="A92" t="s">
+        <v>18</v>
+      </c>
+      <c r="B92" t="s">
+        <v>32</v>
+      </c>
+      <c r="C92" t="s">
+        <v>62</v>
+      </c>
+      <c r="D92" t="s">
+        <v>44</v>
+      </c>
+      <c r="E92" t="s">
+        <v>44</v>
+      </c>
+      <c r="F92" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1">
+      <c r="A93" t="s">
+        <v>18</v>
+      </c>
+      <c r="B93" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" t="s">
+        <v>63</v>
+      </c>
+      <c r="D93" t="s">
+        <v>44</v>
+      </c>
+      <c r="E93" t="s">
+        <v>44</v>
+      </c>
+      <c r="F93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1">
+      <c r="A94" t="s">
+        <v>18</v>
+      </c>
+      <c r="B94" t="s">
+        <v>32</v>
+      </c>
+      <c r="C94" t="s">
+        <v>64</v>
+      </c>
+      <c r="D94" t="s">
+        <v>44</v>
+      </c>
+      <c r="E94" t="s">
+        <v>44</v>
+      </c>
+      <c r="F94" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" hidden="1">
+      <c r="A95" t="s">
+        <v>18</v>
+      </c>
+      <c r="B95" t="s">
+        <v>37</v>
+      </c>
+      <c r="C95" t="s">
+        <v>65</v>
+      </c>
+      <c r="D95" t="s">
+        <v>44</v>
+      </c>
+      <c r="E95" t="s">
+        <v>44</v>
+      </c>
+      <c r="F95" t="s">
+        <v>44</v>
+      </c>
+      <c r="G95" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" hidden="1">
+      <c r="A96" t="s">
+        <v>18</v>
+      </c>
+      <c r="B96" t="s">
+        <v>37</v>
+      </c>
+      <c r="C96" t="s">
+        <v>66</v>
+      </c>
+      <c r="D96" t="s">
+        <v>44</v>
+      </c>
+      <c r="E96" t="s">
+        <v>44</v>
+      </c>
+      <c r="F96" t="s">
+        <v>44</v>
+      </c>
+      <c r="G96" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1">
+      <c r="A97" t="s">
+        <v>18</v>
+      </c>
+      <c r="B97" t="s">
+        <v>37</v>
+      </c>
+      <c r="C97" t="s">
+        <v>67</v>
+      </c>
+      <c r="D97" t="s">
+        <v>44</v>
+      </c>
+      <c r="E97" t="s">
+        <v>44</v>
+      </c>
+      <c r="F97" t="s">
+        <v>44</v>
+      </c>
+      <c r="G97" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1">
+      <c r="A98" t="s">
+        <v>18</v>
+      </c>
+      <c r="B98" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" t="s">
+        <v>44</v>
+      </c>
+      <c r="E98" t="s">
+        <v>44</v>
+      </c>
+      <c r="F98" t="s">
+        <v>44</v>
+      </c>
+      <c r="G98" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1">
+      <c r="A99" t="s">
+        <v>18</v>
+      </c>
+      <c r="B99" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99" t="s">
+        <v>69</v>
+      </c>
+      <c r="D99" t="s">
+        <v>44</v>
+      </c>
+      <c r="E99" t="s">
+        <v>44</v>
+      </c>
+      <c r="F99" t="s">
+        <v>44</v>
+      </c>
+      <c r="G99" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1">
+      <c r="A100" t="s">
+        <v>18</v>
+      </c>
+      <c r="B100" t="s">
+        <v>37</v>
+      </c>
+      <c r="C100" t="s">
+        <v>70</v>
+      </c>
+      <c r="D100" t="s">
+        <v>44</v>
+      </c>
+      <c r="E100" t="s">
+        <v>44</v>
+      </c>
+      <c r="F100" t="s">
+        <v>44</v>
+      </c>
+      <c r="G100" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" hidden="1">
+      <c r="A101" t="s">
+        <v>18</v>
+      </c>
+      <c r="B101" t="s">
+        <v>37</v>
+      </c>
+      <c r="C101" t="s">
+        <v>71</v>
+      </c>
+      <c r="D101" t="s">
+        <v>44</v>
+      </c>
+      <c r="E101" t="s">
+        <v>44</v>
+      </c>
+      <c r="F101" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" hidden="1">
+      <c r="A102" t="s">
+        <v>18</v>
+      </c>
+      <c r="B102" t="s">
+        <v>37</v>
+      </c>
+      <c r="C102" t="s">
+        <v>72</v>
+      </c>
+      <c r="D102" t="s">
+        <v>44</v>
+      </c>
+      <c r="E102" t="s">
+        <v>44</v>
+      </c>
+      <c r="F102" t="s">
+        <v>44</v>
+      </c>
+      <c r="G102" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" hidden="1">
+      <c r="A103" t="s">
+        <v>18</v>
+      </c>
+      <c r="B103" t="s">
+        <v>37</v>
+      </c>
+      <c r="C103" t="s">
+        <v>73</v>
+      </c>
+      <c r="D103" t="s">
+        <v>44</v>
+      </c>
+      <c r="E103" t="s">
+        <v>44</v>
+      </c>
+      <c r="F103" t="s">
+        <v>44</v>
+      </c>
+      <c r="G103" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1">
+      <c r="A104" t="s">
+        <v>18</v>
+      </c>
+      <c r="B104" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" t="s">
+        <v>74</v>
+      </c>
+      <c r="D104" t="s">
+        <v>44</v>
+      </c>
+      <c r="E104" t="s">
+        <v>44</v>
+      </c>
+      <c r="F104" t="s">
+        <v>44</v>
+      </c>
+      <c r="G104" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" hidden="1">
+      <c r="A105" t="s">
+        <v>18</v>
+      </c>
+      <c r="B105" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" t="s">
+        <v>75</v>
+      </c>
+      <c r="D105" t="s">
+        <v>44</v>
+      </c>
+      <c r="E105" t="s">
+        <v>44</v>
+      </c>
+      <c r="F105" t="s">
+        <v>44</v>
+      </c>
+      <c r="G105" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" hidden="1">
+      <c r="A106" t="s">
+        <v>18</v>
+      </c>
+      <c r="B106" t="s">
         <v>33</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C106" t="s">
+        <v>76</v>
+      </c>
+      <c r="D106" t="s">
+        <v>44</v>
+      </c>
+      <c r="E106" t="s">
+        <v>44</v>
+      </c>
+      <c r="F106" t="s">
+        <v>44</v>
+      </c>
+      <c r="G106" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" hidden="1">
+      <c r="A107" t="s">
+        <v>18</v>
+      </c>
+      <c r="B107" t="s">
+        <v>33</v>
+      </c>
+      <c r="C107" t="s">
+        <v>77</v>
+      </c>
+      <c r="D107" t="s">
+        <v>44</v>
+      </c>
+      <c r="E107" t="s">
+        <v>44</v>
+      </c>
+      <c r="F107" t="s">
+        <v>44</v>
+      </c>
+      <c r="G107" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" hidden="1">
+      <c r="A108" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" t="s">
+        <v>52</v>
+      </c>
+      <c r="D108" t="s">
+        <v>44</v>
+      </c>
+      <c r="E108" t="s">
+        <v>44</v>
+      </c>
+      <c r="F108" t="s">
+        <v>44</v>
+      </c>
+      <c r="G108" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" hidden="1">
+      <c r="A109" t="s">
+        <v>22</v>
+      </c>
+      <c r="B109" t="s">
+        <v>31</v>
+      </c>
+      <c r="C109" t="s">
+        <v>53</v>
+      </c>
+      <c r="D109" t="s">
+        <v>44</v>
+      </c>
+      <c r="E109" t="s">
+        <v>44</v>
+      </c>
+      <c r="F109" t="s">
+        <v>44</v>
+      </c>
+      <c r="G109" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" hidden="1">
+      <c r="A110" t="s">
+        <v>22</v>
+      </c>
+      <c r="B110" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" t="s">
         <v>54</v>
       </c>
-      <c r="D82" t="s">
-        <v>46</v>
-      </c>
-      <c r="E82" t="s">
-        <v>46</v>
-      </c>
-      <c r="F82" t="s">
-        <v>46</v>
-      </c>
-      <c r="G82" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" t="s">
-        <v>20</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="D110" t="s">
+        <v>44</v>
+      </c>
+      <c r="E110" t="s">
+        <v>44</v>
+      </c>
+      <c r="F110" t="s">
+        <v>44</v>
+      </c>
+      <c r="G110" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" hidden="1">
+      <c r="A111" t="s">
+        <v>22</v>
+      </c>
+      <c r="B111" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" t="s">
+        <v>55</v>
+      </c>
+      <c r="D111" t="s">
+        <v>44</v>
+      </c>
+      <c r="E111" t="s">
+        <v>44</v>
+      </c>
+      <c r="F111" t="s">
+        <v>44</v>
+      </c>
+      <c r="G111" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" hidden="1">
+      <c r="A112" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" t="s">
+        <v>56</v>
+      </c>
+      <c r="D112" t="s">
+        <v>44</v>
+      </c>
+      <c r="E112" t="s">
+        <v>44</v>
+      </c>
+      <c r="F112" t="s">
+        <v>44</v>
+      </c>
+      <c r="G112" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" hidden="1">
+      <c r="A113" t="s">
+        <v>22</v>
+      </c>
+      <c r="B113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" t="s">
+        <v>57</v>
+      </c>
+      <c r="D113" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" t="s">
+        <v>44</v>
+      </c>
+      <c r="F113" t="s">
+        <v>44</v>
+      </c>
+      <c r="G113" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" hidden="1">
+      <c r="A114" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" t="s">
+        <v>58</v>
+      </c>
+      <c r="D114" t="s">
+        <v>44</v>
+      </c>
+      <c r="E114" t="s">
+        <v>44</v>
+      </c>
+      <c r="F114" t="s">
+        <v>44</v>
+      </c>
+      <c r="G114" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" hidden="1">
+      <c r="A115" t="s">
+        <v>22</v>
+      </c>
+      <c r="B115" t="s">
+        <v>32</v>
+      </c>
+      <c r="C115" t="s">
+        <v>59</v>
+      </c>
+      <c r="D115" t="s">
+        <v>44</v>
+      </c>
+      <c r="E115" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" t="s">
+        <v>44</v>
+      </c>
+      <c r="G115" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" hidden="1">
+      <c r="A116" t="s">
+        <v>22</v>
+      </c>
+      <c r="B116" t="s">
+        <v>32</v>
+      </c>
+      <c r="C116" t="s">
+        <v>60</v>
+      </c>
+      <c r="D116" t="s">
+        <v>44</v>
+      </c>
+      <c r="E116" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" t="s">
+        <v>44</v>
+      </c>
+      <c r="G116" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" hidden="1">
+      <c r="A117" t="s">
+        <v>22</v>
+      </c>
+      <c r="B117" t="s">
+        <v>32</v>
+      </c>
+      <c r="C117" t="s">
+        <v>61</v>
+      </c>
+      <c r="D117" t="s">
+        <v>44</v>
+      </c>
+      <c r="E117" t="s">
+        <v>44</v>
+      </c>
+      <c r="F117" t="s">
+        <v>44</v>
+      </c>
+      <c r="G117" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" hidden="1">
+      <c r="A118" t="s">
+        <v>22</v>
+      </c>
+      <c r="B118" t="s">
+        <v>32</v>
+      </c>
+      <c r="C118" t="s">
+        <v>62</v>
+      </c>
+      <c r="D118" t="s">
+        <v>44</v>
+      </c>
+      <c r="E118" t="s">
+        <v>44</v>
+      </c>
+      <c r="F118" t="s">
+        <v>44</v>
+      </c>
+      <c r="G118" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" hidden="1">
+      <c r="A119" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119" t="s">
+        <v>32</v>
+      </c>
+      <c r="C119" t="s">
+        <v>63</v>
+      </c>
+      <c r="D119" t="s">
+        <v>44</v>
+      </c>
+      <c r="E119" t="s">
+        <v>44</v>
+      </c>
+      <c r="F119" t="s">
+        <v>44</v>
+      </c>
+      <c r="G119" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" hidden="1">
+      <c r="A120" t="s">
+        <v>22</v>
+      </c>
+      <c r="B120" t="s">
+        <v>32</v>
+      </c>
+      <c r="C120" t="s">
+        <v>64</v>
+      </c>
+      <c r="D120" t="s">
+        <v>44</v>
+      </c>
+      <c r="E120" t="s">
+        <v>44</v>
+      </c>
+      <c r="F120" t="s">
+        <v>44</v>
+      </c>
+      <c r="G120" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" hidden="1">
+      <c r="A121" t="s">
+        <v>22</v>
+      </c>
+      <c r="B121" t="s">
+        <v>37</v>
+      </c>
+      <c r="C121" t="s">
+        <v>65</v>
+      </c>
+      <c r="D121" t="s">
+        <v>44</v>
+      </c>
+      <c r="E121" t="s">
+        <v>44</v>
+      </c>
+      <c r="F121" t="s">
+        <v>44</v>
+      </c>
+      <c r="G121" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" hidden="1">
+      <c r="A122" t="s">
+        <v>22</v>
+      </c>
+      <c r="B122" t="s">
+        <v>37</v>
+      </c>
+      <c r="C122" t="s">
+        <v>66</v>
+      </c>
+      <c r="D122" t="s">
+        <v>44</v>
+      </c>
+      <c r="E122" t="s">
+        <v>44</v>
+      </c>
+      <c r="F122" t="s">
+        <v>44</v>
+      </c>
+      <c r="G122" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" hidden="1">
+      <c r="A123" t="s">
+        <v>22</v>
+      </c>
+      <c r="B123" t="s">
+        <v>37</v>
+      </c>
+      <c r="C123" t="s">
+        <v>67</v>
+      </c>
+      <c r="D123" t="s">
+        <v>44</v>
+      </c>
+      <c r="E123" t="s">
+        <v>44</v>
+      </c>
+      <c r="F123" t="s">
+        <v>44</v>
+      </c>
+      <c r="G123" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" hidden="1">
+      <c r="A124" t="s">
+        <v>22</v>
+      </c>
+      <c r="B124" t="s">
+        <v>37</v>
+      </c>
+      <c r="C124" t="s">
+        <v>68</v>
+      </c>
+      <c r="D124" t="s">
+        <v>44</v>
+      </c>
+      <c r="E124" t="s">
+        <v>44</v>
+      </c>
+      <c r="F124" t="s">
+        <v>44</v>
+      </c>
+      <c r="G124" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" hidden="1">
+      <c r="A125" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125" t="s">
+        <v>37</v>
+      </c>
+      <c r="C125" t="s">
+        <v>69</v>
+      </c>
+      <c r="D125" t="s">
+        <v>44</v>
+      </c>
+      <c r="E125" t="s">
+        <v>44</v>
+      </c>
+      <c r="F125" t="s">
+        <v>44</v>
+      </c>
+      <c r="G125" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" hidden="1">
+      <c r="A126" t="s">
+        <v>22</v>
+      </c>
+      <c r="B126" t="s">
+        <v>37</v>
+      </c>
+      <c r="C126" t="s">
+        <v>70</v>
+      </c>
+      <c r="D126" t="s">
+        <v>44</v>
+      </c>
+      <c r="E126" t="s">
+        <v>44</v>
+      </c>
+      <c r="F126" t="s">
+        <v>44</v>
+      </c>
+      <c r="G126" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1">
+      <c r="A127" t="s">
+        <v>22</v>
+      </c>
+      <c r="B127" t="s">
+        <v>37</v>
+      </c>
+      <c r="C127" t="s">
+        <v>71</v>
+      </c>
+      <c r="D127" t="s">
+        <v>44</v>
+      </c>
+      <c r="E127" t="s">
+        <v>44</v>
+      </c>
+      <c r="F127" t="s">
+        <v>44</v>
+      </c>
+      <c r="G127" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1">
+      <c r="A128" t="s">
+        <v>22</v>
+      </c>
+      <c r="B128" t="s">
+        <v>37</v>
+      </c>
+      <c r="C128" t="s">
+        <v>72</v>
+      </c>
+      <c r="D128" t="s">
+        <v>44</v>
+      </c>
+      <c r="E128" t="s">
+        <v>44</v>
+      </c>
+      <c r="F128" t="s">
+        <v>44</v>
+      </c>
+      <c r="G128" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" hidden="1">
+      <c r="A129" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129" t="s">
+        <v>37</v>
+      </c>
+      <c r="C129" t="s">
+        <v>73</v>
+      </c>
+      <c r="D129" t="s">
+        <v>44</v>
+      </c>
+      <c r="E129" t="s">
+        <v>44</v>
+      </c>
+      <c r="F129" t="s">
+        <v>44</v>
+      </c>
+      <c r="G129" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" hidden="1">
+      <c r="A130" t="s">
+        <v>22</v>
+      </c>
+      <c r="B130" t="s">
+        <v>37</v>
+      </c>
+      <c r="C130" t="s">
+        <v>74</v>
+      </c>
+      <c r="D130" t="s">
+        <v>44</v>
+      </c>
+      <c r="E130" t="s">
+        <v>44</v>
+      </c>
+      <c r="F130" t="s">
+        <v>44</v>
+      </c>
+      <c r="G130" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" hidden="1">
+      <c r="A131" t="s">
+        <v>22</v>
+      </c>
+      <c r="B131" t="s">
+        <v>37</v>
+      </c>
+      <c r="C131" t="s">
+        <v>75</v>
+      </c>
+      <c r="D131" t="s">
+        <v>44</v>
+      </c>
+      <c r="E131" t="s">
+        <v>44</v>
+      </c>
+      <c r="F131" t="s">
+        <v>44</v>
+      </c>
+      <c r="G131" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" hidden="1">
+      <c r="A132" t="s">
+        <v>22</v>
+      </c>
+      <c r="B132" t="s">
         <v>33</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C132" t="s">
+        <v>76</v>
+      </c>
+      <c r="D132" t="s">
+        <v>44</v>
+      </c>
+      <c r="E132" t="s">
+        <v>44</v>
+      </c>
+      <c r="F132" t="s">
+        <v>44</v>
+      </c>
+      <c r="G132" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" hidden="1">
+      <c r="A133" t="s">
+        <v>22</v>
+      </c>
+      <c r="B133" t="s">
+        <v>33</v>
+      </c>
+      <c r="C133" t="s">
+        <v>77</v>
+      </c>
+      <c r="D133" t="s">
+        <v>44</v>
+      </c>
+      <c r="E133" t="s">
+        <v>44</v>
+      </c>
+      <c r="F133" t="s">
+        <v>44</v>
+      </c>
+      <c r="G133" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" hidden="1">
+      <c r="A134" t="s">
+        <v>26</v>
+      </c>
+      <c r="B134" t="s">
+        <v>31</v>
+      </c>
+      <c r="C134" t="s">
+        <v>52</v>
+      </c>
+      <c r="D134" t="s">
+        <v>44</v>
+      </c>
+      <c r="E134" t="s">
+        <v>44</v>
+      </c>
+      <c r="F134" t="s">
+        <v>44</v>
+      </c>
+      <c r="G134" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" hidden="1">
+      <c r="A135" t="s">
+        <v>26</v>
+      </c>
+      <c r="B135" t="s">
+        <v>31</v>
+      </c>
+      <c r="C135" t="s">
+        <v>53</v>
+      </c>
+      <c r="D135" t="s">
+        <v>44</v>
+      </c>
+      <c r="E135" t="s">
+        <v>44</v>
+      </c>
+      <c r="F135" t="s">
+        <v>44</v>
+      </c>
+      <c r="G135" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" hidden="1">
+      <c r="A136" t="s">
+        <v>26</v>
+      </c>
+      <c r="B136" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" t="s">
+        <v>54</v>
+      </c>
+      <c r="D136" t="s">
+        <v>44</v>
+      </c>
+      <c r="E136" t="s">
+        <v>44</v>
+      </c>
+      <c r="F136" t="s">
+        <v>44</v>
+      </c>
+      <c r="G136" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" hidden="1">
+      <c r="A137" t="s">
+        <v>26</v>
+      </c>
+      <c r="B137" t="s">
+        <v>31</v>
+      </c>
+      <c r="C137" t="s">
         <v>55</v>
       </c>
-      <c r="D83" t="s">
-        <v>46</v>
-      </c>
-      <c r="E83" t="s">
-        <v>46</v>
-      </c>
-      <c r="F83" t="s">
-        <v>46</v>
-      </c>
-      <c r="G83" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" t="s">
-        <v>20</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="D137" t="s">
+        <v>44</v>
+      </c>
+      <c r="E137" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" t="s">
+        <v>44</v>
+      </c>
+      <c r="G137" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" hidden="1">
+      <c r="A138" t="s">
+        <v>26</v>
+      </c>
+      <c r="B138" t="s">
+        <v>31</v>
+      </c>
+      <c r="C138" t="s">
+        <v>56</v>
+      </c>
+      <c r="D138" t="s">
+        <v>44</v>
+      </c>
+      <c r="E138" t="s">
+        <v>44</v>
+      </c>
+      <c r="F138" t="s">
+        <v>44</v>
+      </c>
+      <c r="G138" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1">
+      <c r="A139" t="s">
+        <v>26</v>
+      </c>
+      <c r="B139" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" t="s">
+        <v>57</v>
+      </c>
+      <c r="D139" t="s">
+        <v>44</v>
+      </c>
+      <c r="E139" t="s">
+        <v>44</v>
+      </c>
+      <c r="F139" t="s">
+        <v>44</v>
+      </c>
+      <c r="G139" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" hidden="1">
+      <c r="A140" t="s">
+        <v>26</v>
+      </c>
+      <c r="B140" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" t="s">
+        <v>58</v>
+      </c>
+      <c r="D140" t="s">
+        <v>44</v>
+      </c>
+      <c r="E140" t="s">
+        <v>44</v>
+      </c>
+      <c r="F140" t="s">
+        <v>44</v>
+      </c>
+      <c r="G140" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" hidden="1">
+      <c r="A141" t="s">
+        <v>26</v>
+      </c>
+      <c r="B141" t="s">
+        <v>32</v>
+      </c>
+      <c r="C141" t="s">
+        <v>59</v>
+      </c>
+      <c r="D141" t="s">
+        <v>44</v>
+      </c>
+      <c r="E141" t="s">
+        <v>44</v>
+      </c>
+      <c r="F141" t="s">
+        <v>44</v>
+      </c>
+      <c r="G141" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" hidden="1">
+      <c r="A142" t="s">
+        <v>26</v>
+      </c>
+      <c r="B142" t="s">
+        <v>32</v>
+      </c>
+      <c r="C142" t="s">
+        <v>60</v>
+      </c>
+      <c r="D142" t="s">
+        <v>44</v>
+      </c>
+      <c r="E142" t="s">
+        <v>44</v>
+      </c>
+      <c r="F142" t="s">
+        <v>44</v>
+      </c>
+      <c r="G142" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" hidden="1">
+      <c r="A143" t="s">
+        <v>26</v>
+      </c>
+      <c r="B143" t="s">
+        <v>32</v>
+      </c>
+      <c r="C143" t="s">
+        <v>61</v>
+      </c>
+      <c r="D143" t="s">
+        <v>44</v>
+      </c>
+      <c r="E143" t="s">
+        <v>44</v>
+      </c>
+      <c r="F143" t="s">
+        <v>44</v>
+      </c>
+      <c r="G143" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" hidden="1">
+      <c r="A144" t="s">
+        <v>26</v>
+      </c>
+      <c r="B144" t="s">
+        <v>32</v>
+      </c>
+      <c r="C144" t="s">
+        <v>62</v>
+      </c>
+      <c r="D144" t="s">
+        <v>44</v>
+      </c>
+      <c r="E144" t="s">
+        <v>44</v>
+      </c>
+      <c r="F144" t="s">
+        <v>44</v>
+      </c>
+      <c r="G144" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" hidden="1">
+      <c r="A145" t="s">
+        <v>26</v>
+      </c>
+      <c r="B145" t="s">
+        <v>32</v>
+      </c>
+      <c r="C145" t="s">
+        <v>63</v>
+      </c>
+      <c r="D145" t="s">
+        <v>44</v>
+      </c>
+      <c r="E145" t="s">
+        <v>44</v>
+      </c>
+      <c r="F145" t="s">
+        <v>44</v>
+      </c>
+      <c r="G145" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" hidden="1">
+      <c r="A146" t="s">
+        <v>26</v>
+      </c>
+      <c r="B146" t="s">
+        <v>32</v>
+      </c>
+      <c r="C146" t="s">
+        <v>64</v>
+      </c>
+      <c r="D146" t="s">
+        <v>44</v>
+      </c>
+      <c r="E146" t="s">
+        <v>44</v>
+      </c>
+      <c r="F146" t="s">
+        <v>44</v>
+      </c>
+      <c r="G146" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" hidden="1">
+      <c r="A147" t="s">
+        <v>26</v>
+      </c>
+      <c r="B147" t="s">
+        <v>37</v>
+      </c>
+      <c r="C147" t="s">
+        <v>65</v>
+      </c>
+      <c r="D147" t="s">
+        <v>44</v>
+      </c>
+      <c r="E147" t="s">
+        <v>44</v>
+      </c>
+      <c r="F147" t="s">
+        <v>44</v>
+      </c>
+      <c r="G147" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1">
+      <c r="A148" t="s">
+        <v>26</v>
+      </c>
+      <c r="B148" t="s">
+        <v>37</v>
+      </c>
+      <c r="C148" t="s">
+        <v>66</v>
+      </c>
+      <c r="D148" t="s">
+        <v>44</v>
+      </c>
+      <c r="E148" t="s">
+        <v>44</v>
+      </c>
+      <c r="F148" t="s">
+        <v>44</v>
+      </c>
+      <c r="G148" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" hidden="1">
+      <c r="A149" t="s">
+        <v>26</v>
+      </c>
+      <c r="B149" t="s">
+        <v>37</v>
+      </c>
+      <c r="C149" t="s">
+        <v>67</v>
+      </c>
+      <c r="D149" t="s">
+        <v>44</v>
+      </c>
+      <c r="E149" t="s">
+        <v>44</v>
+      </c>
+      <c r="F149" t="s">
+        <v>44</v>
+      </c>
+      <c r="G149" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" hidden="1">
+      <c r="A150" t="s">
+        <v>26</v>
+      </c>
+      <c r="B150" t="s">
+        <v>37</v>
+      </c>
+      <c r="C150" t="s">
+        <v>68</v>
+      </c>
+      <c r="D150" t="s">
+        <v>44</v>
+      </c>
+      <c r="E150" t="s">
+        <v>44</v>
+      </c>
+      <c r="F150" t="s">
+        <v>44</v>
+      </c>
+      <c r="G150" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" hidden="1">
+      <c r="A151" t="s">
+        <v>26</v>
+      </c>
+      <c r="B151" t="s">
+        <v>37</v>
+      </c>
+      <c r="C151" t="s">
+        <v>69</v>
+      </c>
+      <c r="D151" t="s">
+        <v>44</v>
+      </c>
+      <c r="E151" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" t="s">
+        <v>44</v>
+      </c>
+      <c r="G151" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" hidden="1">
+      <c r="A152" t="s">
+        <v>26</v>
+      </c>
+      <c r="B152" t="s">
+        <v>37</v>
+      </c>
+      <c r="C152" t="s">
+        <v>70</v>
+      </c>
+      <c r="D152" t="s">
+        <v>44</v>
+      </c>
+      <c r="E152" t="s">
+        <v>44</v>
+      </c>
+      <c r="F152" t="s">
+        <v>44</v>
+      </c>
+      <c r="G152" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" hidden="1">
+      <c r="A153" t="s">
+        <v>26</v>
+      </c>
+      <c r="B153" t="s">
+        <v>37</v>
+      </c>
+      <c r="C153" t="s">
+        <v>71</v>
+      </c>
+      <c r="D153" t="s">
+        <v>44</v>
+      </c>
+      <c r="E153" t="s">
+        <v>44</v>
+      </c>
+      <c r="F153" t="s">
+        <v>44</v>
+      </c>
+      <c r="G153" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" hidden="1">
+      <c r="A154" t="s">
+        <v>26</v>
+      </c>
+      <c r="B154" t="s">
+        <v>37</v>
+      </c>
+      <c r="C154" t="s">
+        <v>72</v>
+      </c>
+      <c r="D154" t="s">
+        <v>44</v>
+      </c>
+      <c r="E154" t="s">
+        <v>44</v>
+      </c>
+      <c r="F154" t="s">
+        <v>44</v>
+      </c>
+      <c r="G154" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" hidden="1">
+      <c r="A155" t="s">
+        <v>26</v>
+      </c>
+      <c r="B155" t="s">
+        <v>37</v>
+      </c>
+      <c r="C155" t="s">
+        <v>73</v>
+      </c>
+      <c r="D155" t="s">
+        <v>44</v>
+      </c>
+      <c r="E155" t="s">
+        <v>44</v>
+      </c>
+      <c r="F155" t="s">
+        <v>44</v>
+      </c>
+      <c r="G155" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" hidden="1">
+      <c r="A156" t="s">
+        <v>26</v>
+      </c>
+      <c r="B156" t="s">
+        <v>37</v>
+      </c>
+      <c r="C156" t="s">
+        <v>74</v>
+      </c>
+      <c r="D156" t="s">
+        <v>44</v>
+      </c>
+      <c r="E156" t="s">
+        <v>44</v>
+      </c>
+      <c r="F156" t="s">
+        <v>44</v>
+      </c>
+      <c r="G156" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" hidden="1">
+      <c r="A157" t="s">
+        <v>26</v>
+      </c>
+      <c r="B157" t="s">
+        <v>37</v>
+      </c>
+      <c r="C157" t="s">
+        <v>75</v>
+      </c>
+      <c r="D157" t="s">
+        <v>44</v>
+      </c>
+      <c r="E157" t="s">
+        <v>44</v>
+      </c>
+      <c r="F157" t="s">
+        <v>44</v>
+      </c>
+      <c r="G157" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" hidden="1">
+      <c r="A158" t="s">
+        <v>26</v>
+      </c>
+      <c r="B158" t="s">
         <v>33</v>
       </c>
-      <c r="C84" t="s">
-        <v>56</v>
-      </c>
-      <c r="D84" t="s">
-        <v>46</v>
-      </c>
-      <c r="E84" t="s">
-        <v>46</v>
-      </c>
-      <c r="F84" t="s">
-        <v>46</v>
-      </c>
-      <c r="G84" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" t="s">
-        <v>20</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="C158" t="s">
+        <v>76</v>
+      </c>
+      <c r="D158" t="s">
+        <v>44</v>
+      </c>
+      <c r="E158" t="s">
+        <v>44</v>
+      </c>
+      <c r="F158" t="s">
+        <v>44</v>
+      </c>
+      <c r="G158" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" hidden="1">
+      <c r="A159" t="s">
+        <v>26</v>
+      </c>
+      <c r="B159" t="s">
         <v>33</v>
       </c>
-      <c r="C85" t="s">
-        <v>57</v>
-      </c>
-      <c r="D85" t="s">
-        <v>46</v>
-      </c>
-      <c r="E85" t="s">
-        <v>46</v>
-      </c>
-      <c r="F85" t="s">
-        <v>46</v>
-      </c>
-      <c r="G85" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" t="s">
-        <v>20</v>
-      </c>
-      <c r="B86" t="s">
-        <v>33</v>
-      </c>
-      <c r="C86" t="s">
-        <v>58</v>
-      </c>
-      <c r="D86" t="s">
-        <v>46</v>
-      </c>
-      <c r="E86" t="s">
-        <v>46</v>
-      </c>
-      <c r="F86" t="s">
-        <v>46</v>
-      </c>
-      <c r="G86" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" t="s">
-        <v>20</v>
-      </c>
-      <c r="B87" t="s">
-        <v>33</v>
-      </c>
-      <c r="C87" t="s">
-        <v>59</v>
-      </c>
-      <c r="D87" t="s">
-        <v>46</v>
-      </c>
-      <c r="E87" t="s">
-        <v>46</v>
-      </c>
-      <c r="F87" t="s">
-        <v>46</v>
-      </c>
-      <c r="G87" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" t="s">
-        <v>20</v>
-      </c>
-      <c r="B88" t="s">
-        <v>33</v>
-      </c>
-      <c r="C88" t="s">
-        <v>60</v>
-      </c>
-      <c r="D88" t="s">
-        <v>46</v>
-      </c>
-      <c r="E88" t="s">
-        <v>46</v>
-      </c>
-      <c r="F88" t="s">
-        <v>46</v>
-      </c>
-      <c r="G88" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89" t="s">
-        <v>20</v>
-      </c>
-      <c r="B89" t="s">
-        <v>34</v>
-      </c>
-      <c r="C89" t="s">
-        <v>61</v>
-      </c>
-      <c r="D89" t="s">
-        <v>46</v>
-      </c>
-      <c r="E89" t="s">
-        <v>46</v>
-      </c>
-      <c r="F89" t="s">
-        <v>46</v>
-      </c>
-      <c r="G89" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
-      <c r="A90" t="s">
-        <v>20</v>
-      </c>
-      <c r="B90" t="s">
-        <v>34</v>
-      </c>
-      <c r="C90" t="s">
-        <v>62</v>
-      </c>
-      <c r="D90" t="s">
-        <v>46</v>
-      </c>
-      <c r="E90" t="s">
-        <v>46</v>
-      </c>
-      <c r="F90" t="s">
-        <v>46</v>
-      </c>
-      <c r="G90" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
-      <c r="A91" t="s">
-        <v>20</v>
-      </c>
-      <c r="B91" t="s">
-        <v>34</v>
-      </c>
-      <c r="C91" t="s">
-        <v>63</v>
-      </c>
-      <c r="D91" t="s">
-        <v>46</v>
-      </c>
-      <c r="E91" t="s">
-        <v>46</v>
-      </c>
-      <c r="F91" t="s">
-        <v>46</v>
-      </c>
-      <c r="G91" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
-      <c r="A92" t="s">
-        <v>20</v>
-      </c>
-      <c r="B92" t="s">
-        <v>34</v>
-      </c>
-      <c r="C92" t="s">
-        <v>64</v>
-      </c>
-      <c r="D92" t="s">
-        <v>46</v>
-      </c>
-      <c r="E92" t="s">
-        <v>46</v>
-      </c>
-      <c r="F92" t="s">
-        <v>46</v>
-      </c>
-      <c r="G92" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" t="s">
-        <v>20</v>
-      </c>
-      <c r="B93" t="s">
-        <v>34</v>
-      </c>
-      <c r="C93" t="s">
-        <v>65</v>
-      </c>
-      <c r="D93" t="s">
-        <v>46</v>
-      </c>
-      <c r="E93" t="s">
-        <v>46</v>
-      </c>
-      <c r="F93" t="s">
-        <v>46</v>
-      </c>
-      <c r="G93" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" t="s">
-        <v>20</v>
-      </c>
-      <c r="B94" t="s">
-        <v>34</v>
-      </c>
-      <c r="C94" t="s">
-        <v>66</v>
-      </c>
-      <c r="D94" t="s">
-        <v>46</v>
-      </c>
-      <c r="E94" t="s">
-        <v>46</v>
-      </c>
-      <c r="F94" t="s">
-        <v>46</v>
-      </c>
-      <c r="G94" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" t="s">
-        <v>20</v>
-      </c>
-      <c r="B95" t="s">
-        <v>39</v>
-      </c>
-      <c r="C95" t="s">
-        <v>67</v>
-      </c>
-      <c r="D95" t="s">
-        <v>46</v>
-      </c>
-      <c r="E95" t="s">
-        <v>46</v>
-      </c>
-      <c r="F95" t="s">
-        <v>46</v>
-      </c>
-      <c r="G95" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" t="s">
-        <v>20</v>
-      </c>
-      <c r="B96" t="s">
-        <v>39</v>
-      </c>
-      <c r="C96" t="s">
-        <v>68</v>
-      </c>
-      <c r="D96" t="s">
-        <v>46</v>
-      </c>
-      <c r="E96" t="s">
-        <v>46</v>
-      </c>
-      <c r="F96" t="s">
-        <v>46</v>
-      </c>
-      <c r="G96" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" t="s">
-        <v>20</v>
-      </c>
-      <c r="B97" t="s">
-        <v>39</v>
-      </c>
-      <c r="C97" t="s">
-        <v>69</v>
-      </c>
-      <c r="D97" t="s">
-        <v>46</v>
-      </c>
-      <c r="E97" t="s">
-        <v>46</v>
-      </c>
-      <c r="F97" t="s">
-        <v>46</v>
-      </c>
-      <c r="G97" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" t="s">
-        <v>20</v>
-      </c>
-      <c r="B98" t="s">
-        <v>39</v>
-      </c>
-      <c r="C98" t="s">
-        <v>70</v>
-      </c>
-      <c r="D98" t="s">
-        <v>46</v>
-      </c>
-      <c r="E98" t="s">
-        <v>46</v>
-      </c>
-      <c r="F98" t="s">
-        <v>46</v>
-      </c>
-      <c r="G98" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" t="s">
-        <v>20</v>
-      </c>
-      <c r="B99" t="s">
-        <v>39</v>
-      </c>
-      <c r="C99" t="s">
-        <v>71</v>
-      </c>
-      <c r="D99" t="s">
-        <v>46</v>
-      </c>
-      <c r="E99" t="s">
-        <v>46</v>
-      </c>
-      <c r="F99" t="s">
-        <v>46</v>
-      </c>
-      <c r="G99" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" t="s">
-        <v>20</v>
-      </c>
-      <c r="B100" t="s">
-        <v>39</v>
-      </c>
-      <c r="C100" t="s">
-        <v>72</v>
-      </c>
-      <c r="D100" t="s">
-        <v>46</v>
-      </c>
-      <c r="E100" t="s">
-        <v>46</v>
-      </c>
-      <c r="F100" t="s">
-        <v>46</v>
-      </c>
-      <c r="G100" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" t="s">
-        <v>20</v>
-      </c>
-      <c r="B101" t="s">
-        <v>39</v>
-      </c>
-      <c r="C101" t="s">
-        <v>73</v>
-      </c>
-      <c r="D101" t="s">
-        <v>46</v>
-      </c>
-      <c r="E101" t="s">
-        <v>46</v>
-      </c>
-      <c r="F101" t="s">
-        <v>46</v>
-      </c>
-      <c r="G101" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" t="s">
-        <v>20</v>
-      </c>
-      <c r="B102" t="s">
-        <v>39</v>
-      </c>
-      <c r="C102" t="s">
-        <v>74</v>
-      </c>
-      <c r="D102" t="s">
-        <v>46</v>
-      </c>
-      <c r="E102" t="s">
-        <v>46</v>
-      </c>
-      <c r="F102" t="s">
-        <v>46</v>
-      </c>
-      <c r="G102" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" t="s">
-        <v>20</v>
-      </c>
-      <c r="B103" t="s">
-        <v>39</v>
-      </c>
-      <c r="C103" t="s">
-        <v>75</v>
-      </c>
-      <c r="D103" t="s">
-        <v>46</v>
-      </c>
-      <c r="E103" t="s">
-        <v>46</v>
-      </c>
-      <c r="F103" t="s">
-        <v>46</v>
-      </c>
-      <c r="G103" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" t="s">
-        <v>20</v>
-      </c>
-      <c r="B104" t="s">
-        <v>39</v>
-      </c>
-      <c r="C104" t="s">
-        <v>76</v>
-      </c>
-      <c r="D104" t="s">
-        <v>46</v>
-      </c>
-      <c r="E104" t="s">
-        <v>46</v>
-      </c>
-      <c r="F104" t="s">
-        <v>46</v>
-      </c>
-      <c r="G104" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" t="s">
-        <v>20</v>
-      </c>
-      <c r="B105" t="s">
-        <v>39</v>
-      </c>
-      <c r="C105" t="s">
+      <c r="C159" t="s">
         <v>77</v>
       </c>
-      <c r="D105" t="s">
-        <v>46</v>
-      </c>
-      <c r="E105" t="s">
-        <v>46</v>
-      </c>
-      <c r="F105" t="s">
-        <v>46</v>
-      </c>
-      <c r="G105" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106" t="s">
-        <v>20</v>
-      </c>
-      <c r="B106" t="s">
-        <v>35</v>
-      </c>
-      <c r="C106" t="s">
-        <v>78</v>
-      </c>
-      <c r="D106" t="s">
-        <v>46</v>
-      </c>
-      <c r="E106" t="s">
-        <v>46</v>
-      </c>
-      <c r="F106" t="s">
-        <v>46</v>
-      </c>
-      <c r="G106" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107" t="s">
-        <v>20</v>
-      </c>
-      <c r="B107" t="s">
-        <v>35</v>
-      </c>
-      <c r="C107" t="s">
-        <v>79</v>
-      </c>
-      <c r="D107" t="s">
-        <v>46</v>
-      </c>
-      <c r="E107" t="s">
-        <v>46</v>
-      </c>
-      <c r="F107" t="s">
-        <v>46</v>
-      </c>
-      <c r="G107" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108" t="s">
-        <v>24</v>
-      </c>
-      <c r="B108" t="s">
-        <v>33</v>
-      </c>
-      <c r="C108" t="s">
-        <v>54</v>
-      </c>
-      <c r="D108" t="s">
-        <v>46</v>
-      </c>
-      <c r="E108" t="s">
-        <v>46</v>
-      </c>
-      <c r="F108" t="s">
-        <v>46</v>
-      </c>
-      <c r="G108" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" t="s">
-        <v>24</v>
-      </c>
-      <c r="B109" t="s">
-        <v>33</v>
-      </c>
-      <c r="C109" t="s">
-        <v>55</v>
-      </c>
-      <c r="D109" t="s">
-        <v>46</v>
-      </c>
-      <c r="E109" t="s">
-        <v>46</v>
-      </c>
-      <c r="F109" t="s">
-        <v>46</v>
-      </c>
-      <c r="G109" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" t="s">
-        <v>24</v>
-      </c>
-      <c r="B110" t="s">
-        <v>33</v>
-      </c>
-      <c r="C110" t="s">
-        <v>56</v>
-      </c>
-      <c r="D110" t="s">
-        <v>46</v>
-      </c>
-      <c r="E110" t="s">
-        <v>46</v>
-      </c>
-      <c r="F110" t="s">
-        <v>46</v>
-      </c>
-      <c r="G110" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" t="s">
-        <v>24</v>
-      </c>
-      <c r="B111" t="s">
-        <v>33</v>
-      </c>
-      <c r="C111" t="s">
-        <v>57</v>
-      </c>
-      <c r="D111" t="s">
-        <v>46</v>
-      </c>
-      <c r="E111" t="s">
-        <v>46</v>
-      </c>
-      <c r="F111" t="s">
-        <v>46</v>
-      </c>
-      <c r="G111" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
-      <c r="A112" t="s">
-        <v>24</v>
-      </c>
-      <c r="B112" t="s">
-        <v>33</v>
-      </c>
-      <c r="C112" t="s">
-        <v>58</v>
-      </c>
-      <c r="D112" t="s">
-        <v>46</v>
-      </c>
-      <c r="E112" t="s">
-        <v>46</v>
-      </c>
-      <c r="F112" t="s">
-        <v>46</v>
-      </c>
-      <c r="G112" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" t="s">
-        <v>24</v>
-      </c>
-      <c r="B113" t="s">
-        <v>33</v>
-      </c>
-      <c r="C113" t="s">
-        <v>59</v>
-      </c>
-      <c r="D113" t="s">
-        <v>46</v>
-      </c>
-      <c r="E113" t="s">
-        <v>46</v>
-      </c>
-      <c r="F113" t="s">
-        <v>46</v>
-      </c>
-      <c r="G113" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" t="s">
-        <v>24</v>
-      </c>
-      <c r="B114" t="s">
-        <v>33</v>
-      </c>
-      <c r="C114" t="s">
-        <v>60</v>
-      </c>
-      <c r="D114" t="s">
-        <v>46</v>
-      </c>
-      <c r="E114" t="s">
-        <v>46</v>
-      </c>
-      <c r="F114" t="s">
-        <v>46</v>
-      </c>
-      <c r="G114" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" t="s">
-        <v>24</v>
-      </c>
-      <c r="B115" t="s">
-        <v>34</v>
-      </c>
-      <c r="C115" t="s">
-        <v>61</v>
-      </c>
-      <c r="D115" t="s">
-        <v>46</v>
-      </c>
-      <c r="E115" t="s">
-        <v>46</v>
-      </c>
-      <c r="F115" t="s">
-        <v>46</v>
-      </c>
-      <c r="G115" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" t="s">
-        <v>24</v>
-      </c>
-      <c r="B116" t="s">
-        <v>34</v>
-      </c>
-      <c r="C116" t="s">
-        <v>62</v>
-      </c>
-      <c r="D116" t="s">
-        <v>46</v>
-      </c>
-      <c r="E116" t="s">
-        <v>46</v>
-      </c>
-      <c r="F116" t="s">
-        <v>46</v>
-      </c>
-      <c r="G116" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
-      <c r="A117" t="s">
-        <v>24</v>
-      </c>
-      <c r="B117" t="s">
-        <v>34</v>
-      </c>
-      <c r="C117" t="s">
-        <v>63</v>
-      </c>
-      <c r="D117" t="s">
-        <v>46</v>
-      </c>
-      <c r="E117" t="s">
-        <v>46</v>
-      </c>
-      <c r="F117" t="s">
-        <v>46</v>
-      </c>
-      <c r="G117" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
-      <c r="A118" t="s">
-        <v>24</v>
-      </c>
-      <c r="B118" t="s">
-        <v>34</v>
-      </c>
-      <c r="C118" t="s">
-        <v>64</v>
-      </c>
-      <c r="D118" t="s">
-        <v>46</v>
-      </c>
-      <c r="E118" t="s">
-        <v>46</v>
-      </c>
-      <c r="F118" t="s">
-        <v>46</v>
-      </c>
-      <c r="G118" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
-      <c r="A119" t="s">
-        <v>24</v>
-      </c>
-      <c r="B119" t="s">
-        <v>34</v>
-      </c>
-      <c r="C119" t="s">
-        <v>65</v>
-      </c>
-      <c r="D119" t="s">
-        <v>46</v>
-      </c>
-      <c r="E119" t="s">
-        <v>46</v>
-      </c>
-      <c r="F119" t="s">
-        <v>46</v>
-      </c>
-      <c r="G119" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
-      <c r="A120" t="s">
-        <v>24</v>
-      </c>
-      <c r="B120" t="s">
-        <v>34</v>
-      </c>
-      <c r="C120" t="s">
-        <v>66</v>
-      </c>
-      <c r="D120" t="s">
-        <v>46</v>
-      </c>
-      <c r="E120" t="s">
-        <v>46</v>
-      </c>
-      <c r="F120" t="s">
-        <v>46</v>
-      </c>
-      <c r="G120" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
-      <c r="A121" t="s">
-        <v>24</v>
-      </c>
-      <c r="B121" t="s">
-        <v>39</v>
-      </c>
-      <c r="C121" t="s">
-        <v>67</v>
-      </c>
-      <c r="D121" t="s">
-        <v>46</v>
-      </c>
-      <c r="E121" t="s">
-        <v>46</v>
-      </c>
-      <c r="F121" t="s">
-        <v>46</v>
-      </c>
-      <c r="G121" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
-      <c r="A122" t="s">
-        <v>24</v>
-      </c>
-      <c r="B122" t="s">
-        <v>39</v>
-      </c>
-      <c r="C122" t="s">
-        <v>68</v>
-      </c>
-      <c r="D122" t="s">
-        <v>46</v>
-      </c>
-      <c r="E122" t="s">
-        <v>46</v>
-      </c>
-      <c r="F122" t="s">
-        <v>46</v>
-      </c>
-      <c r="G122" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
-      <c r="A123" t="s">
-        <v>24</v>
-      </c>
-      <c r="B123" t="s">
-        <v>39</v>
-      </c>
-      <c r="C123" t="s">
-        <v>69</v>
-      </c>
-      <c r="D123" t="s">
-        <v>46</v>
-      </c>
-      <c r="E123" t="s">
-        <v>46</v>
-      </c>
-      <c r="F123" t="s">
-        <v>46</v>
-      </c>
-      <c r="G123" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
-      <c r="A124" t="s">
-        <v>24</v>
-      </c>
-      <c r="B124" t="s">
-        <v>39</v>
-      </c>
-      <c r="C124" t="s">
-        <v>70</v>
-      </c>
-      <c r="D124" t="s">
-        <v>46</v>
-      </c>
-      <c r="E124" t="s">
-        <v>46</v>
-      </c>
-      <c r="F124" t="s">
-        <v>46</v>
-      </c>
-      <c r="G124" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
-      <c r="A125" t="s">
-        <v>24</v>
-      </c>
-      <c r="B125" t="s">
-        <v>39</v>
-      </c>
-      <c r="C125" t="s">
-        <v>71</v>
-      </c>
-      <c r="D125" t="s">
-        <v>46</v>
-      </c>
-      <c r="E125" t="s">
-        <v>46</v>
-      </c>
-      <c r="F125" t="s">
-        <v>46</v>
-      </c>
-      <c r="G125" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
-      <c r="A126" t="s">
-        <v>24</v>
-      </c>
-      <c r="B126" t="s">
-        <v>39</v>
-      </c>
-      <c r="C126" t="s">
-        <v>72</v>
-      </c>
-      <c r="D126" t="s">
-        <v>46</v>
-      </c>
-      <c r="E126" t="s">
-        <v>46</v>
-      </c>
-      <c r="F126" t="s">
-        <v>46</v>
-      </c>
-      <c r="G126" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
-      <c r="A127" t="s">
-        <v>24</v>
-      </c>
-      <c r="B127" t="s">
-        <v>39</v>
-      </c>
-      <c r="C127" t="s">
-        <v>73</v>
-      </c>
-      <c r="D127" t="s">
-        <v>46</v>
-      </c>
-      <c r="E127" t="s">
-        <v>46</v>
-      </c>
-      <c r="F127" t="s">
-        <v>46</v>
-      </c>
-      <c r="G127" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
-      <c r="A128" t="s">
-        <v>24</v>
-      </c>
-      <c r="B128" t="s">
-        <v>39</v>
-      </c>
-      <c r="C128" t="s">
-        <v>74</v>
-      </c>
-      <c r="D128" t="s">
-        <v>46</v>
-      </c>
-      <c r="E128" t="s">
-        <v>46</v>
-      </c>
-      <c r="F128" t="s">
-        <v>46</v>
-      </c>
-      <c r="G128" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7">
-      <c r="A129" t="s">
-        <v>24</v>
-      </c>
-      <c r="B129" t="s">
-        <v>39</v>
-      </c>
-      <c r="C129" t="s">
-        <v>75</v>
-      </c>
-      <c r="D129" t="s">
-        <v>46</v>
-      </c>
-      <c r="E129" t="s">
-        <v>46</v>
-      </c>
-      <c r="F129" t="s">
-        <v>46</v>
-      </c>
-      <c r="G129" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7">
-      <c r="A130" t="s">
-        <v>24</v>
-      </c>
-      <c r="B130" t="s">
-        <v>39</v>
-      </c>
-      <c r="C130" t="s">
-        <v>76</v>
-      </c>
-      <c r="D130" t="s">
-        <v>46</v>
-      </c>
-      <c r="E130" t="s">
-        <v>46</v>
-      </c>
-      <c r="F130" t="s">
-        <v>46</v>
-      </c>
-      <c r="G130" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7">
-      <c r="A131" t="s">
-        <v>24</v>
-      </c>
-      <c r="B131" t="s">
-        <v>39</v>
-      </c>
-      <c r="C131" t="s">
-        <v>77</v>
-      </c>
-      <c r="D131" t="s">
-        <v>46</v>
-      </c>
-      <c r="E131" t="s">
-        <v>46</v>
-      </c>
-      <c r="F131" t="s">
-        <v>46</v>
-      </c>
-      <c r="G131" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" t="s">
-        <v>24</v>
-      </c>
-      <c r="B132" t="s">
-        <v>35</v>
-      </c>
-      <c r="C132" t="s">
-        <v>78</v>
-      </c>
-      <c r="D132" t="s">
-        <v>46</v>
-      </c>
-      <c r="E132" t="s">
-        <v>46</v>
-      </c>
-      <c r="F132" t="s">
-        <v>46</v>
-      </c>
-      <c r="G132" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" t="s">
-        <v>24</v>
-      </c>
-      <c r="B133" t="s">
-        <v>35</v>
-      </c>
-      <c r="C133" t="s">
-        <v>79</v>
-      </c>
-      <c r="D133" t="s">
-        <v>46</v>
-      </c>
-      <c r="E133" t="s">
-        <v>46</v>
-      </c>
-      <c r="F133" t="s">
-        <v>46</v>
-      </c>
-      <c r="G133" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" t="s">
-        <v>28</v>
-      </c>
-      <c r="B134" t="s">
-        <v>33</v>
-      </c>
-      <c r="C134" t="s">
-        <v>54</v>
-      </c>
-      <c r="D134" t="s">
-        <v>46</v>
-      </c>
-      <c r="E134" t="s">
-        <v>46</v>
-      </c>
-      <c r="F134" t="s">
-        <v>46</v>
-      </c>
-      <c r="G134" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7">
-      <c r="A135" t="s">
-        <v>28</v>
-      </c>
-      <c r="B135" t="s">
-        <v>33</v>
-      </c>
-      <c r="C135" t="s">
-        <v>55</v>
-      </c>
-      <c r="D135" t="s">
-        <v>46</v>
-      </c>
-      <c r="E135" t="s">
-        <v>46</v>
-      </c>
-      <c r="F135" t="s">
-        <v>46</v>
-      </c>
-      <c r="G135" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7">
-      <c r="A136" t="s">
-        <v>28</v>
-      </c>
-      <c r="B136" t="s">
-        <v>33</v>
-      </c>
-      <c r="C136" t="s">
-        <v>56</v>
-      </c>
-      <c r="D136" t="s">
-        <v>46</v>
-      </c>
-      <c r="E136" t="s">
-        <v>46</v>
-      </c>
-      <c r="F136" t="s">
-        <v>46</v>
-      </c>
-      <c r="G136" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137" t="s">
-        <v>28</v>
-      </c>
-      <c r="B137" t="s">
-        <v>33</v>
-      </c>
-      <c r="C137" t="s">
-        <v>57</v>
-      </c>
-      <c r="D137" t="s">
-        <v>46</v>
-      </c>
-      <c r="E137" t="s">
-        <v>46</v>
-      </c>
-      <c r="F137" t="s">
-        <v>46</v>
-      </c>
-      <c r="G137" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="A138" t="s">
-        <v>28</v>
-      </c>
-      <c r="B138" t="s">
-        <v>33</v>
-      </c>
-      <c r="C138" t="s">
-        <v>58</v>
-      </c>
-      <c r="D138" t="s">
-        <v>46</v>
-      </c>
-      <c r="E138" t="s">
-        <v>46</v>
-      </c>
-      <c r="F138" t="s">
-        <v>46</v>
-      </c>
-      <c r="G138" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139" t="s">
-        <v>28</v>
-      </c>
-      <c r="B139" t="s">
-        <v>33</v>
-      </c>
-      <c r="C139" t="s">
-        <v>59</v>
-      </c>
-      <c r="D139" t="s">
-        <v>46</v>
-      </c>
-      <c r="E139" t="s">
-        <v>46</v>
-      </c>
-      <c r="F139" t="s">
-        <v>46</v>
-      </c>
-      <c r="G139" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="A140" t="s">
-        <v>28</v>
-      </c>
-      <c r="B140" t="s">
-        <v>33</v>
-      </c>
-      <c r="C140" t="s">
-        <v>60</v>
-      </c>
-      <c r="D140" t="s">
-        <v>46</v>
-      </c>
-      <c r="E140" t="s">
-        <v>46</v>
-      </c>
-      <c r="F140" t="s">
-        <v>46</v>
-      </c>
-      <c r="G140" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7">
-      <c r="A141" t="s">
-        <v>28</v>
-      </c>
-      <c r="B141" t="s">
-        <v>34</v>
-      </c>
-      <c r="C141" t="s">
-        <v>61</v>
-      </c>
-      <c r="D141" t="s">
-        <v>46</v>
-      </c>
-      <c r="E141" t="s">
-        <v>46</v>
-      </c>
-      <c r="F141" t="s">
-        <v>46</v>
-      </c>
-      <c r="G141" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="A142" t="s">
-        <v>28</v>
-      </c>
-      <c r="B142" t="s">
-        <v>34</v>
-      </c>
-      <c r="C142" t="s">
-        <v>62</v>
-      </c>
-      <c r="D142" t="s">
-        <v>46</v>
-      </c>
-      <c r="E142" t="s">
-        <v>46</v>
-      </c>
-      <c r="F142" t="s">
-        <v>46</v>
-      </c>
-      <c r="G142" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7">
-      <c r="A143" t="s">
-        <v>28</v>
-      </c>
-      <c r="B143" t="s">
-        <v>34</v>
-      </c>
-      <c r="C143" t="s">
-        <v>63</v>
-      </c>
-      <c r="D143" t="s">
-        <v>46</v>
-      </c>
-      <c r="E143" t="s">
-        <v>46</v>
-      </c>
-      <c r="F143" t="s">
-        <v>46</v>
-      </c>
-      <c r="G143" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7">
-      <c r="A144" t="s">
-        <v>28</v>
-      </c>
-      <c r="B144" t="s">
-        <v>34</v>
-      </c>
-      <c r="C144" t="s">
-        <v>64</v>
-      </c>
-      <c r="D144" t="s">
-        <v>46</v>
-      </c>
-      <c r="E144" t="s">
-        <v>46</v>
-      </c>
-      <c r="F144" t="s">
-        <v>46</v>
-      </c>
-      <c r="G144" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145" t="s">
-        <v>28</v>
-      </c>
-      <c r="B145" t="s">
-        <v>34</v>
-      </c>
-      <c r="C145" t="s">
-        <v>65</v>
-      </c>
-      <c r="D145" t="s">
-        <v>46</v>
-      </c>
-      <c r="E145" t="s">
-        <v>46</v>
-      </c>
-      <c r="F145" t="s">
-        <v>46</v>
-      </c>
-      <c r="G145" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7">
-      <c r="A146" t="s">
-        <v>28</v>
-      </c>
-      <c r="B146" t="s">
-        <v>34</v>
-      </c>
-      <c r="C146" t="s">
-        <v>66</v>
-      </c>
-      <c r="D146" t="s">
-        <v>46</v>
-      </c>
-      <c r="E146" t="s">
-        <v>46</v>
-      </c>
-      <c r="F146" t="s">
-        <v>46</v>
-      </c>
-      <c r="G146" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="A147" t="s">
-        <v>28</v>
-      </c>
-      <c r="B147" t="s">
-        <v>39</v>
-      </c>
-      <c r="C147" t="s">
-        <v>67</v>
-      </c>
-      <c r="D147" t="s">
-        <v>46</v>
-      </c>
-      <c r="E147" t="s">
-        <v>46</v>
-      </c>
-      <c r="F147" t="s">
-        <v>46</v>
-      </c>
-      <c r="G147" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="A148" t="s">
-        <v>28</v>
-      </c>
-      <c r="B148" t="s">
-        <v>39</v>
-      </c>
-      <c r="C148" t="s">
-        <v>68</v>
-      </c>
-      <c r="D148" t="s">
-        <v>46</v>
-      </c>
-      <c r="E148" t="s">
-        <v>46</v>
-      </c>
-      <c r="F148" t="s">
-        <v>46</v>
-      </c>
-      <c r="G148" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="A149" t="s">
-        <v>28</v>
-      </c>
-      <c r="B149" t="s">
-        <v>39</v>
-      </c>
-      <c r="C149" t="s">
-        <v>69</v>
-      </c>
-      <c r="D149" t="s">
-        <v>46</v>
-      </c>
-      <c r="E149" t="s">
-        <v>46</v>
-      </c>
-      <c r="F149" t="s">
-        <v>46</v>
-      </c>
-      <c r="G149" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="A150" t="s">
-        <v>28</v>
-      </c>
-      <c r="B150" t="s">
-        <v>39</v>
-      </c>
-      <c r="C150" t="s">
-        <v>70</v>
-      </c>
-      <c r="D150" t="s">
-        <v>46</v>
-      </c>
-      <c r="E150" t="s">
-        <v>46</v>
-      </c>
-      <c r="F150" t="s">
-        <v>46</v>
-      </c>
-      <c r="G150" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="A151" t="s">
-        <v>28</v>
-      </c>
-      <c r="B151" t="s">
-        <v>39</v>
-      </c>
-      <c r="C151" t="s">
-        <v>71</v>
-      </c>
-      <c r="D151" t="s">
-        <v>46</v>
-      </c>
-      <c r="E151" t="s">
-        <v>46</v>
-      </c>
-      <c r="F151" t="s">
-        <v>46</v>
-      </c>
-      <c r="G151" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152" t="s">
-        <v>28</v>
-      </c>
-      <c r="B152" t="s">
-        <v>39</v>
-      </c>
-      <c r="C152" t="s">
-        <v>72</v>
-      </c>
-      <c r="D152" t="s">
-        <v>46</v>
-      </c>
-      <c r="E152" t="s">
-        <v>46</v>
-      </c>
-      <c r="F152" t="s">
-        <v>46</v>
-      </c>
-      <c r="G152" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153" t="s">
-        <v>28</v>
-      </c>
-      <c r="B153" t="s">
-        <v>39</v>
-      </c>
-      <c r="C153" t="s">
-        <v>73</v>
-      </c>
-      <c r="D153" t="s">
-        <v>46</v>
-      </c>
-      <c r="E153" t="s">
-        <v>46</v>
-      </c>
-      <c r="F153" t="s">
-        <v>46</v>
-      </c>
-      <c r="G153" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154" t="s">
-        <v>28</v>
-      </c>
-      <c r="B154" t="s">
-        <v>39</v>
-      </c>
-      <c r="C154" t="s">
-        <v>74</v>
-      </c>
-      <c r="D154" t="s">
-        <v>46</v>
-      </c>
-      <c r="E154" t="s">
-        <v>46</v>
-      </c>
-      <c r="F154" t="s">
-        <v>46</v>
-      </c>
-      <c r="G154" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155" t="s">
-        <v>28</v>
-      </c>
-      <c r="B155" t="s">
-        <v>39</v>
-      </c>
-      <c r="C155" t="s">
-        <v>75</v>
-      </c>
-      <c r="D155" t="s">
-        <v>46</v>
-      </c>
-      <c r="E155" t="s">
-        <v>46</v>
-      </c>
-      <c r="F155" t="s">
-        <v>46</v>
-      </c>
-      <c r="G155" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="A156" t="s">
-        <v>28</v>
-      </c>
-      <c r="B156" t="s">
-        <v>39</v>
-      </c>
-      <c r="C156" t="s">
-        <v>76</v>
-      </c>
-      <c r="D156" t="s">
-        <v>46</v>
-      </c>
-      <c r="E156" t="s">
-        <v>46</v>
-      </c>
-      <c r="F156" t="s">
-        <v>46</v>
-      </c>
-      <c r="G156" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" t="s">
-        <v>28</v>
-      </c>
-      <c r="B157" t="s">
-        <v>39</v>
-      </c>
-      <c r="C157" t="s">
-        <v>77</v>
-      </c>
-      <c r="D157" t="s">
-        <v>46</v>
-      </c>
-      <c r="E157" t="s">
-        <v>46</v>
-      </c>
-      <c r="F157" t="s">
-        <v>46</v>
-      </c>
-      <c r="G157" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158" t="s">
-        <v>28</v>
-      </c>
-      <c r="B158" t="s">
-        <v>35</v>
-      </c>
-      <c r="C158" t="s">
-        <v>78</v>
-      </c>
-      <c r="D158" t="s">
-        <v>46</v>
-      </c>
-      <c r="E158" t="s">
-        <v>46</v>
-      </c>
-      <c r="F158" t="s">
-        <v>46</v>
-      </c>
-      <c r="G158" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" t="s">
-        <v>28</v>
-      </c>
-      <c r="B159" t="s">
-        <v>35</v>
-      </c>
-      <c r="C159" t="s">
-        <v>79</v>
-      </c>
       <c r="D159" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E159" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F159" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G159" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -5612,13 +5608,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="28.05" customHeight="1">
       <c r="A1" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>6</v>
@@ -5629,177 +5625,177 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="B4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="B5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="B6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="B7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="B8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="B9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="B10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="B12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="B13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="B14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="C15" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="C16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="3:3">
       <c r="C17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="3:3">
       <c r="C18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="3:3">
       <c r="C20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="3:3">
       <c r="C21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="3:3">
       <c r="C22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="3:3">
       <c r="C23" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="3:3">
       <c r="C24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="3:3">
       <c r="C25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="3:3">
       <c r="C26" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="3:3">
       <c r="C27" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -5819,7 +5815,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="22.35" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5829,10 +5825,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -5844,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -5853,10 +5849,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -5865,10 +5861,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -5877,10 +5873,10 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -5889,10 +5885,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -5901,10 +5897,10 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -5913,10 +5909,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -5925,10 +5921,10 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V2_43_3_PERMISSION_AUTO_REFRESH_ENGINE\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A00248-C3E9-46A7-A9F2-A7BED90BE45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D953D78-7284-4AC1-ADD5-F0DA45BB67CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -649,9 +649,16 @@
         <filter val="mohamed_syed"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="PMO Audit"/>
+        <filter val="Audit Comparison"/>
+        <filter val="Executive Overall Stages Summary &amp; Cost Exposure"/>
+        <filter val="Executive SOR Summary &amp; Revenue Exposure"/>
+        <filter val="Master Data Inventory"/>
+        <filter val="Missing MET Actual"/>
+        <filter val="Overall Projects Stages — Cost Analysis"/>
+        <filter val="PMO Audit &amp; MET Reconciliation"/>
+        <filter val="SOR Details"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -5979,7 +5986,7 @@
         <v>86</v>
       </c>
       <c r="D203" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E203" t="s">
         <v>41</v>
@@ -5991,7 +5998,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1">
+    <row r="204" spans="1:7">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -6002,7 +6009,7 @@
         <v>87</v>
       </c>
       <c r="D204" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E204" t="s">
         <v>41</v>
@@ -6014,7 +6021,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1">
+    <row r="205" spans="1:7">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -6025,7 +6032,7 @@
         <v>88</v>
       </c>
       <c r="D205" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E205" t="s">
         <v>41</v>
@@ -6048,7 +6055,7 @@
         <v>89</v>
       </c>
       <c r="D206" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E206" t="s">
         <v>41</v>
@@ -6071,7 +6078,7 @@
         <v>90</v>
       </c>
       <c r="D207" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E207" t="s">
         <v>41</v>
@@ -6094,7 +6101,7 @@
         <v>91</v>
       </c>
       <c r="D208" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E208" t="s">
         <v>41</v>
@@ -6244,7 +6251,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1">
+    <row r="215" spans="1:7">
       <c r="A215" t="s">
         <v>16</v>
       </c>
@@ -6255,7 +6262,7 @@
         <v>98</v>
       </c>
       <c r="D215" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E215" t="s">
         <v>41</v>
@@ -6267,7 +6274,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1">
+    <row r="216" spans="1:7">
       <c r="A216" t="s">
         <v>16</v>
       </c>
@@ -6278,7 +6285,7 @@
         <v>99</v>
       </c>
       <c r="D216" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E216" t="s">
         <v>41</v>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Dawiyat\Dashboard Analysis\Dawiyat_Executive_Board_Dashboard_PMO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V3_Admin_Board_User_Permissions_ADMIN_FILTER_BACK_FIXED\Dawiyat_PMO_Executive_Portal_V3_Admin_Board_User_Permissions\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A0FD0E4-5BA3-4008-8E00-6D186CC9C01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E690BC00-C86D-4EAF-900C-8AB8045DC0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="152">
   <si>
     <t>Users</t>
   </si>
@@ -471,6 +471,15 @@
   </si>
   <si>
     <t>Monthly Progress Trend 2025-2026</t>
+  </si>
+  <si>
+    <t>Adham_Ismail</t>
+  </si>
+  <si>
+    <t>Adham@Met123</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
   </si>
 </sst>
 </file>
@@ -501,7 +510,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -523,6 +532,18 @@
         <fgColor rgb="FFE0F2FE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -536,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -551,39 +572,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -696,7 +691,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UsersTable" displayName="UsersTable" ref="A3:F9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="UsersTable" displayName="UsersTable" ref="A3:F10">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Password"/>
@@ -710,7 +705,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="UserPageAccessTable" displayName="UserPageAccessTable" ref="A3:N9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="UserPageAccessTable" displayName="UserPageAccessTable" ref="A3:N10">
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Executive Overview"/>
@@ -732,7 +727,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="UserComponentAccessTable" displayName="UserComponentAccessTable" ref="A3:H506">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="UserComponentAccessTable" displayName="UserComponentAccessTable" ref="A3:H443">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Username"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Page"/>
@@ -896,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -959,27 +954,27 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>15</v>
@@ -993,52 +988,69 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>26</v>
       </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1046,16 +1058,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:D500">
-    <cfRule type="expression" dxfId="17" priority="1">
+  <conditionalFormatting sqref="D4:D501">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="12" priority="2">
       <formula>UPPER(B4)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D4:D500" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="D4:D501" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1068,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1183,13 +1195,13 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>41</v>
@@ -1204,13 +1216,13 @@
         <v>41</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
         <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K5" t="s">
         <v>41</v>
@@ -1227,7 +1239,7 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
         <v>41</v>
@@ -1271,7 +1283,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -1292,7 +1304,7 @@
         <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
         <v>41</v>
@@ -1315,7 +1327,7 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
         <v>41</v>
@@ -1359,45 +1371,89 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" t="s">
-        <v>41</v>
-      </c>
-      <c r="I9" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" t="s">
-        <v>41</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1405,16 +1461,16 @@
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B4:N500">
-    <cfRule type="expression" dxfId="15" priority="1">
+  <conditionalFormatting sqref="B4:N501">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>UPPER(B4)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B4:N500" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="B4:N501" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1427,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18.796875" customWidth="1"/>
@@ -1476,19 +1532,19 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
@@ -1499,19 +1555,19 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
@@ -1522,19 +1578,19 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
@@ -1545,19 +1601,19 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
@@ -1568,19 +1624,19 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
@@ -1591,19 +1647,19 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="A9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
@@ -1614,19 +1670,19 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
@@ -1637,19 +1693,19 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="A11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
@@ -1660,19 +1716,19 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="A12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
@@ -1683,19 +1739,19 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="A13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
@@ -1706,19 +1762,19 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="A14" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
@@ -1729,19 +1785,19 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="A15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
@@ -1752,19 +1808,19 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="A16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="D16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
@@ -1775,19 +1831,19 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="A17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
@@ -1798,19 +1854,19 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="A18" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
@@ -1821,19 +1877,19 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="A19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
@@ -1844,19 +1900,19 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="A20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="D20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
@@ -1867,19 +1923,19 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="A21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="D21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
@@ -1890,19 +1946,19 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="A22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="D22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
@@ -1913,19 +1969,19 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="A23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="D23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
@@ -1936,19 +1992,19 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="A24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="D24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
@@ -1959,19 +2015,19 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="A25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="D25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
@@ -1982,19 +2038,19 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="A26" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D26" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="D26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F26" t="s">
@@ -2005,19 +2061,19 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="A27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
@@ -2028,19 +2084,19 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="A28" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="D28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
@@ -2051,19 +2107,19 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="A29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D29" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
@@ -2074,19 +2130,19 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="A30" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D30" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="D30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
@@ -2097,19 +2153,19 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="A31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D31" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="D31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F31" t="s">
@@ -2120,19 +2176,19 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="A32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D32" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="D32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
@@ -2143,19 +2199,19 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="A33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D33" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" t="s">
+      <c r="D33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
@@ -2166,19 +2222,19 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="A34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D34" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="D34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
@@ -2189,19 +2245,19 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" t="s">
+      <c r="A35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D35" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="D35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
@@ -2212,19 +2268,19 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="A36" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D36" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" t="s">
+      <c r="D36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
@@ -2235,19 +2291,19 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" t="s">
+      <c r="A37" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D37" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="D37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
@@ -2258,19 +2314,19 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" t="s">
+      <c r="A38" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D38" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" t="s">
+      <c r="D38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F38" t="s">
@@ -2281,19 +2337,19 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="s">
+      <c r="A39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D39" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="D39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F39" t="s">
@@ -2304,19 +2360,19 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" t="s">
+      <c r="A40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" t="s">
+      <c r="D40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F40" t="s">
@@ -2327,19 +2383,19 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" t="s">
+      <c r="A41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D41" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="D41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
@@ -2350,19 +2406,19 @@
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" t="s">
+      <c r="A42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D42" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
+      <c r="D42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
@@ -2373,19 +2429,19 @@
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" t="s">
+      <c r="A43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D43" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" t="s">
+      <c r="D43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F43" t="s">
@@ -2396,19 +2452,19 @@
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="A44" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="D44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
@@ -2419,19 +2475,19 @@
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="A45" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D45" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" t="s">
+      <c r="D45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
@@ -2442,19 +2498,19 @@
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="A46" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D46" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" t="s">
+      <c r="D46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F46" t="s">
@@ -2465,19 +2521,19 @@
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="A47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D47" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="D47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F47" t="s">
@@ -2488,19 +2544,19 @@
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" t="s">
+      <c r="A48" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="D48" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" t="s">
+      <c r="D48" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F48" t="s">
@@ -2511,19 +2567,19 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" t="s">
+      <c r="A49" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D49" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" t="s">
+      <c r="D49" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F49" t="s">
@@ -2534,19 +2590,19 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" t="s">
+      <c r="A50" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D50" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="D50" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F50" t="s">
@@ -2557,19 +2613,19 @@
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="A51" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D51" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="D51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
@@ -2580,19 +2636,19 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" t="s">
+      <c r="A52" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="D52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F52" t="s">
@@ -2603,19 +2659,19 @@
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" t="s">
+      <c r="A53" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="D53" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F53" t="s">
@@ -2626,19 +2682,19 @@
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" t="s">
+      <c r="A54" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D54" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="D54" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F54" t="s">
@@ -2649,19 +2705,19 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" t="s">
+      <c r="A55" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="D55" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F55" t="s">
@@ -2672,19 +2728,19 @@
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" t="s">
+      <c r="A56" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D56" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" t="s">
+      <c r="D56" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F56" t="s">
@@ -2695,19 +2751,19 @@
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" t="s">
-        <v>7</v>
-      </c>
-      <c r="B57" t="s">
+      <c r="A57" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D57" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" t="s">
+      <c r="D57" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
@@ -2718,19 +2774,19 @@
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="A58" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D58" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="D58" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F58" t="s">
@@ -2741,19 +2797,19 @@
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" t="s">
-        <v>7</v>
-      </c>
-      <c r="B59" t="s">
+      <c r="A59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D59" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" t="s">
+      <c r="D59" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F59" t="s">
@@ -2764,19 +2820,19 @@
       </c>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60" t="s">
+      <c r="A60" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="D60" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F60" t="s">
@@ -2787,19 +2843,19 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" t="s">
-        <v>7</v>
-      </c>
-      <c r="B61" t="s">
+      <c r="A61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D61" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="D61" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F61" t="s">
@@ -2810,19 +2866,19 @@
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" t="s">
+      <c r="A62" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D62" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="D62" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="s">
@@ -2833,19 +2889,19 @@
       </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" t="s">
+      <c r="A63" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D63" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="D63" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F63" t="s">
@@ -2856,19 +2912,19 @@
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" t="s">
+      <c r="A64" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D64" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="D64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F64" t="s">
@@ -2879,19 +2935,19 @@
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" t="s">
-        <v>7</v>
-      </c>
-      <c r="B65" t="s">
+      <c r="A65" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D65" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="D65" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
@@ -2902,19 +2958,19 @@
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="A66" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="D66" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="D66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F66" t="s">
@@ -2925,19 +2981,19 @@
       </c>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" t="s">
+      <c r="A67" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D67" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" t="s">
+      <c r="D67" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F67" t="s">
@@ -2948,19 +3004,19 @@
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" t="s">
+      <c r="A68" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D68" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" t="s">
+      <c r="D68" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F68" t="s">
@@ -2971,19 +3027,19 @@
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" t="s">
-        <v>7</v>
-      </c>
-      <c r="B69" t="s">
+      <c r="A69" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="D69" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="D69" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F69" t="s">
@@ -2994,19 +3050,19 @@
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" t="s">
-        <v>7</v>
-      </c>
-      <c r="B70" t="s">
+      <c r="A70" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D70" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="D70" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F70" t="s">
@@ -3017,19 +3073,19 @@
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" t="s">
+      <c r="A71" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D71" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="D71" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F71" t="s">
@@ -3040,19 +3096,19 @@
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="A72" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D72" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="D72" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F72" t="s">
@@ -3063,19 +3119,19 @@
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" t="s">
-        <v>7</v>
-      </c>
-      <c r="B73" t="s">
+      <c r="A73" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D73" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="D73" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F73" t="s">
@@ -3086,19 +3142,19 @@
       </c>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" t="s">
+      <c r="A74" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D74" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="D74" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
@@ -3109,19 +3165,19 @@
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" t="s">
-        <v>7</v>
-      </c>
-      <c r="B75" t="s">
+      <c r="A75" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="D75" t="s">
-        <v>10</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="D75" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F75" t="s">
@@ -3132,19 +3188,19 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" t="s">
+      <c r="A76" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D76" t="s">
-        <v>10</v>
-      </c>
-      <c r="E76" t="s">
+      <c r="D76" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F76" t="s">
@@ -3155,19 +3211,19 @@
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" t="s">
-        <v>7</v>
-      </c>
-      <c r="B77" t="s">
+      <c r="A77" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D77" t="s">
-        <v>10</v>
-      </c>
-      <c r="E77" t="s">
+      <c r="D77" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F77" t="s">
@@ -3178,19 +3234,19 @@
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" t="s">
+      <c r="A78" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D78" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" t="s">
+      <c r="D78" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F78" t="s">
@@ -3201,19 +3257,19 @@
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" t="s">
+      <c r="A79" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D79" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="D79" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F79" t="s">
@@ -3224,19 +3280,19 @@
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="A80" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D80" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" t="s">
+      <c r="D80" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F80" t="s">
@@ -3247,19 +3303,19 @@
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" t="s">
-        <v>7</v>
-      </c>
-      <c r="B81" t="s">
+      <c r="A81" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D81" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" t="s">
+      <c r="D81" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F81" t="s">
@@ -3270,19 +3326,19 @@
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" t="s">
-        <v>7</v>
-      </c>
-      <c r="B82" t="s">
+      <c r="A82" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D82" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="D82" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F82" t="s">
@@ -3293,19 +3349,19 @@
       </c>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="A83" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D83" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" t="s">
+      <c r="D83" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F83" t="s">
@@ -3316,19 +3372,19 @@
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" t="s">
-        <v>7</v>
-      </c>
-      <c r="B84" t="s">
+      <c r="A84" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D84" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" t="s">
+      <c r="D84" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F84" t="s">
@@ -3339,19 +3395,19 @@
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" t="s">
-        <v>7</v>
-      </c>
-      <c r="B85" t="s">
+      <c r="A85" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D85" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" t="s">
+      <c r="D85" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F85" t="s">
@@ -3362,19 +3418,19 @@
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" t="s">
-        <v>7</v>
-      </c>
-      <c r="B86" t="s">
+      <c r="A86" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D86" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" t="s">
+      <c r="D86" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
@@ -3385,19 +3441,19 @@
       </c>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" t="s">
-        <v>7</v>
-      </c>
-      <c r="B87" t="s">
+      <c r="A87" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D87" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" t="s">
+      <c r="D87" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F87" t="s">
@@ -3408,19 +3464,19 @@
       </c>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" t="s">
-        <v>7</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="A88" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D88" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="D88" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F88" t="s">
@@ -3431,19 +3487,19 @@
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" t="s">
-        <v>7</v>
-      </c>
-      <c r="B89" t="s">
+      <c r="A89" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D89" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" t="s">
+      <c r="D89" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F89" t="s">
@@ -3454,19 +3510,19 @@
       </c>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" t="s">
-        <v>7</v>
-      </c>
-      <c r="B90" t="s">
+      <c r="A90" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D90" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="D90" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F90" t="s">
@@ -3477,25 +3533,600 @@
       </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" t="s">
-        <v>7</v>
-      </c>
-      <c r="B91" t="s">
+      <c r="A91" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D91" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" t="s">
+      <c r="D91" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F91" t="s">
         <v>10</v>
       </c>
       <c r="G91" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" t="s">
+        <v>10</v>
+      </c>
+      <c r="G92" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" t="s">
+        <v>10</v>
+      </c>
+      <c r="G93" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" t="s">
+        <v>10</v>
+      </c>
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F97" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" t="s">
+        <v>10</v>
+      </c>
+      <c r="G103" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F106" t="s">
+        <v>10</v>
+      </c>
+      <c r="G106" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F107" t="s">
+        <v>10</v>
+      </c>
+      <c r="G107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F108" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F109" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" t="s">
+        <v>10</v>
+      </c>
+      <c r="G110" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F111" t="s">
+        <v>10</v>
+      </c>
+      <c r="G111" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F112" t="s">
+        <v>10</v>
+      </c>
+      <c r="G112" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" t="s">
+        <v>10</v>
+      </c>
+      <c r="G113" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F114" t="s">
+        <v>10</v>
+      </c>
+      <c r="G114" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" t="s">
+        <v>10</v>
+      </c>
+      <c r="G115" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" t="s">
+        <v>10</v>
+      </c>
+      <c r="G116" t="s">
         <v>10</v>
       </c>
     </row>
@@ -3503,64 +4134,48 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D4:G24 D26:G27 D29:G35 D37:G61 D63:G63 D65:G71 D73:G2017">
-    <cfRule type="expression" dxfId="13" priority="15">
+  <conditionalFormatting sqref="D4:G35 D92:G1954">
+    <cfRule type="expression" dxfId="9" priority="19">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="16">
+    <cfRule type="expression" dxfId="8" priority="20">
       <formula>UPPER(B4)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D25:G25">
-    <cfRule type="expression" dxfId="11" priority="11">
-      <formula>UPPER(B25)="YES"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="12">
-      <formula>UPPER(B25)="NO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D28:G28">
-    <cfRule type="expression" dxfId="9" priority="9">
-      <formula>UPPER(B28)="YES"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="10">
-      <formula>UPPER(B28)="NO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D36:G36">
-    <cfRule type="expression" dxfId="7" priority="21">
+  <conditionalFormatting sqref="D36:E36">
+    <cfRule type="expression" dxfId="7" priority="31">
       <formula>UPPER(#REF!)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="22">
+    <cfRule type="expression" dxfId="6" priority="32">
       <formula>UPPER(#REF!)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D62:G62">
-    <cfRule type="expression" dxfId="5" priority="7">
-      <formula>UPPER(B62)="YES"</formula>
+  <conditionalFormatting sqref="D37:G72">
+    <cfRule type="expression" dxfId="5" priority="11">
+      <formula>UPPER(B37)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8">
-      <formula>UPPER(B62)="NO"</formula>
+    <cfRule type="expression" dxfId="4" priority="12">
+      <formula>UPPER(B37)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D64:G64">
-    <cfRule type="expression" dxfId="3" priority="5">
-      <formula>UPPER(B64)="YES"</formula>
+  <conditionalFormatting sqref="D73:G91">
+    <cfRule type="expression" dxfId="3" priority="25">
+      <formula>UPPER(B73)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="6">
-      <formula>UPPER(B64)="NO"</formula>
+    <cfRule type="expression" dxfId="2" priority="26">
+      <formula>UPPER(B73)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D72:G72">
+  <conditionalFormatting sqref="F36:G36">
     <cfRule type="expression" dxfId="1" priority="1">
-      <formula>UPPER(B72)="YES"</formula>
+      <formula>UPPER(D36)="YES"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="2">
-      <formula>UPPER(B72)="NO"</formula>
+      <formula>UPPER(D36)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D75:G85 D4:G74 D86:G603" xr:uid="{00000000-0002-0000-0200-000000000000}">
+    <dataValidation type="list" sqref="D4:G540" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V3_Admin_Board_User_Permissions_ADMIN_FILTER_BACK_FIXED\Dawiyat_PMO_Executive_Portal_V3_Admin_Board_User_Permissions\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E690BC00-C86D-4EAF-900C-8AB8045DC0C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CC54EC-BD19-47C3-8643-6209517120B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="152">
   <si>
     <t>Users</t>
   </si>
@@ -568,17 +568,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFEE2E2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFDCFCE7"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -903,14 +931,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.35" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="28.8" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1059,10 +1087,10 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D501">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>UPPER(B4)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1088,22 +1116,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="22.35" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
     </row>
     <row r="3" spans="1:14" ht="49.2" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1462,10 +1490,10 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:N501">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>UPPER(B4)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1483,7 +1511,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H179"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18.796875" customWidth="1"/>
@@ -1494,16 +1522,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.35" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="28.8" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1532,19 +1560,19 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="D4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
@@ -1555,19 +1583,19 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
@@ -1578,19 +1606,19 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
@@ -1601,19 +1629,19 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
@@ -1624,19 +1652,19 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
@@ -1647,19 +1675,19 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
@@ -1670,19 +1698,19 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="D10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F10" t="s">
@@ -1693,19 +1721,19 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
@@ -1716,19 +1744,19 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F12" t="s">
@@ -1739,19 +1767,19 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="s">
+      <c r="A13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
@@ -1762,19 +1790,19 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
@@ -1785,19 +1813,19 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
@@ -1808,19 +1836,19 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
@@ -1831,19 +1859,19 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F17" t="s">
@@ -1854,19 +1882,19 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
@@ -1877,19 +1905,19 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="A19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="D19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
@@ -1900,19 +1928,19 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="D20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
@@ -1923,19 +1951,19 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="6" t="s">
+      <c r="A21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="D21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
@@ -1946,19 +1974,19 @@
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
@@ -1969,19 +1997,19 @@
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" s="6" t="s">
+      <c r="A23" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
@@ -1992,19 +2020,19 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="6" t="s">
+      <c r="A24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
@@ -2015,19 +2043,19 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="A25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
@@ -2038,19 +2066,19 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" s="6" t="s">
+      <c r="A26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="D26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F26" t="s">
@@ -2061,19 +2089,19 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="A27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="D27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
@@ -2084,19 +2112,19 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="A28" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="6" t="s">
+      <c r="D28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
@@ -2107,19 +2135,19 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="A29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="6" t="s">
+      <c r="D29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
@@ -2130,19 +2158,19 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="A30" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="D30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F30" t="s">
@@ -2153,19 +2181,19 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="A31" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="D31" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F31" t="s">
@@ -2176,19 +2204,19 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B32" s="6" t="s">
+      <c r="A32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
@@ -2199,19 +2227,19 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="6" t="s">
+      <c r="A33" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="D33" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
@@ -2222,19 +2250,19 @@
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34" s="6" t="s">
+      <c r="A34" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
@@ -2245,19 +2273,19 @@
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B35" s="6" t="s">
+      <c r="A35" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="D35" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
@@ -2268,19 +2296,19 @@
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="6" t="s">
+      <c r="A36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="D36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F36" t="s">
@@ -2291,19 +2319,19 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B37" s="6" t="s">
+      <c r="A37" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="6" t="s">
+      <c r="D37" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
@@ -2314,19 +2342,19 @@
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B38" s="6" t="s">
+      <c r="A38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="6" t="s">
+      <c r="D38" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F38" t="s">
@@ -2337,19 +2365,19 @@
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="6" t="s">
+      <c r="A39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="6" t="s">
+      <c r="D39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F39" t="s">
@@ -2360,19 +2388,19 @@
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="6" t="s">
+      <c r="A40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="6" t="s">
+      <c r="D40" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F40" t="s">
@@ -2383,19 +2411,19 @@
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="6" t="s">
+      <c r="A41" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="6" t="s">
+      <c r="D41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
@@ -2406,19 +2434,19 @@
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B42" s="6" t="s">
+      <c r="A42" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="D42" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F42" t="s">
@@ -2429,19 +2457,19 @@
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="A43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="6" t="s">
+      <c r="D43" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F43" t="s">
@@ -2452,19 +2480,19 @@
       </c>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="6" t="s">
+      <c r="A44" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="6" t="s">
+      <c r="D44" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
@@ -2475,19 +2503,19 @@
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B45" s="6" t="s">
+      <c r="A45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="6" t="s">
+      <c r="D45" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
@@ -2498,19 +2526,19 @@
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="6" t="s">
+      <c r="A46" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="D46" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F46" t="s">
@@ -2521,19 +2549,19 @@
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B47" s="6" t="s">
+      <c r="A47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="6" t="s">
+      <c r="D47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F47" t="s">
@@ -2544,19 +2572,19 @@
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="6" t="s">
+      <c r="A48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="6" t="s">
+      <c r="D48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F48" t="s">
@@ -2567,19 +2595,19 @@
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="6" t="s">
+      <c r="A49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="6" t="s">
+      <c r="D49" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F49" t="s">
@@ -2590,19 +2618,19 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="A50" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="6" t="s">
+      <c r="D50" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F50" t="s">
@@ -2613,19 +2641,19 @@
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B51" s="6" t="s">
+      <c r="A51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E51" s="6" t="s">
+      <c r="D51" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
@@ -2636,19 +2664,19 @@
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="6" t="s">
+      <c r="A52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E52" s="6" t="s">
+      <c r="D52" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F52" t="s">
@@ -2659,19 +2687,19 @@
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B53" s="6" t="s">
+      <c r="A53" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D53" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E53" s="6" t="s">
+      <c r="D53" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F53" t="s">
@@ -2682,19 +2710,19 @@
       </c>
     </row>
     <row r="54" spans="1:7">
-      <c r="A54" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B54" s="6" t="s">
+      <c r="A54" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D54" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E54" s="6" t="s">
+      <c r="D54" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F54" t="s">
@@ -2705,19 +2733,19 @@
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B55" s="6" t="s">
+      <c r="A55" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D55" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E55" s="6" t="s">
+      <c r="D55" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F55" t="s">
@@ -2728,19 +2756,19 @@
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B56" s="6" t="s">
+      <c r="A56" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E56" s="6" t="s">
+      <c r="D56" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F56" t="s">
@@ -2751,19 +2779,19 @@
       </c>
     </row>
     <row r="57" spans="1:7">
-      <c r="A57" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="A57" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="6" t="s">
+      <c r="D57" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
@@ -2774,19 +2802,19 @@
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B58" s="6" t="s">
+      <c r="A58" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D58" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E58" s="6" t="s">
+      <c r="D58" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F58" t="s">
@@ -2797,19 +2825,19 @@
       </c>
     </row>
     <row r="59" spans="1:7">
-      <c r="A59" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="A59" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E59" s="6" t="s">
+      <c r="D59" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F59" t="s">
@@ -2820,19 +2848,19 @@
       </c>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60" s="6" t="s">
+      <c r="A60" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E60" s="6" t="s">
+      <c r="D60" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F60" t="s">
@@ -2843,19 +2871,19 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="A61" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E61" s="6" t="s">
+      <c r="D61" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F61" t="s">
@@ -2866,19 +2894,19 @@
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B62" s="6" t="s">
+      <c r="A62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D62" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E62" s="6" t="s">
+      <c r="D62" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="s">
@@ -2889,19 +2917,19 @@
       </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="A63" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B63" s="6" t="s">
+      <c r="A63" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" s="6" t="s">
+      <c r="D63" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F63" t="s">
@@ -2912,19 +2940,19 @@
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="A64" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B64" s="6" t="s">
+      <c r="A64" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D64" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" s="6" t="s">
+      <c r="D64" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F64" t="s">
@@ -2935,19 +2963,19 @@
       </c>
     </row>
     <row r="65" spans="1:7">
-      <c r="A65" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B65" s="6" t="s">
+      <c r="A65" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E65" s="6" t="s">
+      <c r="D65" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
@@ -2958,19 +2986,19 @@
       </c>
     </row>
     <row r="66" spans="1:7">
-      <c r="A66" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B66" s="6" t="s">
+      <c r="A66" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D66" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" s="6" t="s">
+      <c r="D66" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F66" t="s">
@@ -2981,19 +3009,19 @@
       </c>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B67" s="6" t="s">
+      <c r="A67" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D67" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E67" s="6" t="s">
+      <c r="D67" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F67" t="s">
@@ -3004,19 +3032,19 @@
       </c>
     </row>
     <row r="68" spans="1:7">
-      <c r="A68" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B68" s="6" t="s">
+      <c r="A68" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E68" s="6" t="s">
+      <c r="D68" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F68" t="s">
@@ -3027,19 +3055,19 @@
       </c>
     </row>
     <row r="69" spans="1:7">
-      <c r="A69" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B69" s="6" t="s">
+      <c r="A69" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D69" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E69" s="6" t="s">
+      <c r="D69" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F69" t="s">
@@ -3050,19 +3078,19 @@
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B70" s="6" t="s">
+      <c r="A70" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E70" s="6" t="s">
+      <c r="D70" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F70" t="s">
@@ -3073,19 +3101,19 @@
       </c>
     </row>
     <row r="71" spans="1:7">
-      <c r="A71" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" s="6" t="s">
+      <c r="A71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D71" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E71" s="6" t="s">
+      <c r="D71" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F71" t="s">
@@ -3096,19 +3124,19 @@
       </c>
     </row>
     <row r="72" spans="1:7">
-      <c r="A72" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B72" s="6" t="s">
+      <c r="A72" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D72" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E72" s="6" t="s">
+      <c r="D72" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F72" t="s">
@@ -3119,19 +3147,19 @@
       </c>
     </row>
     <row r="73" spans="1:7">
-      <c r="A73" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="A73" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D73" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="6" t="s">
+      <c r="D73" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F73" t="s">
@@ -3142,19 +3170,19 @@
       </c>
     </row>
     <row r="74" spans="1:7">
-      <c r="A74" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B74" s="6" t="s">
+      <c r="A74" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E74" s="6" t="s">
+      <c r="D74" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
@@ -3165,19 +3193,19 @@
       </c>
     </row>
     <row r="75" spans="1:7">
-      <c r="A75" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B75" s="6" t="s">
+      <c r="A75" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D75" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E75" s="6" t="s">
+      <c r="D75" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F75" t="s">
@@ -3188,19 +3216,19 @@
       </c>
     </row>
     <row r="76" spans="1:7">
-      <c r="A76" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B76" s="6" t="s">
+      <c r="A76" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D76" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E76" s="6" t="s">
+      <c r="D76" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F76" t="s">
@@ -3211,19 +3239,19 @@
       </c>
     </row>
     <row r="77" spans="1:7">
-      <c r="A77" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B77" s="6" t="s">
+      <c r="A77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D77" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E77" s="6" t="s">
+      <c r="D77" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F77" t="s">
@@ -3234,19 +3262,19 @@
       </c>
     </row>
     <row r="78" spans="1:7">
-      <c r="A78" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B78" s="6" t="s">
+      <c r="A78" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="6" t="s">
+      <c r="C78" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D78" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E78" s="6" t="s">
+      <c r="D78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F78" t="s">
@@ -3257,19 +3285,19 @@
       </c>
     </row>
     <row r="79" spans="1:7">
-      <c r="A79" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B79" s="6" t="s">
+      <c r="A79" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C79" s="6" t="s">
+      <c r="C79" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D79" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E79" s="6" t="s">
+      <c r="D79" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F79" t="s">
@@ -3280,19 +3308,19 @@
       </c>
     </row>
     <row r="80" spans="1:7">
-      <c r="A80" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B80" s="6" t="s">
+      <c r="A80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C80" s="6" t="s">
+      <c r="C80" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D80" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E80" s="6" t="s">
+      <c r="D80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F80" t="s">
@@ -3303,19 +3331,19 @@
       </c>
     </row>
     <row r="81" spans="1:7">
-      <c r="A81" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B81" s="6" t="s">
+      <c r="A81" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C81" s="6" t="s">
+      <c r="C81" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D81" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="6" t="s">
+      <c r="D81" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F81" t="s">
@@ -3326,19 +3354,19 @@
       </c>
     </row>
     <row r="82" spans="1:7">
-      <c r="A82" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B82" s="6" t="s">
+      <c r="A82" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="C82" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="D82" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E82" s="6" t="s">
+      <c r="D82" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F82" t="s">
@@ -3349,19 +3377,19 @@
       </c>
     </row>
     <row r="83" spans="1:7">
-      <c r="A83" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B83" s="6" t="s">
+      <c r="A83" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C83" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D83" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="6" t="s">
+      <c r="D83" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F83" t="s">
@@ -3372,19 +3400,19 @@
       </c>
     </row>
     <row r="84" spans="1:7">
-      <c r="A84" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B84" s="6" t="s">
+      <c r="A84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C84" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D84" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="6" t="s">
+      <c r="D84" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F84" t="s">
@@ -3395,19 +3423,19 @@
       </c>
     </row>
     <row r="85" spans="1:7">
-      <c r="A85" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B85" s="6" t="s">
+      <c r="A85" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C85" s="6" t="s">
+      <c r="C85" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="6" t="s">
+      <c r="D85" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F85" t="s">
@@ -3418,19 +3446,19 @@
       </c>
     </row>
     <row r="86" spans="1:7">
-      <c r="A86" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B86" s="6" t="s">
+      <c r="A86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="C86" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D86" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="6" t="s">
+      <c r="D86" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
@@ -3441,19 +3469,19 @@
       </c>
     </row>
     <row r="87" spans="1:7">
-      <c r="A87" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B87" s="6" t="s">
+      <c r="A87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="C87" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D87" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="6" t="s">
+      <c r="D87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F87" t="s">
@@ -3464,19 +3492,19 @@
       </c>
     </row>
     <row r="88" spans="1:7">
-      <c r="A88" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B88" s="6" t="s">
+      <c r="A88" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C88" s="6" t="s">
+      <c r="C88" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D88" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="6" t="s">
+      <c r="D88" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F88" t="s">
@@ -3487,19 +3515,19 @@
       </c>
     </row>
     <row r="89" spans="1:7">
-      <c r="A89" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B89" s="6" t="s">
+      <c r="A89" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C89" s="6" t="s">
+      <c r="C89" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D89" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="6" t="s">
+      <c r="D89" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F89" t="s">
@@ -3510,19 +3538,19 @@
       </c>
     </row>
     <row r="90" spans="1:7">
-      <c r="A90" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B90" s="6" t="s">
+      <c r="A90" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C90" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D90" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" s="6" t="s">
+      <c r="D90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F90" t="s">
@@ -3533,19 +3561,19 @@
       </c>
     </row>
     <row r="91" spans="1:7">
-      <c r="A91" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B91" s="6" t="s">
+      <c r="A91" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C91" s="6" t="s">
+      <c r="C91" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D91" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="6" t="s">
+      <c r="D91" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F91" t="s">
@@ -3556,621 +3584,2062 @@
       </c>
     </row>
     <row r="92" spans="1:7">
-      <c r="A92" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B92" s="7" t="s">
+      <c r="A92" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F92" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F94" t="s">
+        <v>41</v>
+      </c>
+      <c r="G94" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F95" t="s">
+        <v>41</v>
+      </c>
+      <c r="G95" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F96" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F97" t="s">
+        <v>41</v>
+      </c>
+      <c r="G97" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F98" t="s">
+        <v>41</v>
+      </c>
+      <c r="G98" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F99" t="s">
+        <v>41</v>
+      </c>
+      <c r="G99" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B100" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C92" s="7" t="s">
+      <c r="C100" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D92" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
-      <c r="A93" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B93" s="7" t="s">
+      <c r="D100" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F100" t="s">
+        <v>10</v>
+      </c>
+      <c r="G100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C93" s="7" t="s">
+      <c r="C101" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D93" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
-      <c r="A94" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B94" s="7" t="s">
+      <c r="D101" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" t="s">
+        <v>10</v>
+      </c>
+      <c r="G101" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C94" s="7" t="s">
+      <c r="C102" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D94" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F94" t="s">
-        <v>10</v>
-      </c>
-      <c r="G94" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B95" s="7" t="s">
+      <c r="D102" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F102" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C95" s="7" t="s">
+      <c r="C103" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D95" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
-      <c r="A96" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B96" s="7" t="s">
+      <c r="D103" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F103" t="s">
+        <v>10</v>
+      </c>
+      <c r="G103" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C96" s="7" t="s">
+      <c r="C104" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D96" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B97" s="7" t="s">
+      <c r="D104" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F104" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F105" t="s">
+        <v>41</v>
+      </c>
+      <c r="G105" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F106" t="s">
+        <v>41</v>
+      </c>
+      <c r="G106" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F107" t="s">
+        <v>41</v>
+      </c>
+      <c r="G107" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F108" t="s">
+        <v>41</v>
+      </c>
+      <c r="G108" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F109" t="s">
+        <v>41</v>
+      </c>
+      <c r="G109" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F110" t="s">
+        <v>41</v>
+      </c>
+      <c r="G110" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F111" t="s">
+        <v>41</v>
+      </c>
+      <c r="G111" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F112" t="s">
+        <v>41</v>
+      </c>
+      <c r="G112" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F113" t="s">
+        <v>41</v>
+      </c>
+      <c r="G113" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F114" t="s">
+        <v>41</v>
+      </c>
+      <c r="G114" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F115" t="s">
+        <v>41</v>
+      </c>
+      <c r="G115" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F116" t="s">
+        <v>41</v>
+      </c>
+      <c r="G116" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F117" t="s">
+        <v>41</v>
+      </c>
+      <c r="G117" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F118" t="s">
+        <v>41</v>
+      </c>
+      <c r="G118" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F119" t="s">
+        <v>41</v>
+      </c>
+      <c r="G119" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F120" t="s">
+        <v>41</v>
+      </c>
+      <c r="G120" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F121" t="s">
+        <v>41</v>
+      </c>
+      <c r="G121" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F122" t="s">
+        <v>41</v>
+      </c>
+      <c r="G122" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F123" t="s">
+        <v>41</v>
+      </c>
+      <c r="G123" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F124" t="s">
+        <v>41</v>
+      </c>
+      <c r="G124" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F125" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E126" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F126" t="s">
+        <v>41</v>
+      </c>
+      <c r="G126" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F127" t="s">
+        <v>41</v>
+      </c>
+      <c r="G127" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E128" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" t="s">
+        <v>41</v>
+      </c>
+      <c r="G128" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F129" t="s">
+        <v>41</v>
+      </c>
+      <c r="G129" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F130" t="s">
+        <v>41</v>
+      </c>
+      <c r="G130" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F131" t="s">
+        <v>41</v>
+      </c>
+      <c r="G131" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E132" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F132" t="s">
+        <v>41</v>
+      </c>
+      <c r="G132" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F133" t="s">
+        <v>41</v>
+      </c>
+      <c r="G133" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E134" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F134" t="s">
+        <v>41</v>
+      </c>
+      <c r="G134" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F135" t="s">
+        <v>41</v>
+      </c>
+      <c r="G135" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E136" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F136" t="s">
+        <v>41</v>
+      </c>
+      <c r="G136" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F137" t="s">
+        <v>41</v>
+      </c>
+      <c r="G137" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F138" t="s">
+        <v>41</v>
+      </c>
+      <c r="G138" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F139" t="s">
+        <v>41</v>
+      </c>
+      <c r="G139" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F140" t="s">
+        <v>41</v>
+      </c>
+      <c r="G140" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F141" t="s">
+        <v>41</v>
+      </c>
+      <c r="G141" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F142" t="s">
+        <v>41</v>
+      </c>
+      <c r="G142" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F143" t="s">
+        <v>41</v>
+      </c>
+      <c r="G143" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F144" t="s">
+        <v>41</v>
+      </c>
+      <c r="G144" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B145" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="7" t="s">
+      <c r="C145" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D97" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F97" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B98" s="7" t="s">
+      <c r="D145" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F145" t="s">
+        <v>10</v>
+      </c>
+      <c r="G145" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C98" s="7" t="s">
+      <c r="C146" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D98" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B99" s="7" t="s">
+      <c r="D146" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F146" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B147" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C99" s="7" t="s">
+      <c r="C147" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D99" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B100" s="7" t="s">
+      <c r="D147" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F147" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B148" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C100" s="7" t="s">
+      <c r="C148" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D100" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F100" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
-      <c r="A101" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B101" s="7" t="s">
+      <c r="D148" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F148" t="s">
+        <v>10</v>
+      </c>
+      <c r="G148" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B149" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C149" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D101" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
-      <c r="A102" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B102" s="7" t="s">
+      <c r="D149" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149" t="s">
+        <v>10</v>
+      </c>
+      <c r="G149" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C102" s="7" t="s">
+      <c r="C150" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" t="s">
-        <v>10</v>
-      </c>
-      <c r="G102" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
-      <c r="A103" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B103" s="7" t="s">
+      <c r="D150" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C103" s="7" t="s">
+      <c r="C151" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D103" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" t="s">
-        <v>10</v>
-      </c>
-      <c r="G103" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
-      <c r="A104" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B104" s="7" t="s">
+      <c r="D151" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F151" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B152" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C104" s="7" t="s">
+      <c r="C152" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="D104" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F104" t="s">
-        <v>10</v>
-      </c>
-      <c r="G104" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B105" s="7" t="s">
+      <c r="D152" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F152" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B153" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C105" s="7" t="s">
+      <c r="C153" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D105" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F105" t="s">
-        <v>10</v>
-      </c>
-      <c r="G105" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
-      <c r="A106" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B106" s="7" t="s">
+      <c r="D153" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F153" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B154" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C154" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="D106" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F106" t="s">
-        <v>10</v>
-      </c>
-      <c r="G106" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B107" s="7" t="s">
+      <c r="D154" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154" t="s">
+        <v>10</v>
+      </c>
+      <c r="G154" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B155" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C107" s="7" t="s">
+      <c r="C155" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="D107" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F107" t="s">
-        <v>10</v>
-      </c>
-      <c r="G107" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
-      <c r="A108" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B108" s="7" t="s">
+      <c r="D155" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F155" t="s">
+        <v>10</v>
+      </c>
+      <c r="G155" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B156" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C108" s="7" t="s">
+      <c r="C156" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D108" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" t="s">
-        <v>10</v>
-      </c>
-      <c r="G108" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
-      <c r="A109" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B109" s="7" t="s">
+      <c r="D156" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F156" t="s">
+        <v>10</v>
+      </c>
+      <c r="G156" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C109" s="7" t="s">
+      <c r="C157" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D109" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109" t="s">
-        <v>10</v>
-      </c>
-      <c r="G109" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
-      <c r="A110" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B110" s="7" t="s">
+      <c r="D157" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F157" t="s">
+        <v>10</v>
+      </c>
+      <c r="G157" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B158" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C158" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D110" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" t="s">
-        <v>10</v>
-      </c>
-      <c r="G110" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
-      <c r="A111" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B111" s="7" t="s">
+      <c r="D158" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" t="s">
+        <v>10</v>
+      </c>
+      <c r="G158" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B159" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="C159" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="D111" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F111" t="s">
-        <v>10</v>
-      </c>
-      <c r="G111" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
-      <c r="A112" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B112" s="7" t="s">
+      <c r="D159" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F159" t="s">
+        <v>10</v>
+      </c>
+      <c r="G159" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B160" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C112" s="7" t="s">
+      <c r="C160" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D112" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E112" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F112" t="s">
-        <v>10</v>
-      </c>
-      <c r="G112" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
-      <c r="A113" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B113" s="7" t="s">
+      <c r="D160" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F160" t="s">
+        <v>10</v>
+      </c>
+      <c r="G160" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B161" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C113" s="7" t="s">
+      <c r="C161" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D113" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>10</v>
-      </c>
-      <c r="G113" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
-      <c r="A114" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B114" s="7" t="s">
+      <c r="D161" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F161" t="s">
+        <v>10</v>
+      </c>
+      <c r="G161" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B162" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C162" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D114" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E114" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F114" t="s">
-        <v>10</v>
-      </c>
-      <c r="G114" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
-      <c r="A115" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B115" s="7" t="s">
+      <c r="D162" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F162" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F163" t="s">
+        <v>41</v>
+      </c>
+      <c r="G163" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E164" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F164" t="s">
+        <v>41</v>
+      </c>
+      <c r="G164" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F165" t="s">
+        <v>41</v>
+      </c>
+      <c r="G165" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F166" t="s">
+        <v>41</v>
+      </c>
+      <c r="G166" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F167" t="s">
+        <v>41</v>
+      </c>
+      <c r="G167" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F168" t="s">
+        <v>41</v>
+      </c>
+      <c r="G168" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F169" t="s">
+        <v>41</v>
+      </c>
+      <c r="G169" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F170" t="s">
+        <v>41</v>
+      </c>
+      <c r="G170" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F171" t="s">
+        <v>41</v>
+      </c>
+      <c r="G171" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E172" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F172" t="s">
+        <v>41</v>
+      </c>
+      <c r="G172" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B173" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C115" s="7" t="s">
+      <c r="C173" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D115" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" t="s">
-        <v>10</v>
-      </c>
-      <c r="G115" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
-      <c r="A116" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B116" s="7" t="s">
+      <c r="D173" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F173" t="s">
+        <v>10</v>
+      </c>
+      <c r="G173" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F174" t="s">
+        <v>41</v>
+      </c>
+      <c r="G174" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B175" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C175" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" t="s">
-        <v>10</v>
-      </c>
-      <c r="G116" t="s">
-        <v>10</v>
+      <c r="D175" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E175" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" t="s">
+        <v>10</v>
+      </c>
+      <c r="G175" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E176" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F176" t="s">
+        <v>41</v>
+      </c>
+      <c r="G176" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F177" t="s">
+        <v>41</v>
+      </c>
+      <c r="G177" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E178" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F178" t="s">
+        <v>41</v>
+      </c>
+      <c r="G178" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F179" t="s">
+        <v>41</v>
+      </c>
+      <c r="G179" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <conditionalFormatting sqref="D36:E36">
+    <cfRule type="expression" dxfId="13" priority="31">
+      <formula>UPPER(#REF!)="YES"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="32">
+      <formula>UPPER(#REF!)="NO"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D4:G35 D92:G1954">
-    <cfRule type="expression" dxfId="9" priority="19">
+    <cfRule type="expression" dxfId="5" priority="19">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="20">
+    <cfRule type="expression" dxfId="4" priority="20">
       <formula>UPPER(B4)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D36:E36">
-    <cfRule type="expression" dxfId="7" priority="31">
-      <formula>UPPER(#REF!)="YES"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="32">
-      <formula>UPPER(#REF!)="NO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D37:G72">
-    <cfRule type="expression" dxfId="5" priority="11">
+  <conditionalFormatting sqref="D37:G91">
+    <cfRule type="expression" dxfId="11" priority="11">
       <formula>UPPER(B37)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="12">
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>UPPER(B37)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D73:G91">
-    <cfRule type="expression" dxfId="3" priority="25">
-      <formula>UPPER(B73)="YES"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="26">
-      <formula>UPPER(B73)="NO"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F36:G36">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>UPPER(D36)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>UPPER(D36)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4680,14 +6149,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.35" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V3_Admin_Board_User_Permissions_ADMIN_FILTER_BACK_FIXED\Dawiyat_PMO_Executive_Portal_V3_Admin_Board_User_Permissions\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V3_4_EXCEL_ONLY_PERMISSIONS_FIXED\Dawiyat_PMO_Executive_Portal_V3_Admin_Board_User_Permissions\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CC54EC-BD19-47C3-8643-6209517120B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DB6A26-2AB8-4E44-B33E-2D8EDC8C1E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="152">
   <si>
     <t>Users</t>
   </si>
@@ -510,7 +510,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -544,6 +544,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -557,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -574,53 +580,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFEE2E2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFDCFCE7"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1087,10 +1052,10 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:D501">
-    <cfRule type="expression" dxfId="17" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>UPPER(B4)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1338,7 +1303,7 @@
         <v>41</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="K7" t="s">
         <v>41</v>
@@ -1490,10 +1455,10 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:N501">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>UPPER(B4)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>UPPER(B4)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1511,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H179"/>
+  <dimension ref="A1:H267"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="18.796875" customWidth="1"/>
@@ -5538,7 +5503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:8">
       <c r="A177" s="5" t="s">
         <v>149</v>
       </c>
@@ -5561,7 +5526,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:8">
       <c r="A178" s="5" t="s">
         <v>149</v>
       </c>
@@ -5584,7 +5549,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:8">
       <c r="A179" s="5" t="s">
         <v>149</v>
       </c>
@@ -5606,16 +5571,2128 @@
       <c r="G179" t="s">
         <v>41</v>
       </c>
+    </row>
+    <row r="180" spans="1:8">
+      <c r="A180" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E180" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H180" s="8"/>
+    </row>
+    <row r="181" spans="1:8">
+      <c r="A181" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E181" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H181" s="8"/>
+    </row>
+    <row r="182" spans="1:8">
+      <c r="A182" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D182" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E182" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H182" s="8"/>
+    </row>
+    <row r="183" spans="1:8">
+      <c r="A183" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D183" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E183" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H183" s="8"/>
+    </row>
+    <row r="184" spans="1:8">
+      <c r="A184" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D184" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E184" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H184" s="8"/>
+    </row>
+    <row r="185" spans="1:8">
+      <c r="A185" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D185" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E185" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H185" s="8"/>
+    </row>
+    <row r="186" spans="1:8">
+      <c r="A186" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B186" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D186" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E186" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H186" s="8"/>
+    </row>
+    <row r="187" spans="1:8">
+      <c r="A187" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D187" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E187" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H187" s="8"/>
+    </row>
+    <row r="188" spans="1:8">
+      <c r="A188" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B188" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E188" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H188" s="8"/>
+    </row>
+    <row r="189" spans="1:8">
+      <c r="A189" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D189" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E189" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H189" s="8"/>
+    </row>
+    <row r="190" spans="1:8">
+      <c r="A190" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E190" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H190" s="8"/>
+    </row>
+    <row r="191" spans="1:8">
+      <c r="A191" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C191" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E191" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H191" s="8"/>
+    </row>
+    <row r="192" spans="1:8">
+      <c r="A192" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B192" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D192" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E192" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H192" s="8"/>
+    </row>
+    <row r="193" spans="1:8">
+      <c r="A193" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D193" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E193" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H193" s="8"/>
+    </row>
+    <row r="194" spans="1:8">
+      <c r="A194" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E194" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F194" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H194" s="8"/>
+    </row>
+    <row r="195" spans="1:8">
+      <c r="A195" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D195" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E195" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F195" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H195" s="8"/>
+    </row>
+    <row r="196" spans="1:8">
+      <c r="A196" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B196" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E196" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F196" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H196" s="8"/>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D197" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E197" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F197" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H197" s="8"/>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B198" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D198" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F198" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H198" s="8"/>
+    </row>
+    <row r="199" spans="1:8">
+      <c r="A199" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C199" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D199" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E199" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F199" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H199" s="8"/>
+    </row>
+    <row r="200" spans="1:8">
+      <c r="A200" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C200" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D200" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E200" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F200" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H200" s="8"/>
+    </row>
+    <row r="201" spans="1:8">
+      <c r="A201" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C201" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D201" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E201" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F201" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H201" s="8"/>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C202" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D202" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E202" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F202" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H202" s="8"/>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C203" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D203" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E203" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F203" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H203" s="8"/>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B204" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C204" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D204" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E204" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F204" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H204" s="8"/>
+    </row>
+    <row r="205" spans="1:8">
+      <c r="A205" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C205" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D205" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E205" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F205" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H205" s="8"/>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B206" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C206" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D206" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E206" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F206" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H206" s="8"/>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C207" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D207" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E207" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F207" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H207" s="8"/>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B208" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C208" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D208" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E208" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F208" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H208" s="8"/>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C209" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D209" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E209" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F209" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H209" s="8"/>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B210" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C210" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D210" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E210" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F210" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H210" s="8"/>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B211" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C211" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D211" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E211" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F211" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H211" s="8"/>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B212" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C212" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D212" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E212" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F212" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H212" s="8"/>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B213" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C213" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="D213" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E213" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F213" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H213" s="8"/>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B214" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C214" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D214" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E214" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F214" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H214" s="8"/>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C215" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D215" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E215" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F215" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H215" s="8"/>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C216" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D216" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E216" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F216" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H216" s="8"/>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C217" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D217" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E217" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F217" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H217" s="8"/>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B218" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C218" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D218" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E218" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F218" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H218" s="8"/>
+    </row>
+    <row r="219" spans="1:8">
+      <c r="A219" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C219" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D219" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E219" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F219" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H219" s="8"/>
+    </row>
+    <row r="220" spans="1:8">
+      <c r="A220" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B220" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C220" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D220" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E220" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F220" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H220" s="8"/>
+    </row>
+    <row r="221" spans="1:8">
+      <c r="A221" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C221" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D221" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E221" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F221" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G221" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H221" s="8"/>
+    </row>
+    <row r="222" spans="1:8">
+      <c r="A222" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B222" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C222" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D222" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E222" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F222" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H222" s="8"/>
+    </row>
+    <row r="223" spans="1:8">
+      <c r="A223" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C223" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D223" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E223" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F223" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H223" s="8"/>
+    </row>
+    <row r="224" spans="1:8">
+      <c r="A224" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B224" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C224" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D224" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E224" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F224" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G224" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H224" s="8"/>
+    </row>
+    <row r="225" spans="1:8">
+      <c r="A225" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B225" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C225" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D225" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E225" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F225" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G225" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H225" s="8"/>
+    </row>
+    <row r="226" spans="1:8">
+      <c r="A226" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B226" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C226" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D226" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E226" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F226" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H226" s="8"/>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B227" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C227" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D227" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E227" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F227" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H227" s="8"/>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B228" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C228" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D228" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E228" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F228" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H228" s="8"/>
+    </row>
+    <row r="229" spans="1:8">
+      <c r="A229" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C229" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D229" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E229" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F229" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H229" s="8"/>
+    </row>
+    <row r="230" spans="1:8">
+      <c r="A230" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B230" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C230" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D230" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E230" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F230" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H230" s="8"/>
+    </row>
+    <row r="231" spans="1:8">
+      <c r="A231" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B231" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C231" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D231" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E231" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F231" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G231" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H231" s="8"/>
+    </row>
+    <row r="232" spans="1:8">
+      <c r="A232" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B232" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C232" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D232" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E232" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F232" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H232" s="8"/>
+    </row>
+    <row r="233" spans="1:8">
+      <c r="A233" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B233" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C233" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D233" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E233" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F233" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H233" s="8"/>
+    </row>
+    <row r="234" spans="1:8">
+      <c r="A234" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B234" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C234" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D234" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E234" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F234" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H234" s="8"/>
+    </row>
+    <row r="235" spans="1:8">
+      <c r="A235" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B235" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C235" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D235" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E235" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F235" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G235" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H235" s="8"/>
+    </row>
+    <row r="236" spans="1:8">
+      <c r="A236" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B236" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C236" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D236" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E236" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F236" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H236" s="8"/>
+    </row>
+    <row r="237" spans="1:8">
+      <c r="A237" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B237" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C237" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D237" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E237" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F237" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G237" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H237" s="8"/>
+    </row>
+    <row r="238" spans="1:8">
+      <c r="A238" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B238" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C238" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D238" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E238" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F238" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H238" s="8"/>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C239" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D239" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E239" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F239" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G239" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H239" s="8"/>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C240" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D240" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E240" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F240" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H240" s="8"/>
+    </row>
+    <row r="241" spans="1:8">
+      <c r="A241" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B241" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C241" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D241" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E241" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F241" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H241" s="8"/>
+    </row>
+    <row r="242" spans="1:8">
+      <c r="A242" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B242" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C242" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="D242" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E242" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F242" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G242" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H242" s="8"/>
+    </row>
+    <row r="243" spans="1:8">
+      <c r="A243" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B243" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C243" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D243" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E243" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F243" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G243" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H243" s="8"/>
+    </row>
+    <row r="244" spans="1:8">
+      <c r="A244" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B244" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C244" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D244" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E244" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F244" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G244" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H244" s="8"/>
+    </row>
+    <row r="245" spans="1:8">
+      <c r="A245" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C245" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D245" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E245" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F245" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G245" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H245" s="8"/>
+    </row>
+    <row r="246" spans="1:8">
+      <c r="A246" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B246" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C246" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D246" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E246" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F246" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H246" s="8"/>
+    </row>
+    <row r="247" spans="1:8">
+      <c r="A247" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C247" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D247" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E247" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H247" s="8"/>
+    </row>
+    <row r="248" spans="1:8">
+      <c r="A248" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B248" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C248" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D248" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E248" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F248" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G248" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H248" s="8"/>
+    </row>
+    <row r="249" spans="1:8">
+      <c r="A249" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C249" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E249" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F249" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H249" s="8"/>
+    </row>
+    <row r="250" spans="1:8">
+      <c r="A250" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B250" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C250" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D250" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E250" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F250" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H250" s="8"/>
+    </row>
+    <row r="251" spans="1:8">
+      <c r="A251" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B251" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C251" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E251" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F251" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H251" s="8"/>
+    </row>
+    <row r="252" spans="1:8">
+      <c r="A252" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B252" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C252" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D252" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E252" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F252" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H252" s="8"/>
+    </row>
+    <row r="253" spans="1:8">
+      <c r="A253" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B253" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C253" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E253" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H253" s="8"/>
+    </row>
+    <row r="254" spans="1:8">
+      <c r="A254" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B254" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C254" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E254" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F254" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H254" s="8"/>
+    </row>
+    <row r="255" spans="1:8">
+      <c r="A255" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B255" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C255" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E255" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F255" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H255" s="8"/>
+    </row>
+    <row r="256" spans="1:8">
+      <c r="A256" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B256" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C256" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D256" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E256" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F256" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H256" s="8"/>
+    </row>
+    <row r="257" spans="1:8">
+      <c r="A257" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B257" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C257" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E257" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F257" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H257" s="8"/>
+    </row>
+    <row r="258" spans="1:8">
+      <c r="A258" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C258" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E258" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F258" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H258" s="8"/>
+    </row>
+    <row r="259" spans="1:8">
+      <c r="A259" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C259" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E259" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F259" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H259" s="8"/>
+    </row>
+    <row r="260" spans="1:8">
+      <c r="A260" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C260" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D260" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E260" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F260" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H260" s="8"/>
+    </row>
+    <row r="261" spans="1:8">
+      <c r="A261" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B261" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C261" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D261" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E261" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F261" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H261" s="8"/>
+    </row>
+    <row r="262" spans="1:8">
+      <c r="A262" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B262" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C262" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D262" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E262" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F262" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H262" s="8"/>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B263" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C263" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D263" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E263" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F263" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H263" s="8"/>
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B264" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C264" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E264" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F264" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H264" s="8"/>
+    </row>
+    <row r="265" spans="1:8">
+      <c r="A265" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B265" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C265" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D265" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E265" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F265" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H265" s="8"/>
+    </row>
+    <row r="266" spans="1:8">
+      <c r="A266" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C266" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E266" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F266" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H266" s="8"/>
+    </row>
+    <row r="267" spans="1:8">
+      <c r="A267" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C267" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E267" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F267" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H267" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <conditionalFormatting sqref="D36:E36">
-    <cfRule type="expression" dxfId="13" priority="31">
+    <cfRule type="expression" dxfId="7" priority="31">
       <formula>UPPER(#REF!)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="32">
+    <cfRule type="expression" dxfId="6" priority="32">
       <formula>UPPER(#REF!)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5628,18 +7705,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D37:G91">
-    <cfRule type="expression" dxfId="11" priority="11">
+    <cfRule type="expression" dxfId="3" priority="11">
       <formula>UPPER(B37)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="2" priority="12">
       <formula>UPPER(B37)="NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F36:G36">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>UPPER(D36)="YES"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>UPPER(D36)="NO"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V4_8_HIDDEN_ACTION_PAGES_FIXED\Dawiyat_PMO_Executive_Portal_V4_8_HIDDEN_ACTION_PAGES_FIXED\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5875D78-04D8-4CAD-B9B2-AC7F6B4EFEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B4F7BC-80C5-4748-BDCD-0AA7E2594218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2146" uniqueCount="153">
   <si>
     <t>Username</t>
   </si>
@@ -5617,7 +5617,7 @@
         <v>9</v>
       </c>
       <c r="F186" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G186" t="s">
         <v>9</v>
@@ -6652,7 +6652,7 @@
         <v>9</v>
       </c>
       <c r="F231" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G231" t="s">
         <v>9</v>
@@ -6675,7 +6675,7 @@
         <v>9</v>
       </c>
       <c r="F232" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G232" t="s">
         <v>9</v>
@@ -6698,7 +6698,7 @@
         <v>9</v>
       </c>
       <c r="F233" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G233" t="s">
         <v>9</v>
@@ -6721,7 +6721,7 @@
         <v>9</v>
       </c>
       <c r="F234" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G234" t="s">
         <v>9</v>
@@ -6744,7 +6744,7 @@
         <v>9</v>
       </c>
       <c r="F235" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G235" t="s">
         <v>9</v>
@@ -6767,7 +6767,7 @@
         <v>9</v>
       </c>
       <c r="F236" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G236" t="s">
         <v>9</v>
@@ -6790,7 +6790,7 @@
         <v>9</v>
       </c>
       <c r="F237" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G237" t="s">
         <v>9</v>
@@ -6813,7 +6813,7 @@
         <v>9</v>
       </c>
       <c r="F238" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G238" t="s">
         <v>9</v>
@@ -6836,7 +6836,7 @@
         <v>9</v>
       </c>
       <c r="F239" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G239" t="s">
         <v>9</v>
@@ -6859,7 +6859,7 @@
         <v>9</v>
       </c>
       <c r="F240" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G240" t="s">
         <v>9</v>
@@ -6882,7 +6882,7 @@
         <v>9</v>
       </c>
       <c r="F241" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G241" t="s">
         <v>9</v>
@@ -6905,7 +6905,7 @@
         <v>9</v>
       </c>
       <c r="F242" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G242" t="s">
         <v>9</v>
@@ -6928,7 +6928,7 @@
         <v>9</v>
       </c>
       <c r="F243" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G243" t="s">
         <v>9</v>
@@ -6951,7 +6951,7 @@
         <v>9</v>
       </c>
       <c r="F244" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G244" t="s">
         <v>9</v>
@@ -6974,7 +6974,7 @@
         <v>9</v>
       </c>
       <c r="F245" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G245" t="s">
         <v>9</v>
@@ -6997,7 +6997,7 @@
         <v>9</v>
       </c>
       <c r="F246" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G246" t="s">
         <v>9</v>
@@ -7020,7 +7020,7 @@
         <v>9</v>
       </c>
       <c r="F247" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G247" t="s">
         <v>9</v>
@@ -7043,7 +7043,7 @@
         <v>9</v>
       </c>
       <c r="F248" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G248" t="s">
         <v>9</v>
@@ -7342,7 +7342,7 @@
         <v>9</v>
       </c>
       <c r="F261" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G261" t="s">
         <v>9</v>
@@ -7447,7 +7447,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -7480,468 +7480,482 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>41</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C20" t="s">
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C21" t="s">
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C22" t="s">
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C23" t="s">
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C24" t="s">
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C25" t="s">
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C26" t="s">
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C27" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C27" t="s">
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C28" t="s">
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C29" t="s">
+    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C30" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C30" t="s">
+    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C31" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C31" t="s">
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C32" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="36" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C36" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C43" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C48" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C49" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
     </row>
     <row r="50" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C50" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C51" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C53" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C55" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C58" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C59" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C61" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="62" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C62" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="63" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C63" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="64" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C65" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C67" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
     </row>
     <row r="68" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C69" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C72" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C75" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="76" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C76" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="77" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="79" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C79" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="80" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C80" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="81" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C81" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="82" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="83" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C83" t="s">
-        <v>38</v>
+        <v>128</v>
       </c>
     </row>
     <row r="84" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C84" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C85" t="s">
         <v>129</v>
       </c>
     </row>
@@ -7952,7 +7966,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -7973,70 +7987,78 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="B8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>151</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>152</v>
       </c>
     </row>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V5_2_SELECTIVE_PDF_COMPONENT_EXPORT_FIXED\Dawiyat_PMO_Executive_Portal_V4_8_HIDDEN_ACTION_PAGES_FIXED\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\Dawiyat_PMO_Executive_Portal_V5_3_SELECTIVE_PDF_ENFORCEMENT_FIXED\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5D54EA-0345-47FA-B89E-1E184F4368BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215592CD-3288-422F-A2D4-F2B27717FEF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3428,7 +3428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -3451,7 +3451,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>12</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>12</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>12</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>12</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>12</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>12</v>
       </c>
@@ -3629,7 +3629,7 @@
         <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="G98" t="s">
         <v>9</v>
@@ -3727,7 +3727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>12</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>12</v>
       </c>
@@ -3773,7 +3773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>12</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>12</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>12</v>
       </c>
@@ -3842,7 +3842,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>12</v>
       </c>
@@ -3865,7 +3865,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>12</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>12</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>12</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>12</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>12</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>12</v>
       </c>
@@ -4003,7 +4003,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>12</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>12</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>12</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>12</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>12</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>12</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>12</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>12</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>12</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>12</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>12</v>
       </c>
@@ -4302,7 +4302,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>12</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>12</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>12</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>12</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>12</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>12</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>12</v>
       </c>
@@ -4463,7 +4463,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>12</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>12</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>12</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>12</v>
       </c>
@@ -4555,7 +4555,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>12</v>
       </c>
@@ -4578,7 +4578,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>12</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>12</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>12</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>12</v>
       </c>
@@ -4670,7 +4670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>12</v>
       </c>
@@ -4687,13 +4687,13 @@
         <v>9</v>
       </c>
       <c r="F144" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="G144" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>12</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>12</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>12</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>12</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>12</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>12</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>12</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>12</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>12</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>12</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>12</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>12</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>12</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>12</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>12</v>
       </c>
@@ -5038,7 +5038,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>12</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>12</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>12</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>12</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>12</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>12</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>12</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>12</v>
       </c>
@@ -5222,7 +5222,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>12</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>12</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>12</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>12</v>
       </c>
@@ -5337,7 +5337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>12</v>
       </c>
@@ -5360,7 +5360,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>12</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>12</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>12</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>12</v>
       </c>
@@ -7502,7 +7502,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>12</v>
       </c>
@@ -7663,11 +7663,6 @@
     <filterColumn colId="0">
       <filters>
         <filter val="Adham_Ismail"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Tables &amp; Exports"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6966255-B31B-4648-8DA6-956B3AF63D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06130B65-01A3-41FF-B159-6170E1D92A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -1217,6 +1217,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H357"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1251,7 +1252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1274,7 +1275,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1297,7 +1298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1320,7 +1321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1343,7 +1344,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1366,7 +1367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1389,7 +1390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1412,7 +1413,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1435,7 +1436,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1481,7 +1482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1504,7 +1505,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1527,7 +1528,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1550,7 +1551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1573,7 +1574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1596,7 +1597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1619,7 +1620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1642,7 +1643,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1665,7 +1666,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1688,7 +1689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1711,7 +1712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1734,7 +1735,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1757,7 +1758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1780,7 +1781,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1803,7 +1804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1826,7 +1827,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1849,7 +1850,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1872,7 +1873,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1895,7 +1896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1918,7 +1919,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1941,7 +1942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1964,7 +1965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1987,7 +1988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -2010,7 +2011,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2033,7 +2034,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2056,7 +2057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -2079,7 +2080,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2125,7 +2126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2148,7 +2149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2171,7 +2172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2194,7 +2195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2217,7 +2218,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -2240,7 +2241,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -2263,7 +2264,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -2286,7 +2287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -2309,7 +2310,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -2332,7 +2333,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2355,7 +2356,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2378,7 +2379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2401,7 +2402,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2424,7 +2425,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -2447,7 +2448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -2470,7 +2471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -2493,7 +2494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -2516,7 +2517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -2539,7 +2540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -2562,7 +2563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2585,7 +2586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -2608,7 +2609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -2631,7 +2632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -2654,7 +2655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -2677,7 +2678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -2700,7 +2701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -2723,7 +2724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -2746,7 +2747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -2769,7 +2770,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -2792,7 +2793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2815,7 +2816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -2884,7 +2885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -2907,7 +2908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -2930,7 +2931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -2953,7 +2954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2976,7 +2977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -2999,7 +3000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -3022,7 +3023,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -3045,7 +3046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -3068,7 +3069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -3091,7 +3092,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -3114,7 +3115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -3137,7 +3138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -3160,7 +3161,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -3183,7 +3184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -3206,7 +3207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -3229,7 +3230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -3252,7 +3253,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -3275,7 +3276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -3301,7 +3302,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>19</v>
       </c>
@@ -3324,7 +3325,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -3347,7 +3348,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>19</v>
       </c>
@@ -3370,7 +3371,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -3393,7 +3394,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>19</v>
       </c>
@@ -3416,7 +3417,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -3439,7 +3440,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -3462,7 +3463,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>19</v>
       </c>
@@ -3485,7 +3486,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -3508,7 +3509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -3531,7 +3532,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -3554,7 +3555,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -3577,7 +3578,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -3600,7 +3601,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -3623,7 +3624,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -3646,7 +3647,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>19</v>
       </c>
@@ -3669,7 +3670,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>19</v>
       </c>
@@ -3692,7 +3693,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -3715,7 +3716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>19</v>
       </c>
@@ -3738,7 +3739,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>19</v>
       </c>
@@ -3761,7 +3762,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>19</v>
       </c>
@@ -3784,7 +3785,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>19</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>19</v>
       </c>
@@ -3830,7 +3831,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -3853,7 +3854,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>19</v>
       </c>
@@ -3876,7 +3877,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>19</v>
       </c>
@@ -3899,7 +3900,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>19</v>
       </c>
@@ -3922,7 +3923,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>19</v>
       </c>
@@ -3945,7 +3946,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>19</v>
       </c>
@@ -3968,7 +3969,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>19</v>
       </c>
@@ -3991,7 +3992,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>19</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>19</v>
       </c>
@@ -4037,7 +4038,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -4060,7 +4061,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>19</v>
       </c>
@@ -4083,7 +4084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>19</v>
       </c>
@@ -4106,7 +4107,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>19</v>
       </c>
@@ -4129,7 +4130,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>19</v>
       </c>
@@ -4152,7 +4153,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>19</v>
       </c>
@@ -4175,7 +4176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>19</v>
       </c>
@@ -4198,7 +4199,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>19</v>
       </c>
@@ -4221,7 +4222,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>19</v>
       </c>
@@ -4244,7 +4245,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -4267,7 +4268,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -4290,7 +4291,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -4313,7 +4314,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -4336,7 +4337,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>19</v>
       </c>
@@ -4359,7 +4360,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>19</v>
       </c>
@@ -4382,7 +4383,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>19</v>
       </c>
@@ -4405,7 +4406,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>19</v>
       </c>
@@ -4428,7 +4429,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>19</v>
       </c>
@@ -4451,7 +4452,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -4474,7 +4475,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>19</v>
       </c>
@@ -4497,7 +4498,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>19</v>
       </c>
@@ -4520,7 +4521,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>19</v>
       </c>
@@ -4543,7 +4544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>19</v>
       </c>
@@ -4566,7 +4567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>19</v>
       </c>
@@ -4589,7 +4590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>19</v>
       </c>
@@ -4612,7 +4613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>19</v>
       </c>
@@ -4635,7 +4636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>19</v>
       </c>
@@ -4658,7 +4659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -4681,7 +4682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>19</v>
       </c>
@@ -4704,7 +4705,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>19</v>
       </c>
@@ -4727,7 +4728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -4750,7 +4751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>19</v>
       </c>
@@ -4773,7 +4774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>19</v>
       </c>
@@ -4796,7 +4797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>19</v>
       </c>
@@ -4819,7 +4820,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>19</v>
       </c>
@@ -4842,7 +4843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>19</v>
       </c>
@@ -4865,7 +4866,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>19</v>
       </c>
@@ -4888,7 +4889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>19</v>
       </c>
@@ -4911,7 +4912,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>19</v>
       </c>
@@ -4934,7 +4935,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>19</v>
       </c>
@@ -4957,7 +4958,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>19</v>
       </c>
@@ -4980,7 +4981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>19</v>
       </c>
@@ -5003,7 +5004,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>19</v>
       </c>
@@ -5026,7 +5027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>19</v>
       </c>
@@ -5049,7 +5050,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>19</v>
       </c>
@@ -5072,7 +5073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>19</v>
       </c>
@@ -5095,7 +5096,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>19</v>
       </c>
@@ -5118,7 +5119,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>19</v>
       </c>
@@ -5141,7 +5142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>19</v>
       </c>
@@ -5164,7 +5165,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>19</v>
       </c>
@@ -5187,7 +5188,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>19</v>
       </c>
@@ -5210,7 +5211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>19</v>
       </c>
@@ -5233,7 +5234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>19</v>
       </c>
@@ -5256,7 +5257,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>19</v>
       </c>
@@ -5279,7 +5280,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -5302,7 +5303,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>19</v>
       </c>
@@ -5325,7 +5326,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>19</v>
       </c>
@@ -5351,7 +5352,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>12</v>
       </c>
@@ -5374,7 +5375,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>12</v>
       </c>
@@ -5397,7 +5398,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>12</v>
       </c>
@@ -5420,7 +5421,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>12</v>
       </c>
@@ -5443,7 +5444,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>12</v>
       </c>
@@ -5466,7 +5467,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>12</v>
       </c>
@@ -5489,7 +5490,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -5512,7 +5513,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -5535,7 +5536,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>12</v>
       </c>
@@ -5558,7 +5559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>12</v>
       </c>
@@ -5581,7 +5582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>12</v>
       </c>
@@ -5604,7 +5605,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>12</v>
       </c>
@@ -5627,7 +5628,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>12</v>
       </c>
@@ -5650,7 +5651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>12</v>
       </c>
@@ -5673,7 +5674,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>12</v>
       </c>
@@ -5696,7 +5697,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>12</v>
       </c>
@@ -5719,7 +5720,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5742,7 +5743,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>12</v>
       </c>
@@ -5765,7 +5766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>12</v>
       </c>
@@ -5788,7 +5789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>12</v>
       </c>
@@ -5811,7 +5812,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>12</v>
       </c>
@@ -5834,7 +5835,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>12</v>
       </c>
@@ -5857,7 +5858,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>12</v>
       </c>
@@ -5880,7 +5881,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>12</v>
       </c>
@@ -5903,7 +5904,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>12</v>
       </c>
@@ -5926,7 +5927,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>12</v>
       </c>
@@ -5949,7 +5950,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5972,7 +5973,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>12</v>
       </c>
@@ -5995,7 +5996,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>12</v>
       </c>
@@ -6018,7 +6019,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>12</v>
       </c>
@@ -6041,7 +6042,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>12</v>
       </c>
@@ -6064,7 +6065,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>12</v>
       </c>
@@ -6087,7 +6088,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>12</v>
       </c>
@@ -6110,7 +6111,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>12</v>
       </c>
@@ -6133,7 +6134,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>12</v>
       </c>
@@ -6156,7 +6157,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>12</v>
       </c>
@@ -6179,7 +6180,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>12</v>
       </c>
@@ -6202,7 +6203,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>12</v>
       </c>
@@ -6225,7 +6226,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>12</v>
       </c>
@@ -6248,7 +6249,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>12</v>
       </c>
@@ -6271,7 +6272,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>12</v>
       </c>
@@ -6294,7 +6295,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>12</v>
       </c>
@@ -6317,7 +6318,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>12</v>
       </c>
@@ -6340,7 +6341,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>12</v>
       </c>
@@ -6363,7 +6364,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>12</v>
       </c>
@@ -6386,7 +6387,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>12</v>
       </c>
@@ -6409,7 +6410,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>12</v>
       </c>
@@ -6432,7 +6433,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>12</v>
       </c>
@@ -6455,7 +6456,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>12</v>
       </c>
@@ -6478,7 +6479,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>12</v>
       </c>
@@ -6501,7 +6502,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>12</v>
       </c>
@@ -6524,7 +6525,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>12</v>
       </c>
@@ -6547,7 +6548,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>12</v>
       </c>
@@ -6570,7 +6571,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>12</v>
       </c>
@@ -6593,7 +6594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>12</v>
       </c>
@@ -6616,7 +6617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>12</v>
       </c>
@@ -6639,7 +6640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>12</v>
       </c>
@@ -6662,7 +6663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>12</v>
       </c>
@@ -6685,7 +6686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>12</v>
       </c>
@@ -6708,7 +6709,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>12</v>
       </c>
@@ -6731,7 +6732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>12</v>
       </c>
@@ -6754,7 +6755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>12</v>
       </c>
@@ -6777,7 +6778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>12</v>
       </c>
@@ -6800,7 +6801,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>12</v>
       </c>
@@ -6823,7 +6824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>12</v>
       </c>
@@ -6846,7 +6847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>12</v>
       </c>
@@ -6869,7 +6870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>12</v>
       </c>
@@ -6892,7 +6893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>12</v>
       </c>
@@ -6915,7 +6916,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>12</v>
       </c>
@@ -6938,7 +6939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>12</v>
       </c>
@@ -6961,7 +6962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>12</v>
       </c>
@@ -6984,7 +6985,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>12</v>
       </c>
@@ -7007,7 +7008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>12</v>
       </c>
@@ -7030,7 +7031,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>12</v>
       </c>
@@ -7053,7 +7054,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>12</v>
       </c>
@@ -7076,7 +7077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>12</v>
       </c>
@@ -7099,7 +7100,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>12</v>
       </c>
@@ -7122,7 +7123,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>12</v>
       </c>
@@ -7145,7 +7146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>12</v>
       </c>
@@ -7168,7 +7169,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>12</v>
       </c>
@@ -7191,7 +7192,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>12</v>
       </c>
@@ -7214,7 +7215,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>12</v>
       </c>
@@ -7237,7 +7238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>12</v>
       </c>
@@ -7260,7 +7261,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>12</v>
       </c>
@@ -7283,7 +7284,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>12</v>
       </c>
@@ -7306,7 +7307,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>12</v>
       </c>
@@ -7329,7 +7330,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>12</v>
       </c>
@@ -7352,7 +7353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>12</v>
       </c>
@@ -7375,7 +7376,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>12</v>
       </c>
@@ -9452,7 +9453,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H357" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:H357" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Nada_Yehia"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06130B65-01A3-41FF-B159-6170E1D92A8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B4BAB7-EC01-467E-A003-2BB178B0FE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2807" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3450" uniqueCount="157">
   <si>
     <t>Username</t>
   </si>
@@ -480,6 +480,24 @@
   </si>
   <si>
     <t>Nada_Yehia</t>
+  </si>
+  <si>
+    <t>Mustafa</t>
+  </si>
+  <si>
+    <t>M_123$</t>
+  </si>
+  <si>
+    <t>Key Account Manager</t>
+  </si>
+  <si>
+    <t>Control Team</t>
+  </si>
+  <si>
+    <t>Invoicing &amp; Document Controller</t>
+  </si>
+  <si>
+    <t>Coordinator &amp; Heldorder Manager</t>
   </si>
 </sst>
 </file>
@@ -819,10 +837,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -879,7 +900,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -896,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -913,7 +934,7 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -930,7 +951,24 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" t="s">
         <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -1210,6 +1248,50 @@
         <v>35</v>
       </c>
     </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" t="s">
+        <v>35</v>
+      </c>
+      <c r="N7" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1217,8 +1299,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:H357"/>
+  <dimension ref="A1:H446"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" customWidth="1"/>
@@ -1252,7 +1333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1275,7 +1356,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1298,7 +1379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1321,7 +1402,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1344,7 +1425,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1367,7 +1448,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1390,7 +1471,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1413,7 +1494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1436,7 +1517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1459,7 +1540,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1482,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1505,7 +1586,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1528,7 +1609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1551,7 +1632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1574,7 +1655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1597,7 +1678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1620,7 +1701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1643,7 +1724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1666,7 +1747,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1689,7 +1770,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1712,7 +1793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1735,7 +1816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1758,7 +1839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1781,7 +1862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1804,7 +1885,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1827,7 +1908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1850,7 +1931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1873,7 +1954,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1896,7 +1977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1919,7 +2000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -1942,7 +2023,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -1965,7 +2046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -1988,7 +2069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -2011,7 +2092,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -2034,7 +2115,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -2057,7 +2138,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -2080,7 +2161,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -2103,7 +2184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -2126,7 +2207,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -2149,7 +2230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -2172,7 +2253,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -2195,7 +2276,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -2218,7 +2299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -2241,7 +2322,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -2264,7 +2345,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -2287,7 +2368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -2310,7 +2391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -2333,7 +2414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -2356,7 +2437,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -2379,7 +2460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -2402,7 +2483,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -2425,7 +2506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -2448,7 +2529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -2471,7 +2552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -2494,7 +2575,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -2517,7 +2598,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -2540,7 +2621,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -2563,7 +2644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -2586,7 +2667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -2609,7 +2690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -2632,7 +2713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -2655,7 +2736,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -2678,7 +2759,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -2701,7 +2782,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -2724,7 +2805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -2747,7 +2828,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -2770,7 +2851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -2793,7 +2874,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -2816,7 +2897,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -2839,7 +2920,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -2862,7 +2943,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -2885,7 +2966,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -2908,7 +2989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -2931,7 +3012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -2954,7 +3035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -2977,7 +3058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -3000,7 +3081,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -3023,7 +3104,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -3046,7 +3127,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -3069,7 +3150,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -3092,7 +3173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -3115,7 +3196,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -3138,7 +3219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -3161,7 +3242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -3184,7 +3265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -3207,7 +3288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -3230,7 +3311,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -3253,7 +3334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -3276,7 +3357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -3302,7 +3383,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>19</v>
       </c>
@@ -3325,7 +3406,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>19</v>
       </c>
@@ -3348,7 +3429,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>19</v>
       </c>
@@ -3371,7 +3452,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>19</v>
       </c>
@@ -3394,7 +3475,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>19</v>
       </c>
@@ -3417,7 +3498,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>19</v>
       </c>
@@ -3440,7 +3521,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>19</v>
       </c>
@@ -3463,7 +3544,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>19</v>
       </c>
@@ -3486,7 +3567,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>19</v>
       </c>
@@ -3509,7 +3590,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>19</v>
       </c>
@@ -3532,7 +3613,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>19</v>
       </c>
@@ -3555,7 +3636,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>19</v>
       </c>
@@ -3578,7 +3659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>19</v>
       </c>
@@ -3601,7 +3682,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>19</v>
       </c>
@@ -3624,7 +3705,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -3647,7 +3728,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>19</v>
       </c>
@@ -3670,7 +3751,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>19</v>
       </c>
@@ -3693,7 +3774,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>19</v>
       </c>
@@ -3716,7 +3797,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>19</v>
       </c>
@@ -3739,7 +3820,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>19</v>
       </c>
@@ -3762,7 +3843,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>19</v>
       </c>
@@ -3785,7 +3866,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>19</v>
       </c>
@@ -3808,7 +3889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>19</v>
       </c>
@@ -3831,7 +3912,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>19</v>
       </c>
@@ -3854,7 +3935,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>19</v>
       </c>
@@ -3877,7 +3958,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>19</v>
       </c>
@@ -3900,7 +3981,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>19</v>
       </c>
@@ -3923,7 +4004,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>19</v>
       </c>
@@ -3946,7 +4027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>19</v>
       </c>
@@ -3969,7 +4050,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>19</v>
       </c>
@@ -3992,7 +4073,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>19</v>
       </c>
@@ -4015,7 +4096,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>19</v>
       </c>
@@ -4038,7 +4119,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>19</v>
       </c>
@@ -4061,7 +4142,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>19</v>
       </c>
@@ -4084,7 +4165,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>19</v>
       </c>
@@ -4107,7 +4188,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>19</v>
       </c>
@@ -4130,7 +4211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>19</v>
       </c>
@@ -4153,7 +4234,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>19</v>
       </c>
@@ -4176,7 +4257,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>19</v>
       </c>
@@ -4199,7 +4280,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>19</v>
       </c>
@@ -4222,7 +4303,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>19</v>
       </c>
@@ -4245,7 +4326,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>19</v>
       </c>
@@ -4268,7 +4349,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>19</v>
       </c>
@@ -4291,7 +4372,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>19</v>
       </c>
@@ -4314,7 +4395,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>19</v>
       </c>
@@ -4337,7 +4418,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>19</v>
       </c>
@@ -4360,7 +4441,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>19</v>
       </c>
@@ -4383,7 +4464,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>19</v>
       </c>
@@ -4406,7 +4487,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>19</v>
       </c>
@@ -4429,7 +4510,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>19</v>
       </c>
@@ -4452,7 +4533,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -4475,7 +4556,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>19</v>
       </c>
@@ -4498,7 +4579,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>19</v>
       </c>
@@ -4521,7 +4602,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>19</v>
       </c>
@@ -4544,7 +4625,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>19</v>
       </c>
@@ -4567,7 +4648,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>19</v>
       </c>
@@ -4590,7 +4671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>19</v>
       </c>
@@ -4613,7 +4694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>19</v>
       </c>
@@ -4636,7 +4717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>19</v>
       </c>
@@ -4659,7 +4740,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>19</v>
       </c>
@@ -4682,7 +4763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>19</v>
       </c>
@@ -4705,7 +4786,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>19</v>
       </c>
@@ -4728,7 +4809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>19</v>
       </c>
@@ -4751,7 +4832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>19</v>
       </c>
@@ -4774,7 +4855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>19</v>
       </c>
@@ -4797,7 +4878,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>19</v>
       </c>
@@ -4820,7 +4901,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>19</v>
       </c>
@@ -4843,7 +4924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>19</v>
       </c>
@@ -4866,7 +4947,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>19</v>
       </c>
@@ -4889,7 +4970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>19</v>
       </c>
@@ -4912,7 +4993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>19</v>
       </c>
@@ -4935,7 +5016,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>19</v>
       </c>
@@ -4958,7 +5039,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>19</v>
       </c>
@@ -4981,7 +5062,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>19</v>
       </c>
@@ -5004,7 +5085,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>19</v>
       </c>
@@ -5027,7 +5108,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>19</v>
       </c>
@@ -5050,7 +5131,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>19</v>
       </c>
@@ -5073,7 +5154,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>19</v>
       </c>
@@ -5096,7 +5177,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>19</v>
       </c>
@@ -5119,7 +5200,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>19</v>
       </c>
@@ -5142,7 +5223,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>19</v>
       </c>
@@ -5165,7 +5246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>19</v>
       </c>
@@ -5188,7 +5269,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>19</v>
       </c>
@@ -5211,7 +5292,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>19</v>
       </c>
@@ -5234,7 +5315,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>19</v>
       </c>
@@ -5257,7 +5338,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>19</v>
       </c>
@@ -5280,7 +5361,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>19</v>
       </c>
@@ -5303,7 +5384,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>19</v>
       </c>
@@ -5326,7 +5407,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>19</v>
       </c>
@@ -5352,7 +5433,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>12</v>
       </c>
@@ -5375,7 +5456,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>12</v>
       </c>
@@ -5398,7 +5479,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>12</v>
       </c>
@@ -5421,7 +5502,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>12</v>
       </c>
@@ -5444,7 +5525,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>12</v>
       </c>
@@ -5467,7 +5548,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>12</v>
       </c>
@@ -5490,7 +5571,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>12</v>
       </c>
@@ -5513,7 +5594,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>12</v>
       </c>
@@ -5536,7 +5617,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>12</v>
       </c>
@@ -5559,7 +5640,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>12</v>
       </c>
@@ -5582,7 +5663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>12</v>
       </c>
@@ -5605,7 +5686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>12</v>
       </c>
@@ -5628,7 +5709,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>12</v>
       </c>
@@ -5651,7 +5732,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>12</v>
       </c>
@@ -5674,7 +5755,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>12</v>
       </c>
@@ -5697,7 +5778,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>12</v>
       </c>
@@ -5720,7 +5801,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>12</v>
       </c>
@@ -5743,7 +5824,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>12</v>
       </c>
@@ -5766,7 +5847,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>12</v>
       </c>
@@ -5789,7 +5870,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>12</v>
       </c>
@@ -5812,7 +5893,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>12</v>
       </c>
@@ -5835,7 +5916,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>12</v>
       </c>
@@ -5858,7 +5939,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>12</v>
       </c>
@@ -5881,7 +5962,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>12</v>
       </c>
@@ -5904,7 +5985,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>12</v>
       </c>
@@ -5927,7 +6008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>12</v>
       </c>
@@ -5950,7 +6031,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>12</v>
       </c>
@@ -5973,7 +6054,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>12</v>
       </c>
@@ -5996,7 +6077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>12</v>
       </c>
@@ -6019,7 +6100,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>12</v>
       </c>
@@ -6042,7 +6123,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>12</v>
       </c>
@@ -6065,7 +6146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>12</v>
       </c>
@@ -6088,7 +6169,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>12</v>
       </c>
@@ -6111,7 +6192,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>12</v>
       </c>
@@ -6134,7 +6215,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>12</v>
       </c>
@@ -6157,7 +6238,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>12</v>
       </c>
@@ -6180,7 +6261,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>12</v>
       </c>
@@ -6203,7 +6284,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>12</v>
       </c>
@@ -6226,7 +6307,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>12</v>
       </c>
@@ -6249,7 +6330,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>12</v>
       </c>
@@ -6272,7 +6353,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>12</v>
       </c>
@@ -6295,7 +6376,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>12</v>
       </c>
@@ -6318,7 +6399,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>12</v>
       </c>
@@ -6341,7 +6422,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>12</v>
       </c>
@@ -6364,7 +6445,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>12</v>
       </c>
@@ -6387,7 +6468,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>12</v>
       </c>
@@ -6410,7 +6491,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>12</v>
       </c>
@@ -6433,7 +6514,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>12</v>
       </c>
@@ -6456,7 +6537,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>12</v>
       </c>
@@ -6479,7 +6560,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>12</v>
       </c>
@@ -6502,7 +6583,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>12</v>
       </c>
@@ -6525,7 +6606,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>12</v>
       </c>
@@ -6548,7 +6629,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>12</v>
       </c>
@@ -6571,7 +6652,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>12</v>
       </c>
@@ -6594,7 +6675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>12</v>
       </c>
@@ -6617,7 +6698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>12</v>
       </c>
@@ -6640,7 +6721,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>12</v>
       </c>
@@ -6663,7 +6744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>12</v>
       </c>
@@ -6686,7 +6767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>12</v>
       </c>
@@ -6709,7 +6790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>12</v>
       </c>
@@ -6732,7 +6813,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>12</v>
       </c>
@@ -6755,7 +6836,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>12</v>
       </c>
@@ -6778,7 +6859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>12</v>
       </c>
@@ -6801,7 +6882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>12</v>
       </c>
@@ -6824,7 +6905,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>12</v>
       </c>
@@ -6847,7 +6928,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>12</v>
       </c>
@@ -6870,7 +6951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>12</v>
       </c>
@@ -6893,7 +6974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>12</v>
       </c>
@@ -6916,7 +6997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>12</v>
       </c>
@@ -6939,7 +7020,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>12</v>
       </c>
@@ -6962,7 +7043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>12</v>
       </c>
@@ -6985,7 +7066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>12</v>
       </c>
@@ -7008,7 +7089,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>12</v>
       </c>
@@ -7031,7 +7112,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>12</v>
       </c>
@@ -7054,7 +7135,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>12</v>
       </c>
@@ -7077,7 +7158,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>12</v>
       </c>
@@ -7100,7 +7181,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>12</v>
       </c>
@@ -7123,7 +7204,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>12</v>
       </c>
@@ -7146,7 +7227,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>12</v>
       </c>
@@ -7169,7 +7250,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>12</v>
       </c>
@@ -7192,7 +7273,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>12</v>
       </c>
@@ -7215,7 +7296,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>12</v>
       </c>
@@ -7238,7 +7319,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>12</v>
       </c>
@@ -7261,7 +7342,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>12</v>
       </c>
@@ -7284,7 +7365,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>12</v>
       </c>
@@ -7307,7 +7388,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>12</v>
       </c>
@@ -7330,7 +7411,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>12</v>
       </c>
@@ -7353,7 +7434,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>12</v>
       </c>
@@ -7376,7 +7457,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>12</v>
       </c>
@@ -9452,14 +9533,2057 @@
         <v>125</v>
       </c>
     </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A358" t="s">
+        <v>151</v>
+      </c>
+      <c r="B358" t="s">
+        <v>22</v>
+      </c>
+      <c r="C358" t="s">
+        <v>42</v>
+      </c>
+      <c r="D358" t="s">
+        <v>35</v>
+      </c>
+      <c r="E358" t="s">
+        <v>35</v>
+      </c>
+      <c r="F358" t="s">
+        <v>35</v>
+      </c>
+      <c r="G358" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A359" t="s">
+        <v>151</v>
+      </c>
+      <c r="B359" t="s">
+        <v>22</v>
+      </c>
+      <c r="C359" t="s">
+        <v>43</v>
+      </c>
+      <c r="D359" t="s">
+        <v>35</v>
+      </c>
+      <c r="E359" t="s">
+        <v>35</v>
+      </c>
+      <c r="F359" t="s">
+        <v>35</v>
+      </c>
+      <c r="G359" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A360" t="s">
+        <v>151</v>
+      </c>
+      <c r="B360" t="s">
+        <v>22</v>
+      </c>
+      <c r="C360" t="s">
+        <v>44</v>
+      </c>
+      <c r="D360" t="s">
+        <v>35</v>
+      </c>
+      <c r="E360" t="s">
+        <v>35</v>
+      </c>
+      <c r="F360" t="s">
+        <v>35</v>
+      </c>
+      <c r="G360" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A361" t="s">
+        <v>151</v>
+      </c>
+      <c r="B361" t="s">
+        <v>22</v>
+      </c>
+      <c r="C361" t="s">
+        <v>45</v>
+      </c>
+      <c r="D361" t="s">
+        <v>35</v>
+      </c>
+      <c r="E361" t="s">
+        <v>35</v>
+      </c>
+      <c r="F361" t="s">
+        <v>35</v>
+      </c>
+      <c r="G361" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A362" t="s">
+        <v>151</v>
+      </c>
+      <c r="B362" t="s">
+        <v>22</v>
+      </c>
+      <c r="C362" t="s">
+        <v>46</v>
+      </c>
+      <c r="D362" t="s">
+        <v>35</v>
+      </c>
+      <c r="E362" t="s">
+        <v>35</v>
+      </c>
+      <c r="F362" t="s">
+        <v>35</v>
+      </c>
+      <c r="G362" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A363" t="s">
+        <v>151</v>
+      </c>
+      <c r="B363" t="s">
+        <v>22</v>
+      </c>
+      <c r="C363" t="s">
+        <v>47</v>
+      </c>
+      <c r="D363" t="s">
+        <v>35</v>
+      </c>
+      <c r="E363" t="s">
+        <v>35</v>
+      </c>
+      <c r="F363" t="s">
+        <v>35</v>
+      </c>
+      <c r="G363" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A364" t="s">
+        <v>151</v>
+      </c>
+      <c r="B364" t="s">
+        <v>22</v>
+      </c>
+      <c r="C364" t="s">
+        <v>48</v>
+      </c>
+      <c r="D364" t="s">
+        <v>35</v>
+      </c>
+      <c r="E364" t="s">
+        <v>35</v>
+      </c>
+      <c r="F364" t="s">
+        <v>35</v>
+      </c>
+      <c r="G364" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A365" t="s">
+        <v>151</v>
+      </c>
+      <c r="B365" t="s">
+        <v>22</v>
+      </c>
+      <c r="C365" t="s">
+        <v>49</v>
+      </c>
+      <c r="D365" t="s">
+        <v>35</v>
+      </c>
+      <c r="E365" t="s">
+        <v>35</v>
+      </c>
+      <c r="F365" t="s">
+        <v>35</v>
+      </c>
+      <c r="G365" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>151</v>
+      </c>
+      <c r="B366" t="s">
+        <v>23</v>
+      </c>
+      <c r="C366" t="s">
+        <v>50</v>
+      </c>
+      <c r="D366" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366" t="s">
+        <v>9</v>
+      </c>
+      <c r="F366" t="s">
+        <v>35</v>
+      </c>
+      <c r="G366" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>151</v>
+      </c>
+      <c r="B367" t="s">
+        <v>23</v>
+      </c>
+      <c r="C367" t="s">
+        <v>51</v>
+      </c>
+      <c r="D367" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" t="s">
+        <v>9</v>
+      </c>
+      <c r="F367" t="s">
+        <v>35</v>
+      </c>
+      <c r="G367" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>151</v>
+      </c>
+      <c r="B368" t="s">
+        <v>23</v>
+      </c>
+      <c r="C368" t="s">
+        <v>52</v>
+      </c>
+      <c r="D368" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" t="s">
+        <v>9</v>
+      </c>
+      <c r="F368" t="s">
+        <v>35</v>
+      </c>
+      <c r="G368" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>151</v>
+      </c>
+      <c r="B369" t="s">
+        <v>23</v>
+      </c>
+      <c r="C369" t="s">
+        <v>53</v>
+      </c>
+      <c r="D369" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" t="s">
+        <v>9</v>
+      </c>
+      <c r="F369" t="s">
+        <v>35</v>
+      </c>
+      <c r="G369" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>151</v>
+      </c>
+      <c r="B370" t="s">
+        <v>23</v>
+      </c>
+      <c r="C370" t="s">
+        <v>54</v>
+      </c>
+      <c r="D370" t="s">
+        <v>9</v>
+      </c>
+      <c r="E370" t="s">
+        <v>9</v>
+      </c>
+      <c r="F370" t="s">
+        <v>35</v>
+      </c>
+      <c r="G370" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>151</v>
+      </c>
+      <c r="B371" t="s">
+        <v>24</v>
+      </c>
+      <c r="C371" t="s">
+        <v>55</v>
+      </c>
+      <c r="D371" t="s">
+        <v>35</v>
+      </c>
+      <c r="E371" t="s">
+        <v>35</v>
+      </c>
+      <c r="F371" t="s">
+        <v>35</v>
+      </c>
+      <c r="G371" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>151</v>
+      </c>
+      <c r="B372" t="s">
+        <v>24</v>
+      </c>
+      <c r="C372" t="s">
+        <v>56</v>
+      </c>
+      <c r="D372" t="s">
+        <v>35</v>
+      </c>
+      <c r="E372" t="s">
+        <v>35</v>
+      </c>
+      <c r="F372" t="s">
+        <v>35</v>
+      </c>
+      <c r="G372" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>151</v>
+      </c>
+      <c r="B373" t="s">
+        <v>24</v>
+      </c>
+      <c r="C373" t="s">
+        <v>57</v>
+      </c>
+      <c r="D373" t="s">
+        <v>35</v>
+      </c>
+      <c r="E373" t="s">
+        <v>35</v>
+      </c>
+      <c r="F373" t="s">
+        <v>35</v>
+      </c>
+      <c r="G373" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>151</v>
+      </c>
+      <c r="B374" t="s">
+        <v>24</v>
+      </c>
+      <c r="C374" t="s">
+        <v>58</v>
+      </c>
+      <c r="D374" t="s">
+        <v>35</v>
+      </c>
+      <c r="E374" t="s">
+        <v>35</v>
+      </c>
+      <c r="F374" t="s">
+        <v>35</v>
+      </c>
+      <c r="G374" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>151</v>
+      </c>
+      <c r="B375" t="s">
+        <v>24</v>
+      </c>
+      <c r="C375" t="s">
+        <v>59</v>
+      </c>
+      <c r="D375" t="s">
+        <v>35</v>
+      </c>
+      <c r="E375" t="s">
+        <v>35</v>
+      </c>
+      <c r="F375" t="s">
+        <v>35</v>
+      </c>
+      <c r="G375" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>151</v>
+      </c>
+      <c r="B376" t="s">
+        <v>24</v>
+      </c>
+      <c r="C376" t="s">
+        <v>60</v>
+      </c>
+      <c r="D376" t="s">
+        <v>35</v>
+      </c>
+      <c r="E376" t="s">
+        <v>35</v>
+      </c>
+      <c r="F376" t="s">
+        <v>35</v>
+      </c>
+      <c r="G376" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>151</v>
+      </c>
+      <c r="B377" t="s">
+        <v>24</v>
+      </c>
+      <c r="C377" t="s">
+        <v>61</v>
+      </c>
+      <c r="D377" t="s">
+        <v>35</v>
+      </c>
+      <c r="E377" t="s">
+        <v>35</v>
+      </c>
+      <c r="F377" t="s">
+        <v>35</v>
+      </c>
+      <c r="G377" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>151</v>
+      </c>
+      <c r="B378" t="s">
+        <v>24</v>
+      </c>
+      <c r="C378" t="s">
+        <v>62</v>
+      </c>
+      <c r="D378" t="s">
+        <v>35</v>
+      </c>
+      <c r="E378" t="s">
+        <v>35</v>
+      </c>
+      <c r="F378" t="s">
+        <v>35</v>
+      </c>
+      <c r="G378" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>151</v>
+      </c>
+      <c r="B379" t="s">
+        <v>25</v>
+      </c>
+      <c r="C379" t="s">
+        <v>49</v>
+      </c>
+      <c r="D379" t="s">
+        <v>35</v>
+      </c>
+      <c r="E379" t="s">
+        <v>35</v>
+      </c>
+      <c r="F379" t="s">
+        <v>35</v>
+      </c>
+      <c r="G379" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A380" t="s">
+        <v>151</v>
+      </c>
+      <c r="B380" t="s">
+        <v>25</v>
+      </c>
+      <c r="C380" t="s">
+        <v>63</v>
+      </c>
+      <c r="D380" t="s">
+        <v>35</v>
+      </c>
+      <c r="E380" t="s">
+        <v>35</v>
+      </c>
+      <c r="F380" t="s">
+        <v>35</v>
+      </c>
+      <c r="G380" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A381" t="s">
+        <v>151</v>
+      </c>
+      <c r="B381" t="s">
+        <v>25</v>
+      </c>
+      <c r="C381" t="s">
+        <v>64</v>
+      </c>
+      <c r="D381" t="s">
+        <v>35</v>
+      </c>
+      <c r="E381" t="s">
+        <v>35</v>
+      </c>
+      <c r="F381" t="s">
+        <v>35</v>
+      </c>
+      <c r="G381" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A382" t="s">
+        <v>151</v>
+      </c>
+      <c r="B382" t="s">
+        <v>25</v>
+      </c>
+      <c r="C382" t="s">
+        <v>48</v>
+      </c>
+      <c r="D382" t="s">
+        <v>35</v>
+      </c>
+      <c r="E382" t="s">
+        <v>35</v>
+      </c>
+      <c r="F382" t="s">
+        <v>35</v>
+      </c>
+      <c r="G382" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A383" t="s">
+        <v>151</v>
+      </c>
+      <c r="B383" t="s">
+        <v>25</v>
+      </c>
+      <c r="C383" t="s">
+        <v>65</v>
+      </c>
+      <c r="D383" t="s">
+        <v>35</v>
+      </c>
+      <c r="E383" t="s">
+        <v>35</v>
+      </c>
+      <c r="F383" t="s">
+        <v>35</v>
+      </c>
+      <c r="G383" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A384" t="s">
+        <v>151</v>
+      </c>
+      <c r="B384" t="s">
+        <v>25</v>
+      </c>
+      <c r="C384" t="s">
+        <v>66</v>
+      </c>
+      <c r="D384" t="s">
+        <v>35</v>
+      </c>
+      <c r="E384" t="s">
+        <v>35</v>
+      </c>
+      <c r="F384" t="s">
+        <v>35</v>
+      </c>
+      <c r="G384" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A385" t="s">
+        <v>151</v>
+      </c>
+      <c r="B385" t="s">
+        <v>25</v>
+      </c>
+      <c r="C385" t="s">
+        <v>67</v>
+      </c>
+      <c r="D385" t="s">
+        <v>35</v>
+      </c>
+      <c r="E385" t="s">
+        <v>35</v>
+      </c>
+      <c r="F385" t="s">
+        <v>35</v>
+      </c>
+      <c r="G385" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A386" t="s">
+        <v>151</v>
+      </c>
+      <c r="B386" t="s">
+        <v>25</v>
+      </c>
+      <c r="C386" t="s">
+        <v>68</v>
+      </c>
+      <c r="D386" t="s">
+        <v>35</v>
+      </c>
+      <c r="E386" t="s">
+        <v>35</v>
+      </c>
+      <c r="F386" t="s">
+        <v>35</v>
+      </c>
+      <c r="G386" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A387" t="s">
+        <v>151</v>
+      </c>
+      <c r="B387" t="s">
+        <v>25</v>
+      </c>
+      <c r="C387" t="s">
+        <v>69</v>
+      </c>
+      <c r="D387" t="s">
+        <v>35</v>
+      </c>
+      <c r="E387" t="s">
+        <v>35</v>
+      </c>
+      <c r="F387" t="s">
+        <v>35</v>
+      </c>
+      <c r="G387" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A388" t="s">
+        <v>151</v>
+      </c>
+      <c r="B388" t="s">
+        <v>25</v>
+      </c>
+      <c r="C388" t="s">
+        <v>70</v>
+      </c>
+      <c r="D388" t="s">
+        <v>35</v>
+      </c>
+      <c r="E388" t="s">
+        <v>35</v>
+      </c>
+      <c r="F388" t="s">
+        <v>35</v>
+      </c>
+      <c r="G388" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A389" t="s">
+        <v>151</v>
+      </c>
+      <c r="B389" t="s">
+        <v>26</v>
+      </c>
+      <c r="C389" t="s">
+        <v>71</v>
+      </c>
+      <c r="D389" t="s">
+        <v>35</v>
+      </c>
+      <c r="E389" t="s">
+        <v>35</v>
+      </c>
+      <c r="F389" t="s">
+        <v>35</v>
+      </c>
+      <c r="G389" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A390" t="s">
+        <v>151</v>
+      </c>
+      <c r="B390" t="s">
+        <v>26</v>
+      </c>
+      <c r="C390" t="s">
+        <v>72</v>
+      </c>
+      <c r="D390" t="s">
+        <v>35</v>
+      </c>
+      <c r="E390" t="s">
+        <v>35</v>
+      </c>
+      <c r="F390" t="s">
+        <v>35</v>
+      </c>
+      <c r="G390" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A391" t="s">
+        <v>151</v>
+      </c>
+      <c r="B391" t="s">
+        <v>26</v>
+      </c>
+      <c r="C391" t="s">
+        <v>73</v>
+      </c>
+      <c r="D391" t="s">
+        <v>35</v>
+      </c>
+      <c r="E391" t="s">
+        <v>35</v>
+      </c>
+      <c r="F391" t="s">
+        <v>35</v>
+      </c>
+      <c r="G391" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A392" t="s">
+        <v>151</v>
+      </c>
+      <c r="B392" t="s">
+        <v>26</v>
+      </c>
+      <c r="C392" t="s">
+        <v>74</v>
+      </c>
+      <c r="D392" t="s">
+        <v>35</v>
+      </c>
+      <c r="E392" t="s">
+        <v>35</v>
+      </c>
+      <c r="F392" t="s">
+        <v>35</v>
+      </c>
+      <c r="G392" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A393" t="s">
+        <v>151</v>
+      </c>
+      <c r="B393" t="s">
+        <v>26</v>
+      </c>
+      <c r="C393" t="s">
+        <v>75</v>
+      </c>
+      <c r="D393" t="s">
+        <v>35</v>
+      </c>
+      <c r="E393" t="s">
+        <v>35</v>
+      </c>
+      <c r="F393" t="s">
+        <v>35</v>
+      </c>
+      <c r="G393" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A394" t="s">
+        <v>151</v>
+      </c>
+      <c r="B394" t="s">
+        <v>26</v>
+      </c>
+      <c r="C394" t="s">
+        <v>76</v>
+      </c>
+      <c r="D394" t="s">
+        <v>35</v>
+      </c>
+      <c r="E394" t="s">
+        <v>35</v>
+      </c>
+      <c r="F394" t="s">
+        <v>35</v>
+      </c>
+      <c r="G394" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A395" t="s">
+        <v>151</v>
+      </c>
+      <c r="B395" t="s">
+        <v>26</v>
+      </c>
+      <c r="C395" t="s">
+        <v>77</v>
+      </c>
+      <c r="D395" t="s">
+        <v>35</v>
+      </c>
+      <c r="E395" t="s">
+        <v>35</v>
+      </c>
+      <c r="F395" t="s">
+        <v>35</v>
+      </c>
+      <c r="G395" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A396" t="s">
+        <v>151</v>
+      </c>
+      <c r="B396" t="s">
+        <v>26</v>
+      </c>
+      <c r="C396" t="s">
+        <v>78</v>
+      </c>
+      <c r="D396" t="s">
+        <v>35</v>
+      </c>
+      <c r="E396" t="s">
+        <v>35</v>
+      </c>
+      <c r="F396" t="s">
+        <v>35</v>
+      </c>
+      <c r="G396" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A397" t="s">
+        <v>151</v>
+      </c>
+      <c r="B397" t="s">
+        <v>26</v>
+      </c>
+      <c r="C397" t="s">
+        <v>79</v>
+      </c>
+      <c r="D397" t="s">
+        <v>35</v>
+      </c>
+      <c r="E397" t="s">
+        <v>35</v>
+      </c>
+      <c r="F397" t="s">
+        <v>35</v>
+      </c>
+      <c r="G397" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A398" t="s">
+        <v>151</v>
+      </c>
+      <c r="B398" t="s">
+        <v>26</v>
+      </c>
+      <c r="C398" t="s">
+        <v>80</v>
+      </c>
+      <c r="D398" t="s">
+        <v>35</v>
+      </c>
+      <c r="E398" t="s">
+        <v>35</v>
+      </c>
+      <c r="F398" t="s">
+        <v>35</v>
+      </c>
+      <c r="G398" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A399" t="s">
+        <v>151</v>
+      </c>
+      <c r="B399" t="s">
+        <v>26</v>
+      </c>
+      <c r="C399" t="s">
+        <v>81</v>
+      </c>
+      <c r="D399" t="s">
+        <v>35</v>
+      </c>
+      <c r="E399" t="s">
+        <v>35</v>
+      </c>
+      <c r="F399" t="s">
+        <v>35</v>
+      </c>
+      <c r="G399" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A400" t="s">
+        <v>151</v>
+      </c>
+      <c r="B400" t="s">
+        <v>26</v>
+      </c>
+      <c r="C400" t="s">
+        <v>82</v>
+      </c>
+      <c r="D400" t="s">
+        <v>35</v>
+      </c>
+      <c r="E400" t="s">
+        <v>35</v>
+      </c>
+      <c r="F400" t="s">
+        <v>35</v>
+      </c>
+      <c r="G400" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A401" t="s">
+        <v>151</v>
+      </c>
+      <c r="B401" t="s">
+        <v>26</v>
+      </c>
+      <c r="C401" t="s">
+        <v>83</v>
+      </c>
+      <c r="D401" t="s">
+        <v>35</v>
+      </c>
+      <c r="E401" t="s">
+        <v>35</v>
+      </c>
+      <c r="F401" t="s">
+        <v>35</v>
+      </c>
+      <c r="G401" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A402" t="s">
+        <v>151</v>
+      </c>
+      <c r="B402" t="s">
+        <v>27</v>
+      </c>
+      <c r="C402" t="s">
+        <v>84</v>
+      </c>
+      <c r="D402" t="s">
+        <v>35</v>
+      </c>
+      <c r="E402" t="s">
+        <v>35</v>
+      </c>
+      <c r="F402" t="s">
+        <v>35</v>
+      </c>
+      <c r="G402" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A403" t="s">
+        <v>151</v>
+      </c>
+      <c r="B403" t="s">
+        <v>27</v>
+      </c>
+      <c r="C403" t="s">
+        <v>85</v>
+      </c>
+      <c r="D403" t="s">
+        <v>35</v>
+      </c>
+      <c r="E403" t="s">
+        <v>35</v>
+      </c>
+      <c r="F403" t="s">
+        <v>35</v>
+      </c>
+      <c r="G403" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="404" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A404" t="s">
+        <v>151</v>
+      </c>
+      <c r="B404" t="s">
+        <v>27</v>
+      </c>
+      <c r="C404" t="s">
+        <v>86</v>
+      </c>
+      <c r="D404" t="s">
+        <v>35</v>
+      </c>
+      <c r="E404" t="s">
+        <v>35</v>
+      </c>
+      <c r="F404" t="s">
+        <v>35</v>
+      </c>
+      <c r="G404" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A405" t="s">
+        <v>151</v>
+      </c>
+      <c r="B405" t="s">
+        <v>27</v>
+      </c>
+      <c r="C405" t="s">
+        <v>87</v>
+      </c>
+      <c r="D405" t="s">
+        <v>35</v>
+      </c>
+      <c r="E405" t="s">
+        <v>35</v>
+      </c>
+      <c r="F405" t="s">
+        <v>35</v>
+      </c>
+      <c r="G405" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A406" t="s">
+        <v>151</v>
+      </c>
+      <c r="B406" t="s">
+        <v>27</v>
+      </c>
+      <c r="C406" t="s">
+        <v>88</v>
+      </c>
+      <c r="D406" t="s">
+        <v>35</v>
+      </c>
+      <c r="E406" t="s">
+        <v>35</v>
+      </c>
+      <c r="F406" t="s">
+        <v>35</v>
+      </c>
+      <c r="G406" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="407" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A407" t="s">
+        <v>151</v>
+      </c>
+      <c r="B407" t="s">
+        <v>27</v>
+      </c>
+      <c r="C407" t="s">
+        <v>89</v>
+      </c>
+      <c r="D407" t="s">
+        <v>35</v>
+      </c>
+      <c r="E407" t="s">
+        <v>35</v>
+      </c>
+      <c r="F407" t="s">
+        <v>35</v>
+      </c>
+      <c r="G407" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A408" t="s">
+        <v>151</v>
+      </c>
+      <c r="B408" t="s">
+        <v>27</v>
+      </c>
+      <c r="C408" t="s">
+        <v>90</v>
+      </c>
+      <c r="D408" t="s">
+        <v>35</v>
+      </c>
+      <c r="E408" t="s">
+        <v>35</v>
+      </c>
+      <c r="F408" t="s">
+        <v>35</v>
+      </c>
+      <c r="G408" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A409" t="s">
+        <v>151</v>
+      </c>
+      <c r="B409" t="s">
+        <v>27</v>
+      </c>
+      <c r="C409" t="s">
+        <v>91</v>
+      </c>
+      <c r="D409" t="s">
+        <v>35</v>
+      </c>
+      <c r="E409" t="s">
+        <v>35</v>
+      </c>
+      <c r="F409" t="s">
+        <v>35</v>
+      </c>
+      <c r="G409" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A410" t="s">
+        <v>151</v>
+      </c>
+      <c r="B410" t="s">
+        <v>27</v>
+      </c>
+      <c r="C410" t="s">
+        <v>92</v>
+      </c>
+      <c r="D410" t="s">
+        <v>35</v>
+      </c>
+      <c r="E410" t="s">
+        <v>35</v>
+      </c>
+      <c r="F410" t="s">
+        <v>35</v>
+      </c>
+      <c r="G410" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="411" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A411" t="s">
+        <v>151</v>
+      </c>
+      <c r="B411" t="s">
+        <v>28</v>
+      </c>
+      <c r="C411" t="s">
+        <v>93</v>
+      </c>
+      <c r="D411" t="s">
+        <v>9</v>
+      </c>
+      <c r="E411" t="s">
+        <v>9</v>
+      </c>
+      <c r="F411" t="s">
+        <v>35</v>
+      </c>
+      <c r="G411" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A412" t="s">
+        <v>151</v>
+      </c>
+      <c r="B412" t="s">
+        <v>28</v>
+      </c>
+      <c r="C412" t="s">
+        <v>94</v>
+      </c>
+      <c r="D412" t="s">
+        <v>9</v>
+      </c>
+      <c r="E412" t="s">
+        <v>9</v>
+      </c>
+      <c r="F412" t="s">
+        <v>35</v>
+      </c>
+      <c r="G412" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A413" t="s">
+        <v>151</v>
+      </c>
+      <c r="B413" t="s">
+        <v>28</v>
+      </c>
+      <c r="C413" t="s">
+        <v>95</v>
+      </c>
+      <c r="D413" t="s">
+        <v>9</v>
+      </c>
+      <c r="E413" t="s">
+        <v>9</v>
+      </c>
+      <c r="F413" t="s">
+        <v>35</v>
+      </c>
+      <c r="G413" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="414" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A414" t="s">
+        <v>151</v>
+      </c>
+      <c r="B414" t="s">
+        <v>28</v>
+      </c>
+      <c r="C414" t="s">
+        <v>42</v>
+      </c>
+      <c r="D414" t="s">
+        <v>9</v>
+      </c>
+      <c r="E414" t="s">
+        <v>9</v>
+      </c>
+      <c r="F414" t="s">
+        <v>35</v>
+      </c>
+      <c r="G414" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A415" t="s">
+        <v>151</v>
+      </c>
+      <c r="B415" t="s">
+        <v>28</v>
+      </c>
+      <c r="C415" t="s">
+        <v>96</v>
+      </c>
+      <c r="D415" t="s">
+        <v>9</v>
+      </c>
+      <c r="E415" t="s">
+        <v>9</v>
+      </c>
+      <c r="F415" t="s">
+        <v>35</v>
+      </c>
+      <c r="G415" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A416" t="s">
+        <v>151</v>
+      </c>
+      <c r="B416" t="s">
+        <v>28</v>
+      </c>
+      <c r="C416" t="s">
+        <v>56</v>
+      </c>
+      <c r="D416" t="s">
+        <v>9</v>
+      </c>
+      <c r="E416" t="s">
+        <v>9</v>
+      </c>
+      <c r="F416" t="s">
+        <v>35</v>
+      </c>
+      <c r="G416" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="417" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A417" t="s">
+        <v>151</v>
+      </c>
+      <c r="B417" t="s">
+        <v>28</v>
+      </c>
+      <c r="C417" t="s">
+        <v>97</v>
+      </c>
+      <c r="D417" t="s">
+        <v>9</v>
+      </c>
+      <c r="E417" t="s">
+        <v>9</v>
+      </c>
+      <c r="F417" t="s">
+        <v>35</v>
+      </c>
+      <c r="G417" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A418" t="s">
+        <v>151</v>
+      </c>
+      <c r="B418" t="s">
+        <v>28</v>
+      </c>
+      <c r="C418" t="s">
+        <v>58</v>
+      </c>
+      <c r="D418" t="s">
+        <v>9</v>
+      </c>
+      <c r="E418" t="s">
+        <v>9</v>
+      </c>
+      <c r="F418" t="s">
+        <v>35</v>
+      </c>
+      <c r="G418" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A419" t="s">
+        <v>151</v>
+      </c>
+      <c r="B419" t="s">
+        <v>28</v>
+      </c>
+      <c r="C419" t="s">
+        <v>98</v>
+      </c>
+      <c r="D419" t="s">
+        <v>9</v>
+      </c>
+      <c r="E419" t="s">
+        <v>9</v>
+      </c>
+      <c r="F419" t="s">
+        <v>35</v>
+      </c>
+      <c r="G419" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="420" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A420" t="s">
+        <v>151</v>
+      </c>
+      <c r="B420" t="s">
+        <v>28</v>
+      </c>
+      <c r="C420" t="s">
+        <v>99</v>
+      </c>
+      <c r="D420" t="s">
+        <v>9</v>
+      </c>
+      <c r="E420" t="s">
+        <v>9</v>
+      </c>
+      <c r="F420" t="s">
+        <v>35</v>
+      </c>
+      <c r="G420" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="421" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A421" t="s">
+        <v>151</v>
+      </c>
+      <c r="B421" t="s">
+        <v>28</v>
+      </c>
+      <c r="C421" t="s">
+        <v>100</v>
+      </c>
+      <c r="D421" t="s">
+        <v>9</v>
+      </c>
+      <c r="E421" t="s">
+        <v>9</v>
+      </c>
+      <c r="F421" t="s">
+        <v>35</v>
+      </c>
+      <c r="G421" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A422" t="s">
+        <v>151</v>
+      </c>
+      <c r="B422" t="s">
+        <v>28</v>
+      </c>
+      <c r="C422" t="s">
+        <v>101</v>
+      </c>
+      <c r="D422" t="s">
+        <v>9</v>
+      </c>
+      <c r="E422" t="s">
+        <v>9</v>
+      </c>
+      <c r="F422" t="s">
+        <v>35</v>
+      </c>
+      <c r="G422" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A423" t="s">
+        <v>151</v>
+      </c>
+      <c r="B423" t="s">
+        <v>28</v>
+      </c>
+      <c r="C423" t="s">
+        <v>102</v>
+      </c>
+      <c r="D423" t="s">
+        <v>9</v>
+      </c>
+      <c r="E423" t="s">
+        <v>9</v>
+      </c>
+      <c r="F423" t="s">
+        <v>35</v>
+      </c>
+      <c r="G423" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A424" t="s">
+        <v>151</v>
+      </c>
+      <c r="B424" t="s">
+        <v>28</v>
+      </c>
+      <c r="C424" t="s">
+        <v>103</v>
+      </c>
+      <c r="D424" t="s">
+        <v>9</v>
+      </c>
+      <c r="E424" t="s">
+        <v>9</v>
+      </c>
+      <c r="F424" t="s">
+        <v>35</v>
+      </c>
+      <c r="G424" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="425" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A425" t="s">
+        <v>151</v>
+      </c>
+      <c r="B425" t="s">
+        <v>28</v>
+      </c>
+      <c r="C425" t="s">
+        <v>104</v>
+      </c>
+      <c r="D425" t="s">
+        <v>9</v>
+      </c>
+      <c r="E425" t="s">
+        <v>9</v>
+      </c>
+      <c r="F425" t="s">
+        <v>35</v>
+      </c>
+      <c r="G425" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="426" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A426" t="s">
+        <v>151</v>
+      </c>
+      <c r="B426" t="s">
+        <v>28</v>
+      </c>
+      <c r="C426" t="s">
+        <v>105</v>
+      </c>
+      <c r="D426" t="s">
+        <v>9</v>
+      </c>
+      <c r="E426" t="s">
+        <v>9</v>
+      </c>
+      <c r="F426" t="s">
+        <v>35</v>
+      </c>
+      <c r="G426" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A427" t="s">
+        <v>151</v>
+      </c>
+      <c r="B427" t="s">
+        <v>28</v>
+      </c>
+      <c r="C427" t="s">
+        <v>106</v>
+      </c>
+      <c r="D427" t="s">
+        <v>9</v>
+      </c>
+      <c r="E427" t="s">
+        <v>9</v>
+      </c>
+      <c r="F427" t="s">
+        <v>35</v>
+      </c>
+      <c r="G427" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A428" t="s">
+        <v>151</v>
+      </c>
+      <c r="B428" t="s">
+        <v>28</v>
+      </c>
+      <c r="C428" t="s">
+        <v>107</v>
+      </c>
+      <c r="D428" t="s">
+        <v>9</v>
+      </c>
+      <c r="E428" t="s">
+        <v>9</v>
+      </c>
+      <c r="F428" t="s">
+        <v>35</v>
+      </c>
+      <c r="G428" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A429" t="s">
+        <v>151</v>
+      </c>
+      <c r="B429" t="s">
+        <v>22</v>
+      </c>
+      <c r="C429" t="s">
+        <v>108</v>
+      </c>
+      <c r="D429" t="s">
+        <v>35</v>
+      </c>
+      <c r="E429" t="s">
+        <v>35</v>
+      </c>
+      <c r="F429" t="s">
+        <v>35</v>
+      </c>
+      <c r="G429" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A430" t="s">
+        <v>151</v>
+      </c>
+      <c r="B430" t="s">
+        <v>22</v>
+      </c>
+      <c r="C430" t="s">
+        <v>109</v>
+      </c>
+      <c r="D430" t="s">
+        <v>35</v>
+      </c>
+      <c r="E430" t="s">
+        <v>35</v>
+      </c>
+      <c r="F430" t="s">
+        <v>35</v>
+      </c>
+      <c r="G430" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A431" t="s">
+        <v>151</v>
+      </c>
+      <c r="B431" t="s">
+        <v>22</v>
+      </c>
+      <c r="C431" t="s">
+        <v>110</v>
+      </c>
+      <c r="D431" t="s">
+        <v>35</v>
+      </c>
+      <c r="E431" t="s">
+        <v>35</v>
+      </c>
+      <c r="F431" t="s">
+        <v>35</v>
+      </c>
+      <c r="G431" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A432" t="s">
+        <v>151</v>
+      </c>
+      <c r="B432" t="s">
+        <v>27</v>
+      </c>
+      <c r="C432" t="s">
+        <v>111</v>
+      </c>
+      <c r="D432" t="s">
+        <v>35</v>
+      </c>
+      <c r="E432" t="s">
+        <v>35</v>
+      </c>
+      <c r="F432" t="s">
+        <v>35</v>
+      </c>
+      <c r="G432" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A433" t="s">
+        <v>151</v>
+      </c>
+      <c r="B433" t="s">
+        <v>22</v>
+      </c>
+      <c r="C433" t="s">
+        <v>112</v>
+      </c>
+      <c r="D433" t="s">
+        <v>35</v>
+      </c>
+      <c r="E433" t="s">
+        <v>35</v>
+      </c>
+      <c r="F433" t="s">
+        <v>35</v>
+      </c>
+      <c r="G433" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A434" t="s">
+        <v>151</v>
+      </c>
+      <c r="B434" t="s">
+        <v>22</v>
+      </c>
+      <c r="C434" t="s">
+        <v>113</v>
+      </c>
+      <c r="D434" t="s">
+        <v>35</v>
+      </c>
+      <c r="E434" t="s">
+        <v>35</v>
+      </c>
+      <c r="F434" t="s">
+        <v>35</v>
+      </c>
+      <c r="G434" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A435" t="s">
+        <v>151</v>
+      </c>
+      <c r="B435" t="s">
+        <v>22</v>
+      </c>
+      <c r="C435" t="s">
+        <v>114</v>
+      </c>
+      <c r="D435" t="s">
+        <v>35</v>
+      </c>
+      <c r="E435" t="s">
+        <v>35</v>
+      </c>
+      <c r="F435" t="s">
+        <v>35</v>
+      </c>
+      <c r="G435" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A436" t="s">
+        <v>151</v>
+      </c>
+      <c r="B436" t="s">
+        <v>25</v>
+      </c>
+      <c r="C436" t="s">
+        <v>115</v>
+      </c>
+      <c r="D436" t="s">
+        <v>35</v>
+      </c>
+      <c r="E436" t="s">
+        <v>35</v>
+      </c>
+      <c r="F436" t="s">
+        <v>35</v>
+      </c>
+      <c r="G436" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A437" t="s">
+        <v>151</v>
+      </c>
+      <c r="B437" t="s">
+        <v>22</v>
+      </c>
+      <c r="C437" t="s">
+        <v>116</v>
+      </c>
+      <c r="D437" t="s">
+        <v>35</v>
+      </c>
+      <c r="E437" t="s">
+        <v>35</v>
+      </c>
+      <c r="F437" t="s">
+        <v>35</v>
+      </c>
+      <c r="G437" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A438" t="s">
+        <v>151</v>
+      </c>
+      <c r="B438" t="s">
+        <v>22</v>
+      </c>
+      <c r="C438" t="s">
+        <v>117</v>
+      </c>
+      <c r="D438" t="s">
+        <v>35</v>
+      </c>
+      <c r="E438" t="s">
+        <v>35</v>
+      </c>
+      <c r="F438" t="s">
+        <v>35</v>
+      </c>
+      <c r="G438" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A439" t="s">
+        <v>151</v>
+      </c>
+      <c r="B439" t="s">
+        <v>23</v>
+      </c>
+      <c r="C439" t="s">
+        <v>39</v>
+      </c>
+      <c r="D439" t="s">
+        <v>9</v>
+      </c>
+      <c r="E439" t="s">
+        <v>9</v>
+      </c>
+      <c r="F439" t="s">
+        <v>35</v>
+      </c>
+      <c r="G439" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A440" t="s">
+        <v>151</v>
+      </c>
+      <c r="B440" t="s">
+        <v>29</v>
+      </c>
+      <c r="C440" t="s">
+        <v>118</v>
+      </c>
+      <c r="D440" t="s">
+        <v>35</v>
+      </c>
+      <c r="E440" t="s">
+        <v>35</v>
+      </c>
+      <c r="F440" t="s">
+        <v>35</v>
+      </c>
+      <c r="G440" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A441" t="s">
+        <v>151</v>
+      </c>
+      <c r="B441" t="s">
+        <v>30</v>
+      </c>
+      <c r="C441" t="s">
+        <v>119</v>
+      </c>
+      <c r="D441" t="s">
+        <v>9</v>
+      </c>
+      <c r="E441" t="s">
+        <v>9</v>
+      </c>
+      <c r="F441" t="s">
+        <v>35</v>
+      </c>
+      <c r="G441" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A442" t="s">
+        <v>151</v>
+      </c>
+      <c r="B442" t="s">
+        <v>32</v>
+      </c>
+      <c r="C442" t="s">
+        <v>120</v>
+      </c>
+      <c r="D442" t="s">
+        <v>35</v>
+      </c>
+      <c r="E442" t="s">
+        <v>35</v>
+      </c>
+      <c r="F442" t="s">
+        <v>35</v>
+      </c>
+      <c r="G442" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A443" t="s">
+        <v>151</v>
+      </c>
+      <c r="B443" t="s">
+        <v>33</v>
+      </c>
+      <c r="C443" t="s">
+        <v>121</v>
+      </c>
+      <c r="D443" t="s">
+        <v>35</v>
+      </c>
+      <c r="E443" t="s">
+        <v>35</v>
+      </c>
+      <c r="F443" t="s">
+        <v>35</v>
+      </c>
+      <c r="G443" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A444" t="s">
+        <v>151</v>
+      </c>
+      <c r="B444" t="s">
+        <v>31</v>
+      </c>
+      <c r="C444" t="s">
+        <v>31</v>
+      </c>
+      <c r="D444" t="s">
+        <v>35</v>
+      </c>
+      <c r="E444" t="s">
+        <v>35</v>
+      </c>
+      <c r="F444" t="s">
+        <v>35</v>
+      </c>
+      <c r="G444" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A445" t="s">
+        <v>151</v>
+      </c>
+      <c r="B445" t="s">
+        <v>34</v>
+      </c>
+      <c r="C445" t="s">
+        <v>122</v>
+      </c>
+      <c r="D445" t="s">
+        <v>35</v>
+      </c>
+      <c r="E445" t="s">
+        <v>35</v>
+      </c>
+      <c r="F445" t="s">
+        <v>35</v>
+      </c>
+      <c r="G445" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A446" t="s">
+        <v>151</v>
+      </c>
+      <c r="B446" t="s">
+        <v>123</v>
+      </c>
+      <c r="C446" t="s">
+        <v>124</v>
+      </c>
+      <c r="D446" t="s">
+        <v>35</v>
+      </c>
+      <c r="E446" t="s">
+        <v>35</v>
+      </c>
+      <c r="F446" t="s">
+        <v>35</v>
+      </c>
+      <c r="G446" t="s">
+        <v>35</v>
+      </c>
+      <c r="H446" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H357" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Nada_Yehia"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/permissions.xlsx
+++ b/data/permissions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED6D893-23B7-4B87-87ED-BB20F3A7F641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C15748-AF0B-4625-8786-B14E67850A6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -509,13 +509,13 @@
     <t>Quality And Performance Director</t>
   </si>
   <si>
-    <t>adham_Ismail</t>
-  </si>
-  <si>
-    <t>nada_Yehia</t>
-  </si>
-  <si>
     <t>mustafa</t>
+  </si>
+  <si>
+    <t>adham_ismail</t>
+  </si>
+  <si>
+    <t>nada_yehia</t>
   </si>
 </sst>
 </file>
@@ -907,7 +907,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
@@ -958,7 +958,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
         <v>148</v>
